--- a/mockdata/StarAMR_Metrics.xlsx
+++ b/mockdata/StarAMR_Metrics.xlsx
@@ -11,7 +11,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" uniqueCount="21">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" uniqueCount="25">
   <si>
     <t>Isolate ID</t>
   </si>
@@ -25,6 +25,9 @@
     <t>Predicted Phenotype</t>
   </si>
   <si>
+    <t>SIR Profile</t>
+  </si>
+  <si>
     <t>Plasmid</t>
   </si>
   <si>
@@ -46,6 +49,9 @@
     <t>kanamycin, ampicillin, ceftriaxone</t>
   </si>
   <si>
+    <t>Resistant</t>
+  </si>
+  <si>
     <t>IncFIB(K)</t>
   </si>
   <si>
@@ -61,6 +67,9 @@
     <t>tetracycline</t>
   </si>
   <si>
+    <t>Intermediate</t>
+  </si>
+  <si>
     <t>Col(BS512)</t>
   </si>
   <si>
@@ -71,6 +80,9 @@
   </si>
   <si>
     <t>ampicillin, sulfisoxazole</t>
+  </si>
+  <si>
+    <t>Susceptible</t>
   </si>
   <si>
     <t>IncX1</t>
@@ -95,6 +107,11 @@
       <name val="Helvetica Neue"/>
     </font>
     <font>
+      <sz val="15"/>
+      <color indexed="8"/>
+      <name val="Calibri"/>
+    </font>
+    <font>
       <b val="1"/>
       <sz val="12"/>
       <color indexed="9"/>
@@ -105,14 +122,8 @@
       <color indexed="9"/>
       <name val="Helvetica"/>
     </font>
-    <font>
-      <b val="1"/>
-      <sz val="10"/>
-      <color indexed="8"/>
-      <name val="Helvetica Neue"/>
-    </font>
   </fonts>
-  <fills count="4">
+  <fills count="3">
     <fill>
       <patternFill patternType="none"/>
     </fill>
@@ -125,109 +136,13 @@
         <bgColor auto="1"/>
       </patternFill>
     </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor indexed="13"/>
-        <bgColor auto="1"/>
-      </patternFill>
-    </fill>
   </fills>
-  <borders count="8">
+  <borders count="2">
     <border>
       <left/>
       <right/>
       <top/>
       <bottom/>
-      <diagonal/>
-    </border>
-    <border>
-      <left style="thin">
-        <color indexed="11"/>
-      </left>
-      <right style="thin">
-        <color indexed="11"/>
-      </right>
-      <top style="thin">
-        <color indexed="11"/>
-      </top>
-      <bottom style="thin">
-        <color indexed="12"/>
-      </bottom>
-      <diagonal/>
-    </border>
-    <border>
-      <left style="thin">
-        <color indexed="11"/>
-      </left>
-      <right style="thin">
-        <color indexed="12"/>
-      </right>
-      <top style="thin">
-        <color indexed="12"/>
-      </top>
-      <bottom style="thin">
-        <color indexed="11"/>
-      </bottom>
-      <diagonal/>
-    </border>
-    <border>
-      <left style="thin">
-        <color indexed="12"/>
-      </left>
-      <right style="thin">
-        <color indexed="11"/>
-      </right>
-      <top style="thin">
-        <color indexed="12"/>
-      </top>
-      <bottom style="thin">
-        <color indexed="11"/>
-      </bottom>
-      <diagonal/>
-    </border>
-    <border>
-      <left style="thin">
-        <color indexed="11"/>
-      </left>
-      <right style="thin">
-        <color indexed="11"/>
-      </right>
-      <top style="thin">
-        <color indexed="12"/>
-      </top>
-      <bottom style="thin">
-        <color indexed="11"/>
-      </bottom>
-      <diagonal/>
-    </border>
-    <border>
-      <left style="thin">
-        <color indexed="11"/>
-      </left>
-      <right style="thin">
-        <color indexed="12"/>
-      </right>
-      <top style="thin">
-        <color indexed="11"/>
-      </top>
-      <bottom style="thin">
-        <color indexed="11"/>
-      </bottom>
-      <diagonal/>
-    </border>
-    <border>
-      <left style="thin">
-        <color indexed="12"/>
-      </left>
-      <right style="thin">
-        <color indexed="11"/>
-      </right>
-      <top style="thin">
-        <color indexed="11"/>
-      </top>
-      <bottom style="thin">
-        <color indexed="11"/>
-      </bottom>
       <diagonal/>
     </border>
     <border>
@@ -251,62 +166,29 @@
       <alignment vertical="top" wrapText="1"/>
     </xf>
   </cellStyleXfs>
-  <cellXfs count="19">
+  <cellXfs count="8">
     <xf numFmtId="0" fontId="0" applyNumberFormat="0" applyFont="1" applyFill="0" applyBorder="0" applyAlignment="1" applyProtection="0">
       <alignment vertical="top" wrapText="1"/>
     </xf>
     <xf numFmtId="0" fontId="0" applyNumberFormat="1" applyFont="1" applyFill="0" applyBorder="0" applyAlignment="1" applyProtection="0">
       <alignment vertical="top" wrapText="1"/>
     </xf>
-    <xf numFmtId="49" fontId="2" fillId="2" borderId="1" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="0">
+    <xf numFmtId="49" fontId="3" fillId="2" borderId="1" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="0">
       <alignment vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="2" fillId="2" borderId="1" applyNumberFormat="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="0">
+    <xf numFmtId="0" fontId="3" fillId="2" borderId="1" applyNumberFormat="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="0">
       <alignment vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="49" fontId="3" borderId="2" applyNumberFormat="1" applyFont="1" applyFill="0" applyBorder="1" applyAlignment="1" applyProtection="0">
+    <xf numFmtId="49" fontId="4" borderId="1" applyNumberFormat="1" applyFont="1" applyFill="0" applyBorder="1" applyAlignment="1" applyProtection="0">
       <alignment vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="49" fontId="3" borderId="3" applyNumberFormat="1" applyFont="1" applyFill="0" applyBorder="1" applyAlignment="1" applyProtection="0">
+    <xf numFmtId="0" fontId="4" borderId="1" applyNumberFormat="1" applyFont="1" applyFill="0" applyBorder="1" applyAlignment="1" applyProtection="0">
       <alignment vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="49" fontId="3" borderId="4" applyNumberFormat="1" applyFont="1" applyFill="0" applyBorder="1" applyAlignment="1" applyProtection="0">
+    <xf numFmtId="0" fontId="4" borderId="1" applyNumberFormat="0" applyFont="1" applyFill="0" applyBorder="1" applyAlignment="1" applyProtection="0">
       <alignment vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="3" borderId="4" applyNumberFormat="1" applyFont="1" applyFill="0" applyBorder="1" applyAlignment="1" applyProtection="0">
-      <alignment vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="3" borderId="4" applyNumberFormat="0" applyFont="1" applyFill="0" applyBorder="1" applyAlignment="1" applyProtection="0">
-      <alignment vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="49" fontId="3" borderId="5" applyNumberFormat="1" applyFont="1" applyFill="0" applyBorder="1" applyAlignment="1" applyProtection="0">
-      <alignment vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="49" fontId="3" borderId="6" applyNumberFormat="1" applyFont="1" applyFill="0" applyBorder="1" applyAlignment="1" applyProtection="0">
-      <alignment vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="49" fontId="3" borderId="7" applyNumberFormat="1" applyFont="1" applyFill="0" applyBorder="1" applyAlignment="1" applyProtection="0">
-      <alignment vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="3" borderId="7" applyNumberFormat="1" applyFont="1" applyFill="0" applyBorder="1" applyAlignment="1" applyProtection="0">
-      <alignment vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="3" borderId="7" applyNumberFormat="0" applyFont="1" applyFill="0" applyBorder="1" applyAlignment="1" applyProtection="0">
-      <alignment vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="3" borderId="5" applyNumberFormat="0" applyFont="1" applyFill="0" applyBorder="1" applyAlignment="1" applyProtection="0">
-      <alignment vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="3" borderId="6" applyNumberFormat="0" applyFont="1" applyFill="0" applyBorder="1" applyAlignment="1" applyProtection="0">
-      <alignment vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" borderId="7" applyNumberFormat="0" applyFont="1" applyFill="0" applyBorder="1" applyAlignment="1" applyProtection="0">
-      <alignment vertical="top" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="4" fillId="3" borderId="5" applyNumberFormat="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="0">
-      <alignment vertical="top" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" borderId="6" applyNumberFormat="0" applyFont="1" applyFill="0" applyBorder="1" applyAlignment="1" applyProtection="0">
+    <xf numFmtId="0" fontId="0" borderId="1" applyNumberFormat="0" applyFont="1" applyFill="0" applyBorder="1" applyAlignment="1" applyProtection="0">
       <alignment vertical="top" wrapText="1"/>
     </xf>
   </cellXfs>
@@ -329,8 +211,6 @@
       <rgbColor rgb="ff1f1f1f"/>
       <rgbColor rgb="ffefefef"/>
       <rgbColor rgb="ffa5a5a5"/>
-      <rgbColor rgb="ff3f3f3f"/>
-      <rgbColor rgb="ffdbdbdb"/>
     </indexedColors>
   </colors>
 </styleSheet>
@@ -347,10 +227,10 @@
         <a:srgbClr val="FFFFFF"/>
       </a:lt1>
       <a:dk2>
-        <a:srgbClr val="5E5E5E"/>
+        <a:srgbClr val="A7A7A7"/>
       </a:dk2>
       <a:lt2>
-        <a:srgbClr val="D5D5D5"/>
+        <a:srgbClr val="535353"/>
       </a:lt2>
       <a:accent1>
         <a:srgbClr val="00A2FF"/>
@@ -527,11 +407,14 @@
     <a:spDef>
       <a:spPr>
         <a:solidFill>
-          <a:srgbClr val="000000"/>
+          <a:srgbClr val="FFFFFF"/>
         </a:solidFill>
-        <a:ln w="12700" cap="flat">
-          <a:noFill/>
-          <a:miter lim="400000"/>
+        <a:ln w="25400" cap="flat">
+          <a:solidFill>
+            <a:schemeClr val="accent1"/>
+          </a:solidFill>
+          <a:prstDash val="solid"/>
+          <a:round/>
         </a:ln>
         <a:effectLst/>
         <a:sp3d/>
@@ -540,33 +423,33 @@
         <a:spAutoFit/>
       </a:bodyPr>
       <a:lstStyle>
-        <a:defPPr marL="0" marR="0" indent="0" algn="ctr" defTabSz="584200" rtl="0" fontAlgn="auto" latinLnBrk="0" hangingPunct="0">
-          <a:lnSpc>
-            <a:spcPct val="100000"/>
-          </a:lnSpc>
-          <a:spcBef>
-            <a:spcPts val="0"/>
-          </a:spcBef>
-          <a:spcAft>
-            <a:spcPts val="0"/>
-          </a:spcAft>
-          <a:buClrTx/>
-          <a:buSzTx/>
-          <a:buFontTx/>
-          <a:buNone/>
-          <a:defRPr b="0" baseline="0" cap="none" i="0" spc="0" strike="noStrike" sz="1200" u="none" kumimoji="0" normalizeH="0">
-            <a:ln>
-              <a:noFill/>
-            </a:ln>
-            <a:solidFill>
-              <a:srgbClr val="FFFFFF"/>
-            </a:solidFill>
-            <a:effectLst/>
-            <a:uFillTx/>
-            <a:latin typeface="Helvetica Neue Medium"/>
-            <a:ea typeface="Helvetica Neue Medium"/>
-            <a:cs typeface="Helvetica Neue Medium"/>
-            <a:sym typeface="Helvetica Neue Medium"/>
+        <a:defPPr marL="0" marR="0" indent="0" algn="l" defTabSz="914400" rtl="0" fontAlgn="auto" latinLnBrk="0" hangingPunct="0">
+          <a:lnSpc>
+            <a:spcPct val="100000"/>
+          </a:lnSpc>
+          <a:spcBef>
+            <a:spcPts val="0"/>
+          </a:spcBef>
+          <a:spcAft>
+            <a:spcPts val="0"/>
+          </a:spcAft>
+          <a:buClrTx/>
+          <a:buSzTx/>
+          <a:buFontTx/>
+          <a:buNone/>
+          <a:defRPr b="0" baseline="0" cap="none" i="0" spc="0" strike="noStrike" sz="1100" u="none" kumimoji="0" normalizeH="0">
+            <a:ln>
+              <a:noFill/>
+            </a:ln>
+            <a:solidFill>
+              <a:srgbClr val="000000"/>
+            </a:solidFill>
+            <a:effectLst/>
+            <a:uFillTx/>
+            <a:latin typeface="+mn-lt"/>
+            <a:ea typeface="+mn-ea"/>
+            <a:cs typeface="+mn-cs"/>
+            <a:sym typeface="Helvetica Neue"/>
           </a:defRPr>
         </a:defPPr>
         <a:lvl1pPr marL="0" marR="0" indent="0" algn="l" defTabSz="914400" rtl="0" fontAlgn="auto" latinLnBrk="1" hangingPunct="0">
@@ -805,12 +688,12 @@
     <a:lnDef>
       <a:spPr>
         <a:noFill/>
-        <a:ln w="12700" cap="flat">
+        <a:ln w="25400" cap="flat">
           <a:solidFill>
-            <a:srgbClr val="000000"/>
+            <a:schemeClr val="accent1"/>
           </a:solidFill>
           <a:prstDash val="solid"/>
-          <a:miter lim="400000"/>
+          <a:round/>
         </a:ln>
         <a:effectLst/>
         <a:sp3d/>
@@ -1091,7 +974,7 @@
         <a:spAutoFit/>
       </a:bodyPr>
       <a:lstStyle>
-        <a:defPPr marL="0" marR="0" indent="0" algn="l" defTabSz="457200" rtl="0" fontAlgn="auto" latinLnBrk="0" hangingPunct="0">
+        <a:defPPr marL="0" marR="0" indent="0" algn="l" defTabSz="914400" rtl="0" fontAlgn="auto" latinLnBrk="0" hangingPunct="0">
           <a:lnSpc>
             <a:spcPct val="100000"/>
           </a:lnSpc>
@@ -1359,11 +1242,11 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
-  <dimension ref="A1:M22"/>
-  <sheetFormatPr defaultColWidth="16.3333" defaultRowHeight="19.9" customHeight="1" outlineLevelRow="0" outlineLevelCol="0"/>
+  <dimension ref="A1:O22"/>
+  <sheetFormatPr defaultColWidth="16.3333" defaultRowHeight="13.9" customHeight="1" outlineLevelRow="0" outlineLevelCol="0"/>
   <cols>
-    <col min="1" max="13" width="16.3516" style="1" customWidth="1"/>
-    <col min="14" max="16384" width="16.3516" style="1" customWidth="1"/>
+    <col min="1" max="15" width="16.3516" style="1" customWidth="1"/>
+    <col min="16" max="16384" width="16.3516" style="1" customWidth="1"/>
   </cols>
   <sheetData>
     <row r="1" ht="60.55" customHeight="1">
@@ -1388,369 +1271,421 @@
       <c r="G1" t="s" s="2">
         <v>6</v>
       </c>
-      <c r="H1" s="3"/>
+      <c r="H1" t="s" s="2">
+        <v>7</v>
+      </c>
       <c r="I1" s="3"/>
       <c r="J1" s="3"/>
       <c r="K1" s="3"/>
       <c r="L1" s="3"/>
       <c r="M1" s="3"/>
+      <c r="N1" s="3"/>
+      <c r="O1" s="3"/>
     </row>
     <row r="2" ht="74.55" customHeight="1">
       <c r="A2" t="s" s="4">
-        <v>7</v>
-      </c>
-      <c r="B2" t="s" s="5">
         <v>8</v>
       </c>
-      <c r="C2" t="s" s="6">
+      <c r="B2" t="s" s="4">
         <v>9</v>
       </c>
-      <c r="D2" t="s" s="6">
+      <c r="C2" t="s" s="4">
         <v>10</v>
       </c>
-      <c r="E2" t="s" s="6">
+      <c r="D2" t="s" s="4">
         <v>11</v>
       </c>
-      <c r="F2" s="7">
+      <c r="E2" t="s" s="4">
+        <v>12</v>
+      </c>
+      <c r="F2" t="s" s="4">
+        <v>13</v>
+      </c>
+      <c r="G2" s="5">
         <v>5017831</v>
       </c>
-      <c r="G2" s="7">
+      <c r="H2" s="5">
         <v>156657</v>
       </c>
-      <c r="H2" s="8"/>
-      <c r="I2" s="8"/>
-      <c r="J2" s="8"/>
-      <c r="K2" s="8"/>
-      <c r="L2" s="8"/>
-      <c r="M2" s="8"/>
+      <c r="I2" s="6"/>
+      <c r="J2" s="6"/>
+      <c r="K2" s="6"/>
+      <c r="L2" s="6"/>
+      <c r="M2" s="6"/>
+      <c r="N2" s="6"/>
+      <c r="O2" s="6"/>
     </row>
     <row r="3" ht="46.35" customHeight="1">
-      <c r="A3" t="s" s="9">
-        <v>12</v>
-      </c>
-      <c r="B3" t="s" s="10">
-        <v>13</v>
-      </c>
-      <c r="C3" t="s" s="11">
+      <c r="A3" t="s" s="4">
         <v>14</v>
       </c>
-      <c r="D3" t="s" s="11">
+      <c r="B3" t="s" s="4">
         <v>15</v>
       </c>
-      <c r="E3" t="s" s="11">
+      <c r="C3" t="s" s="4">
         <v>16</v>
       </c>
-      <c r="F3" s="12">
+      <c r="D3" t="s" s="4">
+        <v>17</v>
+      </c>
+      <c r="E3" t="s" s="4">
+        <v>18</v>
+      </c>
+      <c r="F3" t="s" s="4">
+        <v>19</v>
+      </c>
+      <c r="G3" s="5">
         <v>6133820</v>
       </c>
-      <c r="G3" s="12">
+      <c r="H3" s="5">
         <v>1660</v>
       </c>
-      <c r="H3" s="13"/>
-      <c r="I3" s="13"/>
-      <c r="J3" s="13"/>
-      <c r="K3" s="13"/>
-      <c r="L3" s="13"/>
-      <c r="M3" s="13"/>
+      <c r="I3" s="6"/>
+      <c r="J3" s="6"/>
+      <c r="K3" s="6"/>
+      <c r="L3" s="6"/>
+      <c r="M3" s="6"/>
+      <c r="N3" s="6"/>
+      <c r="O3" s="6"/>
     </row>
     <row r="4" ht="60.35" customHeight="1">
-      <c r="A4" t="s" s="9">
-        <v>17</v>
-      </c>
-      <c r="B4" t="s" s="10">
-        <v>8</v>
-      </c>
-      <c r="C4" t="s" s="11">
-        <v>18</v>
-      </c>
-      <c r="D4" t="s" s="11">
-        <v>19</v>
-      </c>
-      <c r="E4" t="s" s="11">
+      <c r="A4" t="s" s="4">
         <v>20</v>
       </c>
-      <c r="F4" s="12">
+      <c r="B4" t="s" s="4">
+        <v>9</v>
+      </c>
+      <c r="C4" t="s" s="4">
+        <v>21</v>
+      </c>
+      <c r="D4" t="s" s="4">
+        <v>22</v>
+      </c>
+      <c r="E4" t="s" s="4">
+        <v>23</v>
+      </c>
+      <c r="F4" t="s" s="4">
+        <v>24</v>
+      </c>
+      <c r="G4" s="5">
         <v>5025249</v>
       </c>
-      <c r="G4" s="12">
+      <c r="H4" s="5">
         <v>125507</v>
       </c>
-      <c r="H4" s="13"/>
-      <c r="I4" s="13"/>
-      <c r="J4" s="13"/>
-      <c r="K4" s="13"/>
-      <c r="L4" s="13"/>
-      <c r="M4" s="13"/>
+      <c r="I4" s="6"/>
+      <c r="J4" s="6"/>
+      <c r="K4" s="6"/>
+      <c r="L4" s="6"/>
+      <c r="M4" s="6"/>
+      <c r="N4" s="6"/>
+      <c r="O4" s="6"/>
     </row>
     <row r="5" ht="46.35" customHeight="1">
-      <c r="A5" s="14"/>
-      <c r="B5" s="15"/>
-      <c r="C5" s="13"/>
-      <c r="D5" s="13"/>
-      <c r="E5" s="13"/>
-      <c r="F5" s="13"/>
-      <c r="G5" s="13"/>
-      <c r="H5" s="16"/>
-      <c r="I5" s="16"/>
-      <c r="J5" s="16"/>
-      <c r="K5" s="16"/>
-      <c r="L5" s="16"/>
-      <c r="M5" s="16"/>
+      <c r="A5" s="6"/>
+      <c r="B5" s="6"/>
+      <c r="C5" s="6"/>
+      <c r="D5" s="6"/>
+      <c r="E5" s="6"/>
+      <c r="F5" s="6"/>
+      <c r="G5" s="6"/>
+      <c r="H5" s="6"/>
+      <c r="I5" s="6"/>
+      <c r="J5" s="6"/>
+      <c r="K5" s="6"/>
+      <c r="L5" s="6"/>
+      <c r="M5" s="7"/>
+      <c r="N5" s="7"/>
+      <c r="O5" s="7"/>
     </row>
     <row r="6" ht="20.05" customHeight="1">
-      <c r="A6" s="17"/>
-      <c r="B6" s="18"/>
-      <c r="C6" s="16"/>
-      <c r="D6" s="16"/>
-      <c r="E6" s="16"/>
-      <c r="F6" s="16"/>
-      <c r="G6" s="16"/>
-      <c r="H6" s="16"/>
-      <c r="I6" s="16"/>
-      <c r="J6" s="16"/>
-      <c r="K6" s="16"/>
-      <c r="L6" s="16"/>
-      <c r="M6" s="16"/>
+      <c r="A6" s="7"/>
+      <c r="B6" s="7"/>
+      <c r="C6" s="7"/>
+      <c r="D6" s="7"/>
+      <c r="E6" s="7"/>
+      <c r="F6" s="7"/>
+      <c r="G6" s="7"/>
+      <c r="H6" s="7"/>
+      <c r="I6" s="7"/>
+      <c r="J6" s="7"/>
+      <c r="K6" s="7"/>
+      <c r="L6" s="7"/>
+      <c r="M6" s="7"/>
+      <c r="N6" s="7"/>
+      <c r="O6" s="7"/>
     </row>
     <row r="7" ht="20.05" customHeight="1">
-      <c r="A7" s="17"/>
-      <c r="B7" s="18"/>
-      <c r="C7" s="16"/>
-      <c r="D7" s="16"/>
-      <c r="E7" s="16"/>
-      <c r="F7" s="16"/>
-      <c r="G7" s="16"/>
-      <c r="H7" s="16"/>
-      <c r="I7" s="16"/>
-      <c r="J7" s="16"/>
-      <c r="K7" s="16"/>
-      <c r="L7" s="16"/>
-      <c r="M7" s="16"/>
+      <c r="A7" s="7"/>
+      <c r="B7" s="7"/>
+      <c r="C7" s="7"/>
+      <c r="D7" s="7"/>
+      <c r="E7" s="7"/>
+      <c r="F7" s="7"/>
+      <c r="G7" s="7"/>
+      <c r="H7" s="7"/>
+      <c r="I7" s="7"/>
+      <c r="J7" s="7"/>
+      <c r="K7" s="7"/>
+      <c r="L7" s="7"/>
+      <c r="M7" s="7"/>
+      <c r="N7" s="7"/>
+      <c r="O7" s="7"/>
     </row>
     <row r="8" ht="20.05" customHeight="1">
-      <c r="A8" s="17"/>
-      <c r="B8" s="18"/>
-      <c r="C8" s="16"/>
-      <c r="D8" s="16"/>
-      <c r="E8" s="16"/>
-      <c r="F8" s="16"/>
-      <c r="G8" s="16"/>
-      <c r="H8" s="16"/>
-      <c r="I8" s="16"/>
-      <c r="J8" s="16"/>
-      <c r="K8" s="16"/>
-      <c r="L8" s="16"/>
-      <c r="M8" s="16"/>
+      <c r="A8" s="7"/>
+      <c r="B8" s="7"/>
+      <c r="C8" s="7"/>
+      <c r="D8" s="7"/>
+      <c r="E8" s="7"/>
+      <c r="F8" s="7"/>
+      <c r="G8" s="7"/>
+      <c r="H8" s="7"/>
+      <c r="I8" s="7"/>
+      <c r="J8" s="7"/>
+      <c r="K8" s="7"/>
+      <c r="L8" s="7"/>
+      <c r="M8" s="7"/>
+      <c r="N8" s="7"/>
+      <c r="O8" s="7"/>
     </row>
     <row r="9" ht="20.05" customHeight="1">
-      <c r="A9" s="17"/>
-      <c r="B9" s="18"/>
-      <c r="C9" s="16"/>
-      <c r="D9" s="16"/>
-      <c r="E9" s="16"/>
-      <c r="F9" s="16"/>
-      <c r="G9" s="16"/>
-      <c r="H9" s="16"/>
-      <c r="I9" s="16"/>
-      <c r="J9" s="16"/>
-      <c r="K9" s="16"/>
-      <c r="L9" s="16"/>
-      <c r="M9" s="16"/>
+      <c r="A9" s="7"/>
+      <c r="B9" s="7"/>
+      <c r="C9" s="7"/>
+      <c r="D9" s="7"/>
+      <c r="E9" s="7"/>
+      <c r="F9" s="7"/>
+      <c r="G9" s="7"/>
+      <c r="H9" s="7"/>
+      <c r="I9" s="7"/>
+      <c r="J9" s="7"/>
+      <c r="K9" s="7"/>
+      <c r="L9" s="7"/>
+      <c r="M9" s="7"/>
+      <c r="N9" s="7"/>
+      <c r="O9" s="7"/>
     </row>
     <row r="10" ht="20.05" customHeight="1">
-      <c r="A10" s="17"/>
-      <c r="B10" s="18"/>
-      <c r="C10" s="16"/>
-      <c r="D10" s="16"/>
-      <c r="E10" s="16"/>
-      <c r="F10" s="16"/>
-      <c r="G10" s="16"/>
-      <c r="H10" s="16"/>
-      <c r="I10" s="16"/>
-      <c r="J10" s="16"/>
-      <c r="K10" s="16"/>
-      <c r="L10" s="16"/>
-      <c r="M10" s="16"/>
+      <c r="A10" s="7"/>
+      <c r="B10" s="7"/>
+      <c r="C10" s="7"/>
+      <c r="D10" s="7"/>
+      <c r="E10" s="7"/>
+      <c r="F10" s="7"/>
+      <c r="G10" s="7"/>
+      <c r="H10" s="7"/>
+      <c r="I10" s="7"/>
+      <c r="J10" s="7"/>
+      <c r="K10" s="7"/>
+      <c r="L10" s="7"/>
+      <c r="M10" s="7"/>
+      <c r="N10" s="7"/>
+      <c r="O10" s="7"/>
     </row>
     <row r="11" ht="20.05" customHeight="1">
-      <c r="A11" s="17"/>
-      <c r="B11" s="18"/>
-      <c r="C11" s="16"/>
-      <c r="D11" s="16"/>
-      <c r="E11" s="16"/>
-      <c r="F11" s="16"/>
-      <c r="G11" s="16"/>
-      <c r="H11" s="16"/>
-      <c r="I11" s="16"/>
-      <c r="J11" s="16"/>
-      <c r="K11" s="16"/>
-      <c r="L11" s="16"/>
-      <c r="M11" s="16"/>
+      <c r="A11" s="7"/>
+      <c r="B11" s="7"/>
+      <c r="C11" s="7"/>
+      <c r="D11" s="7"/>
+      <c r="E11" s="7"/>
+      <c r="F11" s="7"/>
+      <c r="G11" s="7"/>
+      <c r="H11" s="7"/>
+      <c r="I11" s="7"/>
+      <c r="J11" s="7"/>
+      <c r="K11" s="7"/>
+      <c r="L11" s="7"/>
+      <c r="M11" s="7"/>
+      <c r="N11" s="7"/>
+      <c r="O11" s="7"/>
     </row>
     <row r="12" ht="20.05" customHeight="1">
-      <c r="A12" s="17"/>
-      <c r="B12" s="18"/>
-      <c r="C12" s="16"/>
-      <c r="D12" s="16"/>
-      <c r="E12" s="16"/>
-      <c r="F12" s="16"/>
-      <c r="G12" s="16"/>
-      <c r="H12" s="16"/>
-      <c r="I12" s="16"/>
-      <c r="J12" s="16"/>
-      <c r="K12" s="16"/>
-      <c r="L12" s="16"/>
-      <c r="M12" s="16"/>
+      <c r="A12" s="7"/>
+      <c r="B12" s="7"/>
+      <c r="C12" s="7"/>
+      <c r="D12" s="7"/>
+      <c r="E12" s="7"/>
+      <c r="F12" s="7"/>
+      <c r="G12" s="7"/>
+      <c r="H12" s="7"/>
+      <c r="I12" s="7"/>
+      <c r="J12" s="7"/>
+      <c r="K12" s="7"/>
+      <c r="L12" s="7"/>
+      <c r="M12" s="7"/>
+      <c r="N12" s="7"/>
+      <c r="O12" s="7"/>
     </row>
     <row r="13" ht="20.05" customHeight="1">
-      <c r="A13" s="17"/>
-      <c r="B13" s="18"/>
-      <c r="C13" s="16"/>
-      <c r="D13" s="16"/>
-      <c r="E13" s="16"/>
-      <c r="F13" s="16"/>
-      <c r="G13" s="16"/>
-      <c r="H13" s="16"/>
-      <c r="I13" s="16"/>
-      <c r="J13" s="16"/>
-      <c r="K13" s="16"/>
-      <c r="L13" s="16"/>
-      <c r="M13" s="16"/>
+      <c r="A13" s="7"/>
+      <c r="B13" s="7"/>
+      <c r="C13" s="7"/>
+      <c r="D13" s="7"/>
+      <c r="E13" s="7"/>
+      <c r="F13" s="7"/>
+      <c r="G13" s="7"/>
+      <c r="H13" s="7"/>
+      <c r="I13" s="7"/>
+      <c r="J13" s="7"/>
+      <c r="K13" s="7"/>
+      <c r="L13" s="7"/>
+      <c r="M13" s="7"/>
+      <c r="N13" s="7"/>
+      <c r="O13" s="7"/>
     </row>
     <row r="14" ht="20.05" customHeight="1">
-      <c r="A14" s="17"/>
-      <c r="B14" s="18"/>
-      <c r="C14" s="16"/>
-      <c r="D14" s="16"/>
-      <c r="E14" s="16"/>
-      <c r="F14" s="16"/>
-      <c r="G14" s="16"/>
-      <c r="H14" s="16"/>
-      <c r="I14" s="16"/>
-      <c r="J14" s="16"/>
-      <c r="K14" s="16"/>
-      <c r="L14" s="16"/>
-      <c r="M14" s="16"/>
+      <c r="A14" s="7"/>
+      <c r="B14" s="7"/>
+      <c r="C14" s="7"/>
+      <c r="D14" s="7"/>
+      <c r="E14" s="7"/>
+      <c r="F14" s="7"/>
+      <c r="G14" s="7"/>
+      <c r="H14" s="7"/>
+      <c r="I14" s="7"/>
+      <c r="J14" s="7"/>
+      <c r="K14" s="7"/>
+      <c r="L14" s="7"/>
+      <c r="M14" s="7"/>
+      <c r="N14" s="7"/>
+      <c r="O14" s="7"/>
     </row>
     <row r="15" ht="20.05" customHeight="1">
-      <c r="A15" s="17"/>
-      <c r="B15" s="18"/>
-      <c r="C15" s="16"/>
-      <c r="D15" s="16"/>
-      <c r="E15" s="16"/>
-      <c r="F15" s="16"/>
-      <c r="G15" s="16"/>
-      <c r="H15" s="16"/>
-      <c r="I15" s="16"/>
-      <c r="J15" s="16"/>
-      <c r="K15" s="16"/>
-      <c r="L15" s="16"/>
-      <c r="M15" s="16"/>
+      <c r="A15" s="7"/>
+      <c r="B15" s="7"/>
+      <c r="C15" s="7"/>
+      <c r="D15" s="7"/>
+      <c r="E15" s="7"/>
+      <c r="F15" s="7"/>
+      <c r="G15" s="7"/>
+      <c r="H15" s="7"/>
+      <c r="I15" s="7"/>
+      <c r="J15" s="7"/>
+      <c r="K15" s="7"/>
+      <c r="L15" s="7"/>
+      <c r="M15" s="7"/>
+      <c r="N15" s="7"/>
+      <c r="O15" s="7"/>
     </row>
     <row r="16" ht="20.05" customHeight="1">
-      <c r="A16" s="17"/>
-      <c r="B16" s="18"/>
-      <c r="C16" s="16"/>
-      <c r="D16" s="16"/>
-      <c r="E16" s="16"/>
-      <c r="F16" s="16"/>
-      <c r="G16" s="16"/>
-      <c r="H16" s="16"/>
-      <c r="I16" s="16"/>
-      <c r="J16" s="16"/>
-      <c r="K16" s="16"/>
-      <c r="L16" s="16"/>
-      <c r="M16" s="16"/>
+      <c r="A16" s="7"/>
+      <c r="B16" s="7"/>
+      <c r="C16" s="7"/>
+      <c r="D16" s="7"/>
+      <c r="E16" s="7"/>
+      <c r="F16" s="7"/>
+      <c r="G16" s="7"/>
+      <c r="H16" s="7"/>
+      <c r="I16" s="7"/>
+      <c r="J16" s="7"/>
+      <c r="K16" s="7"/>
+      <c r="L16" s="7"/>
+      <c r="M16" s="7"/>
+      <c r="N16" s="7"/>
+      <c r="O16" s="7"/>
     </row>
     <row r="17" ht="20.05" customHeight="1">
-      <c r="A17" s="17"/>
-      <c r="B17" s="18"/>
-      <c r="C17" s="16"/>
-      <c r="D17" s="16"/>
-      <c r="E17" s="16"/>
-      <c r="F17" s="16"/>
-      <c r="G17" s="16"/>
-      <c r="H17" s="16"/>
-      <c r="I17" s="16"/>
-      <c r="J17" s="16"/>
-      <c r="K17" s="16"/>
-      <c r="L17" s="16"/>
-      <c r="M17" s="16"/>
+      <c r="A17" s="7"/>
+      <c r="B17" s="7"/>
+      <c r="C17" s="7"/>
+      <c r="D17" s="7"/>
+      <c r="E17" s="7"/>
+      <c r="F17" s="7"/>
+      <c r="G17" s="7"/>
+      <c r="H17" s="7"/>
+      <c r="I17" s="7"/>
+      <c r="J17" s="7"/>
+      <c r="K17" s="7"/>
+      <c r="L17" s="7"/>
+      <c r="M17" s="7"/>
+      <c r="N17" s="7"/>
+      <c r="O17" s="7"/>
     </row>
     <row r="18" ht="20.05" customHeight="1">
-      <c r="A18" s="17"/>
-      <c r="B18" s="18"/>
-      <c r="C18" s="16"/>
-      <c r="D18" s="16"/>
-      <c r="E18" s="16"/>
-      <c r="F18" s="16"/>
-      <c r="G18" s="16"/>
-      <c r="H18" s="16"/>
-      <c r="I18" s="16"/>
-      <c r="J18" s="16"/>
-      <c r="K18" s="16"/>
-      <c r="L18" s="16"/>
-      <c r="M18" s="16"/>
+      <c r="A18" s="7"/>
+      <c r="B18" s="7"/>
+      <c r="C18" s="7"/>
+      <c r="D18" s="7"/>
+      <c r="E18" s="7"/>
+      <c r="F18" s="7"/>
+      <c r="G18" s="7"/>
+      <c r="H18" s="7"/>
+      <c r="I18" s="7"/>
+      <c r="J18" s="7"/>
+      <c r="K18" s="7"/>
+      <c r="L18" s="7"/>
+      <c r="M18" s="7"/>
+      <c r="N18" s="7"/>
+      <c r="O18" s="7"/>
     </row>
     <row r="19" ht="20.05" customHeight="1">
-      <c r="A19" s="17"/>
-      <c r="B19" s="18"/>
-      <c r="C19" s="16"/>
-      <c r="D19" s="16"/>
-      <c r="E19" s="16"/>
-      <c r="F19" s="16"/>
-      <c r="G19" s="16"/>
-      <c r="H19" s="16"/>
-      <c r="I19" s="16"/>
-      <c r="J19" s="16"/>
-      <c r="K19" s="16"/>
-      <c r="L19" s="16"/>
-      <c r="M19" s="16"/>
+      <c r="A19" s="7"/>
+      <c r="B19" s="7"/>
+      <c r="C19" s="7"/>
+      <c r="D19" s="7"/>
+      <c r="E19" s="7"/>
+      <c r="F19" s="7"/>
+      <c r="G19" s="7"/>
+      <c r="H19" s="7"/>
+      <c r="I19" s="7"/>
+      <c r="J19" s="7"/>
+      <c r="K19" s="7"/>
+      <c r="L19" s="7"/>
+      <c r="M19" s="7"/>
+      <c r="N19" s="7"/>
+      <c r="O19" s="7"/>
     </row>
     <row r="20" ht="20.05" customHeight="1">
-      <c r="A20" s="17"/>
-      <c r="B20" s="18"/>
-      <c r="C20" s="16"/>
-      <c r="D20" s="16"/>
-      <c r="E20" s="16"/>
-      <c r="F20" s="16"/>
-      <c r="G20" s="16"/>
-      <c r="H20" s="16"/>
-      <c r="I20" s="16"/>
-      <c r="J20" s="16"/>
-      <c r="K20" s="16"/>
-      <c r="L20" s="16"/>
-      <c r="M20" s="16"/>
+      <c r="A20" s="7"/>
+      <c r="B20" s="7"/>
+      <c r="C20" s="7"/>
+      <c r="D20" s="7"/>
+      <c r="E20" s="7"/>
+      <c r="F20" s="7"/>
+      <c r="G20" s="7"/>
+      <c r="H20" s="7"/>
+      <c r="I20" s="7"/>
+      <c r="J20" s="7"/>
+      <c r="K20" s="7"/>
+      <c r="L20" s="7"/>
+      <c r="M20" s="7"/>
+      <c r="N20" s="7"/>
+      <c r="O20" s="7"/>
     </row>
     <row r="21" ht="20.05" customHeight="1">
-      <c r="A21" s="17"/>
-      <c r="B21" s="18"/>
-      <c r="C21" s="16"/>
-      <c r="D21" s="16"/>
-      <c r="E21" s="16"/>
-      <c r="F21" s="16"/>
-      <c r="G21" s="16"/>
-      <c r="H21" s="16"/>
-      <c r="I21" s="16"/>
-      <c r="J21" s="16"/>
-      <c r="K21" s="16"/>
-      <c r="L21" s="16"/>
-      <c r="M21" s="16"/>
+      <c r="A21" s="7"/>
+      <c r="B21" s="7"/>
+      <c r="C21" s="7"/>
+      <c r="D21" s="7"/>
+      <c r="E21" s="7"/>
+      <c r="F21" s="7"/>
+      <c r="G21" s="7"/>
+      <c r="H21" s="7"/>
+      <c r="I21" s="7"/>
+      <c r="J21" s="7"/>
+      <c r="K21" s="7"/>
+      <c r="L21" s="7"/>
+      <c r="M21" s="7"/>
+      <c r="N21" s="7"/>
+      <c r="O21" s="7"/>
     </row>
     <row r="22" ht="20.05" customHeight="1">
-      <c r="A22" s="17"/>
-      <c r="B22" s="18"/>
-      <c r="C22" s="16"/>
-      <c r="D22" s="16"/>
-      <c r="E22" s="16"/>
-      <c r="F22" s="16"/>
-      <c r="G22" s="16"/>
-      <c r="H22" s="16"/>
-      <c r="I22" s="16"/>
-      <c r="J22" s="16"/>
-      <c r="K22" s="16"/>
-      <c r="L22" s="16"/>
-      <c r="M22" s="16"/>
+      <c r="A22" s="7"/>
+      <c r="B22" s="7"/>
+      <c r="C22" s="7"/>
+      <c r="D22" s="7"/>
+      <c r="E22" s="7"/>
+      <c r="F22" s="7"/>
+      <c r="G22" s="7"/>
+      <c r="H22" s="7"/>
+      <c r="I22" s="7"/>
+      <c r="J22" s="7"/>
+      <c r="K22" s="7"/>
+      <c r="L22" s="7"/>
+      <c r="M22" s="7"/>
+      <c r="N22" s="7"/>
+      <c r="O22" s="7"/>
     </row>
   </sheetData>
   <pageMargins left="0.5" right="0.5" top="0.75" bottom="0.75" header="0.277778" footer="0.277778"/>

--- a/mockdata/StarAMR_Metrics.xlsx
+++ b/mockdata/StarAMR_Metrics.xlsx
@@ -1,17 +1,26 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
-<workbook xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+<workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="10404"/>
+  <workbookPr/>
+  <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
+    <mc:Choice Requires="x15">
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="/Users/taylorlaurensergel/Desktop/Honours 26'/IMY/Project/IMY772Project/mockdata/"/>
+    </mc:Choice>
+  </mc:AlternateContent>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{464B5913-E26F-1946-A5C1-B964CBFDCAFB}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="0" yWindow="40" windowWidth="15960" windowHeight="18080"/>
+    <workbookView xWindow="0" yWindow="660" windowWidth="30240" windowHeight="18980" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
-    <sheet name="Sheet 1" sheetId="1" r:id="rId4"/>
+    <sheet name="Sheet 1" sheetId="1" r:id="rId1"/>
   </sheets>
+  <calcPr calcId="0"/>
 </workbook>
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" uniqueCount="25">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="284" uniqueCount="126">
   <si>
     <t>Isolate ID</t>
   </si>
@@ -86,41 +95,339 @@
   </si>
   <si>
     <t>IncX1</t>
+  </si>
+  <si>
+    <t>ISO-104</t>
+  </si>
+  <si>
+    <t>bla, blaNDM-1, aph(3')-Ia</t>
+  </si>
+  <si>
+    <t>gentamicin, kanamycin</t>
+  </si>
+  <si>
+    <t>ISO-105</t>
+  </si>
+  <si>
+    <t>blaOXA-48</t>
+  </si>
+  <si>
+    <t>ampicillin, ceftriaxone</t>
+  </si>
+  <si>
+    <t>IncI1</t>
+  </si>
+  <si>
+    <t>ISO-106</t>
+  </si>
+  <si>
+    <t>blaTEM-1, aph(3')-Ia, blaOXA-48</t>
+  </si>
+  <si>
+    <t>ISO-107</t>
+  </si>
+  <si>
+    <t>blaCTX-M</t>
+  </si>
+  <si>
+    <t>ColE1</t>
+  </si>
+  <si>
+    <t>ISO-108</t>
+  </si>
+  <si>
+    <t>erm, blaCTX-M</t>
+  </si>
+  <si>
+    <t>IncN</t>
+  </si>
+  <si>
+    <t>ISO-109</t>
+  </si>
+  <si>
+    <t>catA1, qnrS</t>
+  </si>
+  <si>
+    <t>chloramphenicol</t>
+  </si>
+  <si>
+    <t>p0111</t>
+  </si>
+  <si>
+    <t>ISO-110</t>
+  </si>
+  <si>
+    <t>blaCTX-M, blaNDM-1</t>
+  </si>
+  <si>
+    <t>IncHI1</t>
+  </si>
+  <si>
+    <t>ISO-111</t>
+  </si>
+  <si>
+    <t>erm, aac(3)-I, catA1, blaTEM-1</t>
+  </si>
+  <si>
+    <t>ISO-112</t>
+  </si>
+  <si>
+    <t>bla, blaCTX-M, qnrS, erm</t>
+  </si>
+  <si>
+    <t>ciprofloxacin, nalidixic acid</t>
+  </si>
+  <si>
+    <t>IncFII</t>
+  </si>
+  <si>
+    <t>ISO-113</t>
+  </si>
+  <si>
+    <t>erm, aph(3')-Ia, blaTEM-1</t>
+  </si>
+  <si>
+    <t>ISO-114</t>
+  </si>
+  <si>
+    <t>blaOXA-48, mcr-1, blaTEM-1</t>
+  </si>
+  <si>
+    <t>IncL/M</t>
+  </si>
+  <si>
+    <t>ISO-115</t>
+  </si>
+  <si>
+    <t>aph(3')-Ia, sul1, erm</t>
+  </si>
+  <si>
+    <t>erythromycin, azithromycin</t>
+  </si>
+  <si>
+    <t>ISO-116</t>
+  </si>
+  <si>
+    <t>erm</t>
+  </si>
+  <si>
+    <t>ISO-117</t>
+  </si>
+  <si>
+    <t>aph(3')-Ia, dfrA1, blaNDM-1</t>
+  </si>
+  <si>
+    <t>ISO-118</t>
+  </si>
+  <si>
+    <t>blaOXA-48, sul1</t>
+  </si>
+  <si>
+    <t>sulfisoxazole, trimethoprim-sulfamethoxazole</t>
+  </si>
+  <si>
+    <t>ISO-119</t>
+  </si>
+  <si>
+    <t>bla, dfrA1, tetA</t>
+  </si>
+  <si>
+    <t>ISO-120</t>
+  </si>
+  <si>
+    <t>erm, aph(3')-Ia, tetA</t>
+  </si>
+  <si>
+    <t>ISO-121</t>
+  </si>
+  <si>
+    <t>blaTEM-1, erm, sul2</t>
+  </si>
+  <si>
+    <t>ISO-122</t>
+  </si>
+  <si>
+    <t>bla</t>
+  </si>
+  <si>
+    <t>ISO-123</t>
+  </si>
+  <si>
+    <t>erm, blaNDM-1</t>
+  </si>
+  <si>
+    <t>ISO-124</t>
+  </si>
+  <si>
+    <t>tetA, catA1</t>
+  </si>
+  <si>
+    <t>ISO-125</t>
+  </si>
+  <si>
+    <t>aac(3)-I, qnrS</t>
+  </si>
+  <si>
+    <t>ISO-126</t>
+  </si>
+  <si>
+    <t>aac(3)-I</t>
+  </si>
+  <si>
+    <t>ISO-127</t>
+  </si>
+  <si>
+    <t>ISO-128</t>
+  </si>
+  <si>
+    <t>dfrA1</t>
+  </si>
+  <si>
+    <t>trimethoprim</t>
+  </si>
+  <si>
+    <t>ISO-129</t>
+  </si>
+  <si>
+    <t>qnrS, tetA</t>
+  </si>
+  <si>
+    <t>ciprofloxacin</t>
+  </si>
+  <si>
+    <t>ISO-130</t>
+  </si>
+  <si>
+    <t>blaTEM-1, qnrS</t>
+  </si>
+  <si>
+    <t>ISO-131</t>
+  </si>
+  <si>
+    <t>tetA, qnrS, erm</t>
+  </si>
+  <si>
+    <t>ISO-132</t>
+  </si>
+  <si>
+    <t>mcr-1, blaTEM-1</t>
+  </si>
+  <si>
+    <t>colistin</t>
+  </si>
+  <si>
+    <t>ISO-133</t>
+  </si>
+  <si>
+    <t>erm, blaTEM-1</t>
+  </si>
+  <si>
+    <t>erythromycin</t>
+  </si>
+  <si>
+    <t>ISO-134</t>
+  </si>
+  <si>
+    <t>dfrA1, erm, mcr-1</t>
+  </si>
+  <si>
+    <t>ISO-135</t>
+  </si>
+  <si>
+    <t>erm, dfrA1, mcr-1</t>
+  </si>
+  <si>
+    <t>ISO-136</t>
+  </si>
+  <si>
+    <t>sul1, dfrA1</t>
+  </si>
+  <si>
+    <t>sulfisoxazole</t>
+  </si>
+  <si>
+    <t>ISO-137</t>
+  </si>
+  <si>
+    <t>dfrA1, blaNDM-1, mcr-1</t>
+  </si>
+  <si>
+    <t>ISO-138</t>
+  </si>
+  <si>
+    <t>catA1, erm, blaTEM-1</t>
+  </si>
+  <si>
+    <t>ISO-139</t>
+  </si>
+  <si>
+    <t>mcr-1</t>
+  </si>
+  <si>
+    <t>ISO-140</t>
+  </si>
+  <si>
+    <t>blaNDM-1</t>
+  </si>
+  <si>
+    <t>ISO-141</t>
+  </si>
+  <si>
+    <t>tetA, blaNDM-1</t>
+  </si>
+  <si>
+    <t>ISO-142</t>
+  </si>
+  <si>
+    <t>sul1, qnrS, blaNDM-1</t>
+  </si>
+  <si>
+    <t>ISO-143</t>
+  </si>
+  <si>
+    <t>ISO-144</t>
+  </si>
+  <si>
+    <t>ISO-145</t>
+  </si>
+  <si>
+    <t>catA1, sul1</t>
+  </si>
+  <si>
+    <t>ISO-146</t>
+  </si>
+  <si>
+    <t>qnrS</t>
   </si>
 </sst>
 </file>
 
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
-<styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
-  <numFmts count="1">
-    <numFmt numFmtId="0" formatCode="General"/>
-  </numFmts>
-  <fonts count="5">
+<styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:x16r2="http://schemas.microsoft.com/office/spreadsheetml/2015/02/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" mc:Ignorable="x14ac x16r2 xr">
+  <fonts count="4" x14ac:knownFonts="1">
     <font>
       <sz val="10"/>
       <color indexed="8"/>
       <name val="Helvetica Neue"/>
     </font>
     <font>
-      <sz val="12"/>
-      <color indexed="8"/>
-      <name val="Helvetica Neue"/>
-    </font>
-    <font>
-      <sz val="15"/>
-      <color indexed="8"/>
-      <name val="Calibri"/>
-    </font>
-    <font>
-      <b val="1"/>
+      <b/>
       <sz val="12"/>
       <color indexed="9"/>
       <name val="Helvetica"/>
+      <family val="2"/>
     </font>
     <font>
       <sz val="12"/>
       <color indexed="9"/>
       <name val="Helvetica"/>
+      <family val="2"/>
+    </font>
+    <font>
+      <sz val="12"/>
+      <color indexed="8"/>
+      <name val="Helvetica"/>
+      <family val="2"/>
     </font>
   </fonts>
   <fills count="3">
@@ -162,34 +469,34 @@
     </border>
   </borders>
   <cellStyleXfs count="1">
-    <xf numFmtId="0" fontId="0" applyNumberFormat="0" applyFont="1" applyFill="0" applyBorder="0" applyAlignment="1" applyProtection="0">
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyProtection="0">
       <alignment vertical="top" wrapText="1"/>
     </xf>
   </cellStyleXfs>
   <cellXfs count="8">
-    <xf numFmtId="0" fontId="0" applyNumberFormat="0" applyFont="1" applyFill="0" applyBorder="0" applyAlignment="1" applyProtection="0">
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0">
       <alignment vertical="top" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="0" applyNumberFormat="1" applyFont="1" applyFill="0" applyBorder="0" applyAlignment="1" applyProtection="0">
-      <alignment vertical="top" wrapText="1"/>
-    </xf>
-    <xf numFmtId="49" fontId="3" fillId="2" borderId="1" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="0">
+    <xf numFmtId="49" fontId="1" fillId="2" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="3" fillId="2" borderId="1" applyNumberFormat="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="0">
+    <xf numFmtId="0" fontId="1" fillId="2" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="49" fontId="4" borderId="1" applyNumberFormat="1" applyFont="1" applyFill="0" applyBorder="1" applyAlignment="1" applyProtection="0">
+    <xf numFmtId="49" fontId="2" fillId="0" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="4" borderId="1" applyNumberFormat="1" applyFont="1" applyFill="0" applyBorder="1" applyAlignment="1" applyProtection="0">
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="4" borderId="1" applyNumberFormat="0" applyFont="1" applyFill="0" applyBorder="1" applyAlignment="1" applyProtection="0">
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="0" borderId="1" applyNumberFormat="0" applyFont="1" applyFill="0" applyBorder="1" applyAlignment="1" applyProtection="0">
-      <alignment vertical="top" wrapText="1"/>
+    <xf numFmtId="0" fontId="3" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyAlignment="1">
+      <alignment vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="3" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment vertical="center" wrapText="1"/>
     </xf>
   </cellXfs>
   <cellStyles count="1">
@@ -199,25 +506,85 @@
   <tableStyles count="0"/>
   <colors>
     <indexedColors>
-      <rgbColor rgb="ff000000"/>
-      <rgbColor rgb="ffffffff"/>
-      <rgbColor rgb="ffff0000"/>
-      <rgbColor rgb="ff00ff00"/>
-      <rgbColor rgb="ff0000ff"/>
-      <rgbColor rgb="ffffff00"/>
-      <rgbColor rgb="ffff00ff"/>
-      <rgbColor rgb="ff00ffff"/>
-      <rgbColor rgb="ff000000"/>
-      <rgbColor rgb="ff1f1f1f"/>
-      <rgbColor rgb="ffefefef"/>
-      <rgbColor rgb="ffa5a5a5"/>
+      <rgbColor rgb="FF000000"/>
+      <rgbColor rgb="FFFFFFFF"/>
+      <rgbColor rgb="FFFF0000"/>
+      <rgbColor rgb="FF00FF00"/>
+      <rgbColor rgb="FF0000FF"/>
+      <rgbColor rgb="FFFFFF00"/>
+      <rgbColor rgb="FFFF00FF"/>
+      <rgbColor rgb="FF00FFFF"/>
+      <rgbColor rgb="FF000000"/>
+      <rgbColor rgb="FF1F1F1F"/>
+      <rgbColor rgb="FFEFEFEF"/>
+      <rgbColor rgb="FFA5A5A5"/>
+      <rgbColor rgb="000000FF"/>
+      <rgbColor rgb="00FFFF00"/>
+      <rgbColor rgb="00FF00FF"/>
+      <rgbColor rgb="0000FFFF"/>
+      <rgbColor rgb="00800000"/>
+      <rgbColor rgb="00008000"/>
+      <rgbColor rgb="00000080"/>
+      <rgbColor rgb="00808000"/>
+      <rgbColor rgb="00800080"/>
+      <rgbColor rgb="00008080"/>
+      <rgbColor rgb="00C0C0C0"/>
+      <rgbColor rgb="00808080"/>
+      <rgbColor rgb="009999FF"/>
+      <rgbColor rgb="00993366"/>
+      <rgbColor rgb="00FFFFCC"/>
+      <rgbColor rgb="00CCFFFF"/>
+      <rgbColor rgb="00660066"/>
+      <rgbColor rgb="00FF8080"/>
+      <rgbColor rgb="000066CC"/>
+      <rgbColor rgb="00CCCCFF"/>
+      <rgbColor rgb="00000080"/>
+      <rgbColor rgb="00FF00FF"/>
+      <rgbColor rgb="00FFFF00"/>
+      <rgbColor rgb="0000FFFF"/>
+      <rgbColor rgb="00800080"/>
+      <rgbColor rgb="00800000"/>
+      <rgbColor rgb="00008080"/>
+      <rgbColor rgb="000000FF"/>
+      <rgbColor rgb="0000CCFF"/>
+      <rgbColor rgb="00CCFFFF"/>
+      <rgbColor rgb="00CCFFCC"/>
+      <rgbColor rgb="00FFFF99"/>
+      <rgbColor rgb="0099CCFF"/>
+      <rgbColor rgb="00FF99CC"/>
+      <rgbColor rgb="00CC99FF"/>
+      <rgbColor rgb="00FFCC99"/>
+      <rgbColor rgb="003366FF"/>
+      <rgbColor rgb="0033CCCC"/>
+      <rgbColor rgb="0099CC00"/>
+      <rgbColor rgb="00FFCC00"/>
+      <rgbColor rgb="00FF9900"/>
+      <rgbColor rgb="00FF6600"/>
+      <rgbColor rgb="00666699"/>
+      <rgbColor rgb="00969696"/>
+      <rgbColor rgb="00003366"/>
+      <rgbColor rgb="00339966"/>
+      <rgbColor rgb="00003300"/>
+      <rgbColor rgb="00333300"/>
+      <rgbColor rgb="00993300"/>
+      <rgbColor rgb="00993366"/>
+      <rgbColor rgb="00333399"/>
+      <rgbColor rgb="00333333"/>
     </indexedColors>
   </colors>
+  <extLst>
+    <ext xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" uri="{EB79DEF2-80B8-43e5-95BD-54CBDDF9020C}">
+      <x14:slicerStyles defaultSlicerStyle="SlicerStyleLight1"/>
+    </ext>
+    <ext xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" uri="{9260A510-F301-46a8-8635-F512D64BE5F5}">
+      <x15:timelineStyles defaultTimelineStyle="TimeSlicerStyleLight1"/>
+    </ext>
+  </extLst>
 </styleSheet>
 </file>
 
 <file path=xl/theme/theme1.xml><?xml version="1.0" encoding="utf-8"?>
-<a:theme xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Blank">
+<a:theme xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" name="Blank">
   <a:themeElements>
     <a:clrScheme name="Blank">
       <a:dk1>
@@ -419,7 +786,7 @@
         <a:effectLst/>
         <a:sp3d/>
       </a:spPr>
-      <a:bodyPr rot="0" spcFirstLastPara="1" vertOverflow="overflow" horzOverflow="overflow" vert="horz" wrap="square" lIns="50800" tIns="50800" rIns="50800" bIns="50800" numCol="1" spcCol="38100" rtlCol="0" anchor="ctr" upright="0">
+      <a:bodyPr rot="0" spcFirstLastPara="1" vertOverflow="overflow" horzOverflow="overflow" vert="horz" wrap="square" lIns="50800" tIns="50800" rIns="50800" bIns="50800" numCol="1" spcCol="38100" rtlCol="0" anchor="ctr">
         <a:spAutoFit/>
       </a:bodyPr>
       <a:lstStyle>
@@ -437,7 +804,7 @@
           <a:buSzTx/>
           <a:buFontTx/>
           <a:buNone/>
-          <a:defRPr b="0" baseline="0" cap="none" i="0" spc="0" strike="noStrike" sz="1100" u="none" kumimoji="0" normalizeH="0">
+          <a:defRPr kumimoji="0" sz="1100" b="0" i="0" u="none" strike="noStrike" cap="none" spc="0" normalizeH="0" baseline="0">
             <a:ln>
               <a:noFill/>
             </a:ln>
@@ -466,7 +833,7 @@
           <a:buSzTx/>
           <a:buFontTx/>
           <a:buNone/>
-          <a:defRPr b="0" baseline="0" cap="none" i="0" spc="0" strike="noStrike" sz="1800" u="none" kumimoji="0" normalizeH="0">
+          <a:defRPr kumimoji="0" sz="1800" b="0" i="0" u="none" strike="noStrike" cap="none" spc="0" normalizeH="0" baseline="0">
             <a:ln>
               <a:noFill/>
             </a:ln>
@@ -491,7 +858,7 @@
           <a:buSzTx/>
           <a:buFontTx/>
           <a:buNone/>
-          <a:defRPr b="0" baseline="0" cap="none" i="0" spc="0" strike="noStrike" sz="1800" u="none" kumimoji="0" normalizeH="0">
+          <a:defRPr kumimoji="0" sz="1800" b="0" i="0" u="none" strike="noStrike" cap="none" spc="0" normalizeH="0" baseline="0">
             <a:ln>
               <a:noFill/>
             </a:ln>
@@ -516,7 +883,7 @@
           <a:buSzTx/>
           <a:buFontTx/>
           <a:buNone/>
-          <a:defRPr b="0" baseline="0" cap="none" i="0" spc="0" strike="noStrike" sz="1800" u="none" kumimoji="0" normalizeH="0">
+          <a:defRPr kumimoji="0" sz="1800" b="0" i="0" u="none" strike="noStrike" cap="none" spc="0" normalizeH="0" baseline="0">
             <a:ln>
               <a:noFill/>
             </a:ln>
@@ -541,7 +908,7 @@
           <a:buSzTx/>
           <a:buFontTx/>
           <a:buNone/>
-          <a:defRPr b="0" baseline="0" cap="none" i="0" spc="0" strike="noStrike" sz="1800" u="none" kumimoji="0" normalizeH="0">
+          <a:defRPr kumimoji="0" sz="1800" b="0" i="0" u="none" strike="noStrike" cap="none" spc="0" normalizeH="0" baseline="0">
             <a:ln>
               <a:noFill/>
             </a:ln>
@@ -566,7 +933,7 @@
           <a:buSzTx/>
           <a:buFontTx/>
           <a:buNone/>
-          <a:defRPr b="0" baseline="0" cap="none" i="0" spc="0" strike="noStrike" sz="1800" u="none" kumimoji="0" normalizeH="0">
+          <a:defRPr kumimoji="0" sz="1800" b="0" i="0" u="none" strike="noStrike" cap="none" spc="0" normalizeH="0" baseline="0">
             <a:ln>
               <a:noFill/>
             </a:ln>
@@ -591,7 +958,7 @@
           <a:buSzTx/>
           <a:buFontTx/>
           <a:buNone/>
-          <a:defRPr b="0" baseline="0" cap="none" i="0" spc="0" strike="noStrike" sz="1800" u="none" kumimoji="0" normalizeH="0">
+          <a:defRPr kumimoji="0" sz="1800" b="0" i="0" u="none" strike="noStrike" cap="none" spc="0" normalizeH="0" baseline="0">
             <a:ln>
               <a:noFill/>
             </a:ln>
@@ -616,7 +983,7 @@
           <a:buSzTx/>
           <a:buFontTx/>
           <a:buNone/>
-          <a:defRPr b="0" baseline="0" cap="none" i="0" spc="0" strike="noStrike" sz="1800" u="none" kumimoji="0" normalizeH="0">
+          <a:defRPr kumimoji="0" sz="1800" b="0" i="0" u="none" strike="noStrike" cap="none" spc="0" normalizeH="0" baseline="0">
             <a:ln>
               <a:noFill/>
             </a:ln>
@@ -641,7 +1008,7 @@
           <a:buSzTx/>
           <a:buFontTx/>
           <a:buNone/>
-          <a:defRPr b="0" baseline="0" cap="none" i="0" spc="0" strike="noStrike" sz="1800" u="none" kumimoji="0" normalizeH="0">
+          <a:defRPr kumimoji="0" sz="1800" b="0" i="0" u="none" strike="noStrike" cap="none" spc="0" normalizeH="0" baseline="0">
             <a:ln>
               <a:noFill/>
             </a:ln>
@@ -666,7 +1033,7 @@
           <a:buSzTx/>
           <a:buFontTx/>
           <a:buNone/>
-          <a:defRPr b="0" baseline="0" cap="none" i="0" spc="0" strike="noStrike" sz="1800" u="none" kumimoji="0" normalizeH="0">
+          <a:defRPr kumimoji="0" sz="1800" b="0" i="0" u="none" strike="noStrike" cap="none" spc="0" normalizeH="0" baseline="0">
             <a:ln>
               <a:noFill/>
             </a:ln>
@@ -679,9 +1046,15 @@
         </a:lvl9pPr>
       </a:lstStyle>
       <a:style>
-        <a:lnRef idx="0"/>
-        <a:fillRef idx="0"/>
-        <a:effectRef idx="0"/>
+        <a:lnRef idx="0">
+          <a:scrgbClr r="0" g="0" b="0"/>
+        </a:lnRef>
+        <a:fillRef idx="0">
+          <a:scrgbClr r="0" g="0" b="0"/>
+        </a:fillRef>
+        <a:effectRef idx="0">
+          <a:scrgbClr r="0" g="0" b="0"/>
+        </a:effectRef>
         <a:fontRef idx="none"/>
       </a:style>
     </a:spDef>
@@ -698,7 +1071,7 @@
         <a:effectLst/>
         <a:sp3d/>
       </a:spPr>
-      <a:bodyPr rot="0" spcFirstLastPara="1" vertOverflow="overflow" horzOverflow="overflow" vert="horz" wrap="square" lIns="91439" tIns="45719" rIns="91439" bIns="45719" numCol="1" spcCol="38100" rtlCol="0" anchor="t" upright="0">
+      <a:bodyPr rot="0" spcFirstLastPara="1" vertOverflow="overflow" horzOverflow="overflow" vert="horz" wrap="square" lIns="91439" tIns="45719" rIns="91439" bIns="45719" numCol="1" spcCol="38100" rtlCol="0" anchor="t">
         <a:noAutofit/>
       </a:bodyPr>
       <a:lstStyle>
@@ -716,7 +1089,7 @@
           <a:buSzTx/>
           <a:buFontTx/>
           <a:buNone/>
-          <a:defRPr b="0" baseline="0" cap="none" i="0" spc="0" strike="noStrike" sz="1800" u="none" kumimoji="0" normalizeH="0">
+          <a:defRPr kumimoji="0" sz="1800" b="0" i="0" u="none" strike="noStrike" cap="none" spc="0" normalizeH="0" baseline="0">
             <a:ln>
               <a:noFill/>
             </a:ln>
@@ -741,7 +1114,7 @@
           <a:buSzTx/>
           <a:buFontTx/>
           <a:buNone/>
-          <a:defRPr b="0" baseline="0" cap="none" i="0" spc="0" strike="noStrike" sz="1800" u="none" kumimoji="0" normalizeH="0">
+          <a:defRPr kumimoji="0" sz="1800" b="0" i="0" u="none" strike="noStrike" cap="none" spc="0" normalizeH="0" baseline="0">
             <a:ln>
               <a:noFill/>
             </a:ln>
@@ -766,7 +1139,7 @@
           <a:buSzTx/>
           <a:buFontTx/>
           <a:buNone/>
-          <a:defRPr b="0" baseline="0" cap="none" i="0" spc="0" strike="noStrike" sz="1800" u="none" kumimoji="0" normalizeH="0">
+          <a:defRPr kumimoji="0" sz="1800" b="0" i="0" u="none" strike="noStrike" cap="none" spc="0" normalizeH="0" baseline="0">
             <a:ln>
               <a:noFill/>
             </a:ln>
@@ -791,7 +1164,7 @@
           <a:buSzTx/>
           <a:buFontTx/>
           <a:buNone/>
-          <a:defRPr b="0" baseline="0" cap="none" i="0" spc="0" strike="noStrike" sz="1800" u="none" kumimoji="0" normalizeH="0">
+          <a:defRPr kumimoji="0" sz="1800" b="0" i="0" u="none" strike="noStrike" cap="none" spc="0" normalizeH="0" baseline="0">
             <a:ln>
               <a:noFill/>
             </a:ln>
@@ -816,7 +1189,7 @@
           <a:buSzTx/>
           <a:buFontTx/>
           <a:buNone/>
-          <a:defRPr b="0" baseline="0" cap="none" i="0" spc="0" strike="noStrike" sz="1800" u="none" kumimoji="0" normalizeH="0">
+          <a:defRPr kumimoji="0" sz="1800" b="0" i="0" u="none" strike="noStrike" cap="none" spc="0" normalizeH="0" baseline="0">
             <a:ln>
               <a:noFill/>
             </a:ln>
@@ -841,7 +1214,7 @@
           <a:buSzTx/>
           <a:buFontTx/>
           <a:buNone/>
-          <a:defRPr b="0" baseline="0" cap="none" i="0" spc="0" strike="noStrike" sz="1800" u="none" kumimoji="0" normalizeH="0">
+          <a:defRPr kumimoji="0" sz="1800" b="0" i="0" u="none" strike="noStrike" cap="none" spc="0" normalizeH="0" baseline="0">
             <a:ln>
               <a:noFill/>
             </a:ln>
@@ -866,7 +1239,7 @@
           <a:buSzTx/>
           <a:buFontTx/>
           <a:buNone/>
-          <a:defRPr b="0" baseline="0" cap="none" i="0" spc="0" strike="noStrike" sz="1800" u="none" kumimoji="0" normalizeH="0">
+          <a:defRPr kumimoji="0" sz="1800" b="0" i="0" u="none" strike="noStrike" cap="none" spc="0" normalizeH="0" baseline="0">
             <a:ln>
               <a:noFill/>
             </a:ln>
@@ -891,7 +1264,7 @@
           <a:buSzTx/>
           <a:buFontTx/>
           <a:buNone/>
-          <a:defRPr b="0" baseline="0" cap="none" i="0" spc="0" strike="noStrike" sz="1800" u="none" kumimoji="0" normalizeH="0">
+          <a:defRPr kumimoji="0" sz="1800" b="0" i="0" u="none" strike="noStrike" cap="none" spc="0" normalizeH="0" baseline="0">
             <a:ln>
               <a:noFill/>
             </a:ln>
@@ -916,7 +1289,7 @@
           <a:buSzTx/>
           <a:buFontTx/>
           <a:buNone/>
-          <a:defRPr b="0" baseline="0" cap="none" i="0" spc="0" strike="noStrike" sz="1800" u="none" kumimoji="0" normalizeH="0">
+          <a:defRPr kumimoji="0" sz="1800" b="0" i="0" u="none" strike="noStrike" cap="none" spc="0" normalizeH="0" baseline="0">
             <a:ln>
               <a:noFill/>
             </a:ln>
@@ -941,7 +1314,7 @@
           <a:buSzTx/>
           <a:buFontTx/>
           <a:buNone/>
-          <a:defRPr b="0" baseline="0" cap="none" i="0" spc="0" strike="noStrike" sz="1800" u="none" kumimoji="0" normalizeH="0">
+          <a:defRPr kumimoji="0" sz="1800" b="0" i="0" u="none" strike="noStrike" cap="none" spc="0" normalizeH="0" baseline="0">
             <a:ln>
               <a:noFill/>
             </a:ln>
@@ -954,9 +1327,15 @@
         </a:lvl9pPr>
       </a:lstStyle>
       <a:style>
-        <a:lnRef idx="0"/>
-        <a:fillRef idx="0"/>
-        <a:effectRef idx="0"/>
+        <a:lnRef idx="0">
+          <a:scrgbClr r="0" g="0" b="0"/>
+        </a:lnRef>
+        <a:fillRef idx="0">
+          <a:scrgbClr r="0" g="0" b="0"/>
+        </a:fillRef>
+        <a:effectRef idx="0">
+          <a:scrgbClr r="0" g="0" b="0"/>
+        </a:effectRef>
         <a:fontRef idx="none"/>
       </a:style>
     </a:lnDef>
@@ -970,7 +1349,7 @@
         <a:effectLst/>
         <a:sp3d/>
       </a:spPr>
-      <a:bodyPr rot="0" spcFirstLastPara="1" vertOverflow="overflow" horzOverflow="overflow" vert="horz" wrap="square" lIns="50800" tIns="50800" rIns="50800" bIns="50800" numCol="1" spcCol="38100" rtlCol="0" anchor="t" upright="0">
+      <a:bodyPr rot="0" spcFirstLastPara="1" vertOverflow="overflow" horzOverflow="overflow" vert="horz" wrap="square" lIns="50800" tIns="50800" rIns="50800" bIns="50800" numCol="1" spcCol="38100" rtlCol="0" anchor="t">
         <a:spAutoFit/>
       </a:bodyPr>
       <a:lstStyle>
@@ -988,7 +1367,7 @@
           <a:buSzTx/>
           <a:buFontTx/>
           <a:buNone/>
-          <a:defRPr b="0" baseline="0" cap="none" i="0" spc="0" strike="noStrike" sz="1100" u="none" kumimoji="0" normalizeH="0">
+          <a:defRPr kumimoji="0" sz="1100" b="0" i="0" u="none" strike="noStrike" cap="none" spc="0" normalizeH="0" baseline="0">
             <a:ln>
               <a:noFill/>
             </a:ln>
@@ -1017,7 +1396,7 @@
           <a:buSzTx/>
           <a:buFontTx/>
           <a:buNone/>
-          <a:defRPr b="0" baseline="0" cap="none" i="0" spc="0" strike="noStrike" sz="1800" u="none" kumimoji="0" normalizeH="0">
+          <a:defRPr kumimoji="0" sz="1800" b="0" i="0" u="none" strike="noStrike" cap="none" spc="0" normalizeH="0" baseline="0">
             <a:ln>
               <a:noFill/>
             </a:ln>
@@ -1042,7 +1421,7 @@
           <a:buSzTx/>
           <a:buFontTx/>
           <a:buNone/>
-          <a:defRPr b="0" baseline="0" cap="none" i="0" spc="0" strike="noStrike" sz="1800" u="none" kumimoji="0" normalizeH="0">
+          <a:defRPr kumimoji="0" sz="1800" b="0" i="0" u="none" strike="noStrike" cap="none" spc="0" normalizeH="0" baseline="0">
             <a:ln>
               <a:noFill/>
             </a:ln>
@@ -1067,7 +1446,7 @@
           <a:buSzTx/>
           <a:buFontTx/>
           <a:buNone/>
-          <a:defRPr b="0" baseline="0" cap="none" i="0" spc="0" strike="noStrike" sz="1800" u="none" kumimoji="0" normalizeH="0">
+          <a:defRPr kumimoji="0" sz="1800" b="0" i="0" u="none" strike="noStrike" cap="none" spc="0" normalizeH="0" baseline="0">
             <a:ln>
               <a:noFill/>
             </a:ln>
@@ -1092,7 +1471,7 @@
           <a:buSzTx/>
           <a:buFontTx/>
           <a:buNone/>
-          <a:defRPr b="0" baseline="0" cap="none" i="0" spc="0" strike="noStrike" sz="1800" u="none" kumimoji="0" normalizeH="0">
+          <a:defRPr kumimoji="0" sz="1800" b="0" i="0" u="none" strike="noStrike" cap="none" spc="0" normalizeH="0" baseline="0">
             <a:ln>
               <a:noFill/>
             </a:ln>
@@ -1117,7 +1496,7 @@
           <a:buSzTx/>
           <a:buFontTx/>
           <a:buNone/>
-          <a:defRPr b="0" baseline="0" cap="none" i="0" spc="0" strike="noStrike" sz="1800" u="none" kumimoji="0" normalizeH="0">
+          <a:defRPr kumimoji="0" sz="1800" b="0" i="0" u="none" strike="noStrike" cap="none" spc="0" normalizeH="0" baseline="0">
             <a:ln>
               <a:noFill/>
             </a:ln>
@@ -1142,7 +1521,7 @@
           <a:buSzTx/>
           <a:buFontTx/>
           <a:buNone/>
-          <a:defRPr b="0" baseline="0" cap="none" i="0" spc="0" strike="noStrike" sz="1800" u="none" kumimoji="0" normalizeH="0">
+          <a:defRPr kumimoji="0" sz="1800" b="0" i="0" u="none" strike="noStrike" cap="none" spc="0" normalizeH="0" baseline="0">
             <a:ln>
               <a:noFill/>
             </a:ln>
@@ -1167,7 +1546,7 @@
           <a:buSzTx/>
           <a:buFontTx/>
           <a:buNone/>
-          <a:defRPr b="0" baseline="0" cap="none" i="0" spc="0" strike="noStrike" sz="1800" u="none" kumimoji="0" normalizeH="0">
+          <a:defRPr kumimoji="0" sz="1800" b="0" i="0" u="none" strike="noStrike" cap="none" spc="0" normalizeH="0" baseline="0">
             <a:ln>
               <a:noFill/>
             </a:ln>
@@ -1192,7 +1571,7 @@
           <a:buSzTx/>
           <a:buFontTx/>
           <a:buNone/>
-          <a:defRPr b="0" baseline="0" cap="none" i="0" spc="0" strike="noStrike" sz="1800" u="none" kumimoji="0" normalizeH="0">
+          <a:defRPr kumimoji="0" sz="1800" b="0" i="0" u="none" strike="noStrike" cap="none" spc="0" normalizeH="0" baseline="0">
             <a:ln>
               <a:noFill/>
             </a:ln>
@@ -1217,7 +1596,7 @@
           <a:buSzTx/>
           <a:buFontTx/>
           <a:buNone/>
-          <a:defRPr b="0" baseline="0" cap="none" i="0" spc="0" strike="noStrike" sz="1800" u="none" kumimoji="0" normalizeH="0">
+          <a:defRPr kumimoji="0" sz="1800" b="0" i="0" u="none" strike="noStrike" cap="none" spc="0" normalizeH="0" baseline="0">
             <a:ln>
               <a:noFill/>
             </a:ln>
@@ -1230,183 +1609,222 @@
         </a:lvl9pPr>
       </a:lstStyle>
       <a:style>
-        <a:lnRef idx="0"/>
-        <a:fillRef idx="0"/>
-        <a:effectRef idx="0"/>
+        <a:lnRef idx="0">
+          <a:scrgbClr r="0" g="0" b="0"/>
+        </a:lnRef>
+        <a:fillRef idx="0">
+          <a:scrgbClr r="0" g="0" b="0"/>
+        </a:fillRef>
+        <a:effectRef idx="0">
+          <a:scrgbClr r="0" g="0" b="0"/>
+        </a:effectRef>
         <a:fontRef idx="none"/>
       </a:style>
     </a:txDef>
   </a:objectDefaults>
+  <a:extraClrSchemeLst/>
 </a:theme>
 </file>
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
-  <dimension ref="A1:O22"/>
-  <sheetFormatPr defaultColWidth="16.3333" defaultRowHeight="13.9" customHeight="1" outlineLevelRow="0" outlineLevelCol="0"/>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0000-000000000000}">
+  <dimension ref="A1:O47"/>
+  <sheetFormatPr baseColWidth="10" defaultColWidth="16.33203125" defaultRowHeight="60.25" customHeight="1" x14ac:dyDescent="0.15"/>
   <cols>
-    <col min="1" max="15" width="16.3516" style="1" customWidth="1"/>
-    <col min="16" max="16384" width="16.3516" style="1" customWidth="1"/>
+    <col min="1" max="16" width="16.33203125" style="6" customWidth="1"/>
+    <col min="17" max="16384" width="16.33203125" style="6"/>
   </cols>
   <sheetData>
-    <row r="1" ht="60.55" customHeight="1">
-      <c r="A1" t="s" s="2">
+    <row r="1" spans="1:15" ht="60.25" customHeight="1" x14ac:dyDescent="0.15">
+      <c r="A1" s="1" t="s">
         <v>0</v>
       </c>
-      <c r="B1" t="s" s="2">
+      <c r="B1" s="1" t="s">
         <v>1</v>
       </c>
-      <c r="C1" t="s" s="2">
+      <c r="C1" s="1" t="s">
         <v>2</v>
       </c>
-      <c r="D1" t="s" s="2">
+      <c r="D1" s="1" t="s">
         <v>3</v>
       </c>
-      <c r="E1" t="s" s="2">
+      <c r="E1" s="1" t="s">
         <v>4</v>
       </c>
-      <c r="F1" t="s" s="2">
+      <c r="F1" s="1" t="s">
         <v>5</v>
       </c>
-      <c r="G1" t="s" s="2">
+      <c r="G1" s="1" t="s">
         <v>6</v>
       </c>
-      <c r="H1" t="s" s="2">
+      <c r="H1" s="1" t="s">
         <v>7</v>
       </c>
-      <c r="I1" s="3"/>
-      <c r="J1" s="3"/>
-      <c r="K1" s="3"/>
-      <c r="L1" s="3"/>
-      <c r="M1" s="3"/>
-      <c r="N1" s="3"/>
-      <c r="O1" s="3"/>
-    </row>
-    <row r="2" ht="74.55" customHeight="1">
-      <c r="A2" t="s" s="4">
+      <c r="I1" s="2"/>
+      <c r="J1" s="2"/>
+      <c r="K1" s="2"/>
+      <c r="L1" s="2"/>
+      <c r="M1" s="2"/>
+      <c r="N1" s="2"/>
+      <c r="O1" s="2"/>
+    </row>
+    <row r="2" spans="1:15" ht="60.25" customHeight="1" x14ac:dyDescent="0.15">
+      <c r="A2" s="3" t="s">
         <v>8</v>
       </c>
-      <c r="B2" t="s" s="4">
+      <c r="B2" s="3" t="s">
         <v>9</v>
       </c>
-      <c r="C2" t="s" s="4">
+      <c r="C2" s="3" t="s">
         <v>10</v>
       </c>
-      <c r="D2" t="s" s="4">
+      <c r="D2" s="3" t="s">
         <v>11</v>
       </c>
-      <c r="E2" t="s" s="4">
+      <c r="E2" s="3" t="s">
         <v>12</v>
       </c>
-      <c r="F2" t="s" s="4">
+      <c r="F2" s="3" t="s">
         <v>13</v>
       </c>
-      <c r="G2" s="5">
+      <c r="G2" s="4">
         <v>5017831</v>
       </c>
-      <c r="H2" s="5">
+      <c r="H2" s="4">
         <v>156657</v>
       </c>
-      <c r="I2" s="6"/>
-      <c r="J2" s="6"/>
-      <c r="K2" s="6"/>
-      <c r="L2" s="6"/>
-      <c r="M2" s="6"/>
-      <c r="N2" s="6"/>
-      <c r="O2" s="6"/>
-    </row>
-    <row r="3" ht="46.35" customHeight="1">
-      <c r="A3" t="s" s="4">
+      <c r="I2" s="5"/>
+      <c r="J2" s="5"/>
+      <c r="K2" s="5"/>
+      <c r="L2" s="5"/>
+      <c r="M2" s="5"/>
+      <c r="N2" s="5"/>
+      <c r="O2" s="5"/>
+    </row>
+    <row r="3" spans="1:15" ht="60.25" customHeight="1" x14ac:dyDescent="0.15">
+      <c r="A3" s="3" t="s">
         <v>14</v>
       </c>
-      <c r="B3" t="s" s="4">
+      <c r="B3" s="3" t="s">
         <v>15</v>
       </c>
-      <c r="C3" t="s" s="4">
+      <c r="C3" s="3" t="s">
         <v>16</v>
       </c>
-      <c r="D3" t="s" s="4">
+      <c r="D3" s="3" t="s">
         <v>17</v>
       </c>
-      <c r="E3" t="s" s="4">
+      <c r="E3" s="3" t="s">
         <v>18</v>
       </c>
-      <c r="F3" t="s" s="4">
+      <c r="F3" s="3" t="s">
         <v>19</v>
       </c>
-      <c r="G3" s="5">
+      <c r="G3" s="4">
         <v>6133820</v>
       </c>
-      <c r="H3" s="5">
+      <c r="H3" s="4">
         <v>1660</v>
       </c>
-      <c r="I3" s="6"/>
-      <c r="J3" s="6"/>
-      <c r="K3" s="6"/>
-      <c r="L3" s="6"/>
-      <c r="M3" s="6"/>
-      <c r="N3" s="6"/>
-      <c r="O3" s="6"/>
-    </row>
-    <row r="4" ht="60.35" customHeight="1">
-      <c r="A4" t="s" s="4">
+      <c r="I3" s="5"/>
+      <c r="J3" s="5"/>
+      <c r="K3" s="5"/>
+      <c r="L3" s="5"/>
+      <c r="M3" s="5"/>
+      <c r="N3" s="5"/>
+      <c r="O3" s="5"/>
+    </row>
+    <row r="4" spans="1:15" ht="60.25" customHeight="1" x14ac:dyDescent="0.15">
+      <c r="A4" s="3" t="s">
         <v>20</v>
       </c>
-      <c r="B4" t="s" s="4">
+      <c r="B4" s="3" t="s">
         <v>9</v>
       </c>
-      <c r="C4" t="s" s="4">
+      <c r="C4" s="3" t="s">
         <v>21</v>
       </c>
-      <c r="D4" t="s" s="4">
+      <c r="D4" s="3" t="s">
         <v>22</v>
       </c>
-      <c r="E4" t="s" s="4">
+      <c r="E4" s="3" t="s">
         <v>23</v>
       </c>
-      <c r="F4" t="s" s="4">
+      <c r="F4" s="3" t="s">
         <v>24</v>
       </c>
-      <c r="G4" s="5">
+      <c r="G4" s="4">
         <v>5025249</v>
       </c>
-      <c r="H4" s="5">
+      <c r="H4" s="4">
         <v>125507</v>
       </c>
-      <c r="I4" s="6"/>
-      <c r="J4" s="6"/>
-      <c r="K4" s="6"/>
-      <c r="L4" s="6"/>
-      <c r="M4" s="6"/>
-      <c r="N4" s="6"/>
-      <c r="O4" s="6"/>
-    </row>
-    <row r="5" ht="46.35" customHeight="1">
-      <c r="A5" s="6"/>
-      <c r="B5" s="6"/>
-      <c r="C5" s="6"/>
-      <c r="D5" s="6"/>
-      <c r="E5" s="6"/>
-      <c r="F5" s="6"/>
-      <c r="G5" s="6"/>
-      <c r="H5" s="6"/>
-      <c r="I5" s="6"/>
-      <c r="J5" s="6"/>
-      <c r="K5" s="6"/>
-      <c r="L5" s="6"/>
+      <c r="I4" s="5"/>
+      <c r="J4" s="5"/>
+      <c r="K4" s="5"/>
+      <c r="L4" s="5"/>
+      <c r="M4" s="5"/>
+      <c r="N4" s="5"/>
+      <c r="O4" s="5"/>
+    </row>
+    <row r="5" spans="1:15" ht="60.25" customHeight="1" x14ac:dyDescent="0.15">
+      <c r="A5" s="5" t="s">
+        <v>25</v>
+      </c>
+      <c r="B5" s="5" t="s">
+        <v>9</v>
+      </c>
+      <c r="C5" s="5" t="s">
+        <v>26</v>
+      </c>
+      <c r="D5" s="5" t="s">
+        <v>27</v>
+      </c>
+      <c r="E5" s="5" t="s">
+        <v>12</v>
+      </c>
+      <c r="F5" s="5" t="s">
+        <v>13</v>
+      </c>
+      <c r="G5" s="5">
+        <v>5686839</v>
+      </c>
+      <c r="H5" s="5">
+        <v>227772</v>
+      </c>
+      <c r="I5" s="5"/>
+      <c r="J5" s="5"/>
+      <c r="K5" s="5"/>
+      <c r="L5" s="5"/>
       <c r="M5" s="7"/>
       <c r="N5" s="7"/>
       <c r="O5" s="7"/>
     </row>
-    <row r="6" ht="20.05" customHeight="1">
-      <c r="A6" s="7"/>
-      <c r="B6" s="7"/>
-      <c r="C6" s="7"/>
-      <c r="D6" s="7"/>
-      <c r="E6" s="7"/>
-      <c r="F6" s="7"/>
-      <c r="G6" s="7"/>
-      <c r="H6" s="7"/>
+    <row r="6" spans="1:15" ht="60.25" customHeight="1" x14ac:dyDescent="0.15">
+      <c r="A6" s="7" t="s">
+        <v>28</v>
+      </c>
+      <c r="B6" s="7" t="s">
+        <v>9</v>
+      </c>
+      <c r="C6" s="7" t="s">
+        <v>29</v>
+      </c>
+      <c r="D6" s="7" t="s">
+        <v>30</v>
+      </c>
+      <c r="E6" s="7" t="s">
+        <v>12</v>
+      </c>
+      <c r="F6" s="7" t="s">
+        <v>31</v>
+      </c>
+      <c r="G6" s="7">
+        <v>5773107</v>
+      </c>
+      <c r="H6" s="7">
+        <v>211221</v>
+      </c>
       <c r="I6" s="7"/>
       <c r="J6" s="7"/>
       <c r="K6" s="7"/>
@@ -1415,15 +1833,31 @@
       <c r="N6" s="7"/>
       <c r="O6" s="7"/>
     </row>
-    <row r="7" ht="20.05" customHeight="1">
-      <c r="A7" s="7"/>
-      <c r="B7" s="7"/>
-      <c r="C7" s="7"/>
-      <c r="D7" s="7"/>
-      <c r="E7" s="7"/>
-      <c r="F7" s="7"/>
-      <c r="G7" s="7"/>
-      <c r="H7" s="7"/>
+    <row r="7" spans="1:15" ht="60.25" customHeight="1" x14ac:dyDescent="0.15">
+      <c r="A7" s="7" t="s">
+        <v>32</v>
+      </c>
+      <c r="B7" s="7" t="s">
+        <v>9</v>
+      </c>
+      <c r="C7" s="7" t="s">
+        <v>33</v>
+      </c>
+      <c r="D7" s="7" t="s">
+        <v>30</v>
+      </c>
+      <c r="E7" s="7" t="s">
+        <v>12</v>
+      </c>
+      <c r="F7" s="7" t="s">
+        <v>24</v>
+      </c>
+      <c r="G7" s="7">
+        <v>5817531</v>
+      </c>
+      <c r="H7" s="7">
+        <v>26470</v>
+      </c>
       <c r="I7" s="7"/>
       <c r="J7" s="7"/>
       <c r="K7" s="7"/>
@@ -1432,15 +1866,31 @@
       <c r="N7" s="7"/>
       <c r="O7" s="7"/>
     </row>
-    <row r="8" ht="20.05" customHeight="1">
-      <c r="A8" s="7"/>
-      <c r="B8" s="7"/>
-      <c r="C8" s="7"/>
-      <c r="D8" s="7"/>
-      <c r="E8" s="7"/>
-      <c r="F8" s="7"/>
-      <c r="G8" s="7"/>
-      <c r="H8" s="7"/>
+    <row r="8" spans="1:15" ht="60.25" customHeight="1" x14ac:dyDescent="0.15">
+      <c r="A8" s="7" t="s">
+        <v>34</v>
+      </c>
+      <c r="B8" s="7" t="s">
+        <v>9</v>
+      </c>
+      <c r="C8" s="7" t="s">
+        <v>35</v>
+      </c>
+      <c r="D8" s="7" t="s">
+        <v>30</v>
+      </c>
+      <c r="E8" s="7" t="s">
+        <v>12</v>
+      </c>
+      <c r="F8" s="7" t="s">
+        <v>36</v>
+      </c>
+      <c r="G8" s="7">
+        <v>5265169</v>
+      </c>
+      <c r="H8" s="7">
+        <v>192983</v>
+      </c>
       <c r="I8" s="7"/>
       <c r="J8" s="7"/>
       <c r="K8" s="7"/>
@@ -1449,15 +1899,31 @@
       <c r="N8" s="7"/>
       <c r="O8" s="7"/>
     </row>
-    <row r="9" ht="20.05" customHeight="1">
-      <c r="A9" s="7"/>
-      <c r="B9" s="7"/>
-      <c r="C9" s="7"/>
-      <c r="D9" s="7"/>
-      <c r="E9" s="7"/>
-      <c r="F9" s="7"/>
-      <c r="G9" s="7"/>
-      <c r="H9" s="7"/>
+    <row r="9" spans="1:15" ht="60.25" customHeight="1" x14ac:dyDescent="0.15">
+      <c r="A9" s="7" t="s">
+        <v>37</v>
+      </c>
+      <c r="B9" s="7" t="s">
+        <v>15</v>
+      </c>
+      <c r="C9" s="7" t="s">
+        <v>38</v>
+      </c>
+      <c r="D9" s="7" t="s">
+        <v>30</v>
+      </c>
+      <c r="E9" s="7" t="s">
+        <v>12</v>
+      </c>
+      <c r="F9" s="7" t="s">
+        <v>39</v>
+      </c>
+      <c r="G9" s="7">
+        <v>4868343</v>
+      </c>
+      <c r="H9" s="7">
+        <v>53637</v>
+      </c>
       <c r="I9" s="7"/>
       <c r="J9" s="7"/>
       <c r="K9" s="7"/>
@@ -1466,15 +1932,31 @@
       <c r="N9" s="7"/>
       <c r="O9" s="7"/>
     </row>
-    <row r="10" ht="20.05" customHeight="1">
-      <c r="A10" s="7"/>
-      <c r="B10" s="7"/>
-      <c r="C10" s="7"/>
-      <c r="D10" s="7"/>
-      <c r="E10" s="7"/>
-      <c r="F10" s="7"/>
-      <c r="G10" s="7"/>
-      <c r="H10" s="7"/>
+    <row r="10" spans="1:15" ht="60.25" customHeight="1" x14ac:dyDescent="0.15">
+      <c r="A10" s="7" t="s">
+        <v>40</v>
+      </c>
+      <c r="B10" s="7" t="s">
+        <v>15</v>
+      </c>
+      <c r="C10" s="7" t="s">
+        <v>41</v>
+      </c>
+      <c r="D10" s="7" t="s">
+        <v>42</v>
+      </c>
+      <c r="E10" s="7" t="s">
+        <v>23</v>
+      </c>
+      <c r="F10" s="7" t="s">
+        <v>43</v>
+      </c>
+      <c r="G10" s="7">
+        <v>6415721</v>
+      </c>
+      <c r="H10" s="7">
+        <v>72441</v>
+      </c>
       <c r="I10" s="7"/>
       <c r="J10" s="7"/>
       <c r="K10" s="7"/>
@@ -1483,15 +1965,31 @@
       <c r="N10" s="7"/>
       <c r="O10" s="7"/>
     </row>
-    <row r="11" ht="20.05" customHeight="1">
-      <c r="A11" s="7"/>
-      <c r="B11" s="7"/>
-      <c r="C11" s="7"/>
-      <c r="D11" s="7"/>
-      <c r="E11" s="7"/>
-      <c r="F11" s="7"/>
-      <c r="G11" s="7"/>
-      <c r="H11" s="7"/>
+    <row r="11" spans="1:15" ht="60.25" customHeight="1" x14ac:dyDescent="0.15">
+      <c r="A11" s="7" t="s">
+        <v>44</v>
+      </c>
+      <c r="B11" s="7" t="s">
+        <v>9</v>
+      </c>
+      <c r="C11" s="7" t="s">
+        <v>45</v>
+      </c>
+      <c r="D11" s="7" t="s">
+        <v>30</v>
+      </c>
+      <c r="E11" s="7" t="s">
+        <v>12</v>
+      </c>
+      <c r="F11" s="7" t="s">
+        <v>46</v>
+      </c>
+      <c r="G11" s="7">
+        <v>6186597</v>
+      </c>
+      <c r="H11" s="7">
+        <v>31191</v>
+      </c>
       <c r="I11" s="7"/>
       <c r="J11" s="7"/>
       <c r="K11" s="7"/>
@@ -1500,15 +1998,31 @@
       <c r="N11" s="7"/>
       <c r="O11" s="7"/>
     </row>
-    <row r="12" ht="20.05" customHeight="1">
-      <c r="A12" s="7"/>
-      <c r="B12" s="7"/>
-      <c r="C12" s="7"/>
-      <c r="D12" s="7"/>
-      <c r="E12" s="7"/>
-      <c r="F12" s="7"/>
-      <c r="G12" s="7"/>
-      <c r="H12" s="7"/>
+    <row r="12" spans="1:15" ht="60.25" customHeight="1" x14ac:dyDescent="0.15">
+      <c r="A12" s="7" t="s">
+        <v>47</v>
+      </c>
+      <c r="B12" s="7" t="s">
+        <v>15</v>
+      </c>
+      <c r="C12" s="7" t="s">
+        <v>48</v>
+      </c>
+      <c r="D12" s="7" t="s">
+        <v>42</v>
+      </c>
+      <c r="E12" s="7" t="s">
+        <v>23</v>
+      </c>
+      <c r="F12" s="7" t="s">
+        <v>46</v>
+      </c>
+      <c r="G12" s="7">
+        <v>4689378</v>
+      </c>
+      <c r="H12" s="7">
+        <v>208272</v>
+      </c>
       <c r="I12" s="7"/>
       <c r="J12" s="7"/>
       <c r="K12" s="7"/>
@@ -1517,15 +2031,31 @@
       <c r="N12" s="7"/>
       <c r="O12" s="7"/>
     </row>
-    <row r="13" ht="20.05" customHeight="1">
-      <c r="A13" s="7"/>
-      <c r="B13" s="7"/>
-      <c r="C13" s="7"/>
-      <c r="D13" s="7"/>
-      <c r="E13" s="7"/>
-      <c r="F13" s="7"/>
-      <c r="G13" s="7"/>
-      <c r="H13" s="7"/>
+    <row r="13" spans="1:15" ht="60.25" customHeight="1" x14ac:dyDescent="0.15">
+      <c r="A13" s="7" t="s">
+        <v>49</v>
+      </c>
+      <c r="B13" s="7" t="s">
+        <v>9</v>
+      </c>
+      <c r="C13" s="7" t="s">
+        <v>50</v>
+      </c>
+      <c r="D13" s="7" t="s">
+        <v>51</v>
+      </c>
+      <c r="E13" s="7" t="s">
+        <v>12</v>
+      </c>
+      <c r="F13" s="7" t="s">
+        <v>52</v>
+      </c>
+      <c r="G13" s="7">
+        <v>5725911</v>
+      </c>
+      <c r="H13" s="7">
+        <v>100883</v>
+      </c>
       <c r="I13" s="7"/>
       <c r="J13" s="7"/>
       <c r="K13" s="7"/>
@@ -1534,15 +2064,31 @@
       <c r="N13" s="7"/>
       <c r="O13" s="7"/>
     </row>
-    <row r="14" ht="20.05" customHeight="1">
-      <c r="A14" s="7"/>
-      <c r="B14" s="7"/>
-      <c r="C14" s="7"/>
-      <c r="D14" s="7"/>
-      <c r="E14" s="7"/>
-      <c r="F14" s="7"/>
-      <c r="G14" s="7"/>
-      <c r="H14" s="7"/>
+    <row r="14" spans="1:15" ht="60.25" customHeight="1" x14ac:dyDescent="0.15">
+      <c r="A14" s="7" t="s">
+        <v>53</v>
+      </c>
+      <c r="B14" s="7" t="s">
+        <v>9</v>
+      </c>
+      <c r="C14" s="7" t="s">
+        <v>54</v>
+      </c>
+      <c r="D14" s="7" t="s">
+        <v>30</v>
+      </c>
+      <c r="E14" s="7" t="s">
+        <v>12</v>
+      </c>
+      <c r="F14" s="7" t="s">
+        <v>36</v>
+      </c>
+      <c r="G14" s="7">
+        <v>6354374</v>
+      </c>
+      <c r="H14" s="7">
+        <v>248246</v>
+      </c>
       <c r="I14" s="7"/>
       <c r="J14" s="7"/>
       <c r="K14" s="7"/>
@@ -1551,15 +2097,31 @@
       <c r="N14" s="7"/>
       <c r="O14" s="7"/>
     </row>
-    <row r="15" ht="20.05" customHeight="1">
-      <c r="A15" s="7"/>
-      <c r="B15" s="7"/>
-      <c r="C15" s="7"/>
-      <c r="D15" s="7"/>
-      <c r="E15" s="7"/>
-      <c r="F15" s="7"/>
-      <c r="G15" s="7"/>
-      <c r="H15" s="7"/>
+    <row r="15" spans="1:15" ht="60.25" customHeight="1" x14ac:dyDescent="0.15">
+      <c r="A15" s="7" t="s">
+        <v>55</v>
+      </c>
+      <c r="B15" s="7" t="s">
+        <v>9</v>
+      </c>
+      <c r="C15" s="7" t="s">
+        <v>56</v>
+      </c>
+      <c r="D15" s="7" t="s">
+        <v>30</v>
+      </c>
+      <c r="E15" s="7" t="s">
+        <v>12</v>
+      </c>
+      <c r="F15" s="7" t="s">
+        <v>57</v>
+      </c>
+      <c r="G15" s="7">
+        <v>6407124</v>
+      </c>
+      <c r="H15" s="7">
+        <v>184783</v>
+      </c>
       <c r="I15" s="7"/>
       <c r="J15" s="7"/>
       <c r="K15" s="7"/>
@@ -1568,15 +2130,31 @@
       <c r="N15" s="7"/>
       <c r="O15" s="7"/>
     </row>
-    <row r="16" ht="20.05" customHeight="1">
-      <c r="A16" s="7"/>
-      <c r="B16" s="7"/>
-      <c r="C16" s="7"/>
-      <c r="D16" s="7"/>
-      <c r="E16" s="7"/>
-      <c r="F16" s="7"/>
-      <c r="G16" s="7"/>
-      <c r="H16" s="7"/>
+    <row r="16" spans="1:15" ht="60.25" customHeight="1" x14ac:dyDescent="0.15">
+      <c r="A16" s="7" t="s">
+        <v>58</v>
+      </c>
+      <c r="B16" s="7" t="s">
+        <v>9</v>
+      </c>
+      <c r="C16" s="7" t="s">
+        <v>59</v>
+      </c>
+      <c r="D16" s="7" t="s">
+        <v>60</v>
+      </c>
+      <c r="E16" s="7" t="s">
+        <v>12</v>
+      </c>
+      <c r="F16" s="7" t="s">
+        <v>13</v>
+      </c>
+      <c r="G16" s="7">
+        <v>5138298</v>
+      </c>
+      <c r="H16" s="7">
+        <v>130138</v>
+      </c>
       <c r="I16" s="7"/>
       <c r="J16" s="7"/>
       <c r="K16" s="7"/>
@@ -1585,15 +2163,31 @@
       <c r="N16" s="7"/>
       <c r="O16" s="7"/>
     </row>
-    <row r="17" ht="20.05" customHeight="1">
-      <c r="A17" s="7"/>
-      <c r="B17" s="7"/>
-      <c r="C17" s="7"/>
-      <c r="D17" s="7"/>
-      <c r="E17" s="7"/>
-      <c r="F17" s="7"/>
-      <c r="G17" s="7"/>
-      <c r="H17" s="7"/>
+    <row r="17" spans="1:15" ht="60.25" customHeight="1" x14ac:dyDescent="0.15">
+      <c r="A17" s="7" t="s">
+        <v>61</v>
+      </c>
+      <c r="B17" s="7" t="s">
+        <v>15</v>
+      </c>
+      <c r="C17" s="7" t="s">
+        <v>62</v>
+      </c>
+      <c r="D17" s="7" t="s">
+        <v>60</v>
+      </c>
+      <c r="E17" s="7" t="s">
+        <v>12</v>
+      </c>
+      <c r="F17" s="7" t="s">
+        <v>24</v>
+      </c>
+      <c r="G17" s="7">
+        <v>5315049</v>
+      </c>
+      <c r="H17" s="7">
+        <v>119919</v>
+      </c>
       <c r="I17" s="7"/>
       <c r="J17" s="7"/>
       <c r="K17" s="7"/>
@@ -1602,15 +2196,31 @@
       <c r="N17" s="7"/>
       <c r="O17" s="7"/>
     </row>
-    <row r="18" ht="20.05" customHeight="1">
-      <c r="A18" s="7"/>
-      <c r="B18" s="7"/>
-      <c r="C18" s="7"/>
-      <c r="D18" s="7"/>
-      <c r="E18" s="7"/>
-      <c r="F18" s="7"/>
-      <c r="G18" s="7"/>
-      <c r="H18" s="7"/>
+    <row r="18" spans="1:15" ht="60.25" customHeight="1" x14ac:dyDescent="0.15">
+      <c r="A18" s="7" t="s">
+        <v>63</v>
+      </c>
+      <c r="B18" s="7" t="s">
+        <v>9</v>
+      </c>
+      <c r="C18" s="7" t="s">
+        <v>64</v>
+      </c>
+      <c r="D18" s="7" t="s">
+        <v>30</v>
+      </c>
+      <c r="E18" s="7" t="s">
+        <v>12</v>
+      </c>
+      <c r="F18" s="7" t="s">
+        <v>36</v>
+      </c>
+      <c r="G18" s="7">
+        <v>6056650</v>
+      </c>
+      <c r="H18" s="7">
+        <v>191473</v>
+      </c>
       <c r="I18" s="7"/>
       <c r="J18" s="7"/>
       <c r="K18" s="7"/>
@@ -1619,15 +2229,31 @@
       <c r="N18" s="7"/>
       <c r="O18" s="7"/>
     </row>
-    <row r="19" ht="20.05" customHeight="1">
-      <c r="A19" s="7"/>
-      <c r="B19" s="7"/>
-      <c r="C19" s="7"/>
-      <c r="D19" s="7"/>
-      <c r="E19" s="7"/>
-      <c r="F19" s="7"/>
-      <c r="G19" s="7"/>
-      <c r="H19" s="7"/>
+    <row r="19" spans="1:15" ht="60.25" customHeight="1" x14ac:dyDescent="0.15">
+      <c r="A19" s="7" t="s">
+        <v>65</v>
+      </c>
+      <c r="B19" s="7" t="s">
+        <v>9</v>
+      </c>
+      <c r="C19" s="7" t="s">
+        <v>66</v>
+      </c>
+      <c r="D19" s="7" t="s">
+        <v>67</v>
+      </c>
+      <c r="E19" s="7" t="s">
+        <v>23</v>
+      </c>
+      <c r="F19" s="7" t="s">
+        <v>36</v>
+      </c>
+      <c r="G19" s="7">
+        <v>5355881</v>
+      </c>
+      <c r="H19" s="7">
+        <v>247167</v>
+      </c>
       <c r="I19" s="7"/>
       <c r="J19" s="7"/>
       <c r="K19" s="7"/>
@@ -1636,15 +2262,31 @@
       <c r="N19" s="7"/>
       <c r="O19" s="7"/>
     </row>
-    <row r="20" ht="20.05" customHeight="1">
-      <c r="A20" s="7"/>
-      <c r="B20" s="7"/>
-      <c r="C20" s="7"/>
-      <c r="D20" s="7"/>
-      <c r="E20" s="7"/>
-      <c r="F20" s="7"/>
-      <c r="G20" s="7"/>
-      <c r="H20" s="7"/>
+    <row r="20" spans="1:15" ht="60.25" customHeight="1" x14ac:dyDescent="0.15">
+      <c r="A20" s="7" t="s">
+        <v>68</v>
+      </c>
+      <c r="B20" s="7" t="s">
+        <v>9</v>
+      </c>
+      <c r="C20" s="7" t="s">
+        <v>69</v>
+      </c>
+      <c r="D20" s="7" t="s">
+        <v>30</v>
+      </c>
+      <c r="E20" s="7" t="s">
+        <v>12</v>
+      </c>
+      <c r="F20" s="7" t="s">
+        <v>57</v>
+      </c>
+      <c r="G20" s="7">
+        <v>6493458</v>
+      </c>
+      <c r="H20" s="7">
+        <v>62895</v>
+      </c>
       <c r="I20" s="7"/>
       <c r="J20" s="7"/>
       <c r="K20" s="7"/>
@@ -1653,15 +2295,31 @@
       <c r="N20" s="7"/>
       <c r="O20" s="7"/>
     </row>
-    <row r="21" ht="20.05" customHeight="1">
-      <c r="A21" s="7"/>
-      <c r="B21" s="7"/>
-      <c r="C21" s="7"/>
-      <c r="D21" s="7"/>
-      <c r="E21" s="7"/>
-      <c r="F21" s="7"/>
-      <c r="G21" s="7"/>
-      <c r="H21" s="7"/>
+    <row r="21" spans="1:15" ht="60.25" customHeight="1" x14ac:dyDescent="0.15">
+      <c r="A21" s="7" t="s">
+        <v>70</v>
+      </c>
+      <c r="B21" s="7" t="s">
+        <v>15</v>
+      </c>
+      <c r="C21" s="7" t="s">
+        <v>71</v>
+      </c>
+      <c r="D21" s="7" t="s">
+        <v>27</v>
+      </c>
+      <c r="E21" s="7" t="s">
+        <v>12</v>
+      </c>
+      <c r="F21" s="7" t="s">
+        <v>46</v>
+      </c>
+      <c r="G21" s="7">
+        <v>4626982</v>
+      </c>
+      <c r="H21" s="7">
+        <v>105369</v>
+      </c>
       <c r="I21" s="7"/>
       <c r="J21" s="7"/>
       <c r="K21" s="7"/>
@@ -1670,15 +2328,31 @@
       <c r="N21" s="7"/>
       <c r="O21" s="7"/>
     </row>
-    <row r="22" ht="20.05" customHeight="1">
-      <c r="A22" s="7"/>
-      <c r="B22" s="7"/>
-      <c r="C22" s="7"/>
-      <c r="D22" s="7"/>
-      <c r="E22" s="7"/>
-      <c r="F22" s="7"/>
-      <c r="G22" s="7"/>
-      <c r="H22" s="7"/>
+    <row r="22" spans="1:15" ht="60.25" customHeight="1" x14ac:dyDescent="0.15">
+      <c r="A22" s="7" t="s">
+        <v>72</v>
+      </c>
+      <c r="B22" s="7" t="s">
+        <v>15</v>
+      </c>
+      <c r="C22" s="7" t="s">
+        <v>73</v>
+      </c>
+      <c r="D22" s="7" t="s">
+        <v>60</v>
+      </c>
+      <c r="E22" s="7" t="s">
+        <v>12</v>
+      </c>
+      <c r="F22" s="7" t="s">
+        <v>31</v>
+      </c>
+      <c r="G22" s="7">
+        <v>5845751</v>
+      </c>
+      <c r="H22" s="7">
+        <v>168639</v>
+      </c>
       <c r="I22" s="7"/>
       <c r="J22" s="7"/>
       <c r="K22" s="7"/>
@@ -1687,9 +2361,659 @@
       <c r="N22" s="7"/>
       <c r="O22" s="7"/>
     </row>
+    <row r="23" spans="1:15" ht="60.25" customHeight="1" x14ac:dyDescent="0.15">
+      <c r="A23" s="6" t="s">
+        <v>74</v>
+      </c>
+      <c r="B23" s="6" t="s">
+        <v>9</v>
+      </c>
+      <c r="C23" s="6" t="s">
+        <v>75</v>
+      </c>
+      <c r="D23" s="6" t="s">
+        <v>30</v>
+      </c>
+      <c r="E23" s="6" t="s">
+        <v>12</v>
+      </c>
+      <c r="F23" s="6" t="s">
+        <v>24</v>
+      </c>
+      <c r="G23" s="6">
+        <v>6150412</v>
+      </c>
+      <c r="H23" s="6">
+        <v>149000</v>
+      </c>
+    </row>
+    <row r="24" spans="1:15" ht="60.25" customHeight="1" x14ac:dyDescent="0.15">
+      <c r="A24" s="6" t="s">
+        <v>76</v>
+      </c>
+      <c r="B24" s="6" t="s">
+        <v>15</v>
+      </c>
+      <c r="C24" s="6" t="s">
+        <v>77</v>
+      </c>
+      <c r="D24" s="6" t="s">
+        <v>60</v>
+      </c>
+      <c r="E24" s="6" t="s">
+        <v>12</v>
+      </c>
+      <c r="F24" s="6" t="s">
+        <v>31</v>
+      </c>
+      <c r="G24" s="6">
+        <v>6205095</v>
+      </c>
+      <c r="H24" s="6">
+        <v>228985</v>
+      </c>
+    </row>
+    <row r="25" spans="1:15" ht="60.25" customHeight="1" x14ac:dyDescent="0.15">
+      <c r="A25" s="6" t="s">
+        <v>78</v>
+      </c>
+      <c r="B25" s="6" t="s">
+        <v>15</v>
+      </c>
+      <c r="C25" s="6" t="s">
+        <v>79</v>
+      </c>
+      <c r="D25" s="6" t="s">
+        <v>17</v>
+      </c>
+      <c r="E25" s="6" t="s">
+        <v>18</v>
+      </c>
+      <c r="F25" s="6" t="s">
+        <v>13</v>
+      </c>
+      <c r="G25" s="6">
+        <v>5081487</v>
+      </c>
+      <c r="H25" s="6">
+        <v>226026</v>
+      </c>
+    </row>
+    <row r="26" spans="1:15" ht="60.25" customHeight="1" x14ac:dyDescent="0.15">
+      <c r="A26" s="6" t="s">
+        <v>80</v>
+      </c>
+      <c r="B26" s="6" t="s">
+        <v>9</v>
+      </c>
+      <c r="C26" s="6" t="s">
+        <v>81</v>
+      </c>
+      <c r="D26" s="6" t="s">
+        <v>51</v>
+      </c>
+      <c r="E26" s="6" t="s">
+        <v>12</v>
+      </c>
+      <c r="F26" s="6" t="s">
+        <v>19</v>
+      </c>
+      <c r="G26" s="6">
+        <v>5886338</v>
+      </c>
+      <c r="H26" s="6">
+        <v>228134</v>
+      </c>
+    </row>
+    <row r="27" spans="1:15" ht="60.25" customHeight="1" x14ac:dyDescent="0.15">
+      <c r="A27" s="6" t="s">
+        <v>82</v>
+      </c>
+      <c r="B27" s="6" t="s">
+        <v>9</v>
+      </c>
+      <c r="C27" s="6" t="s">
+        <v>83</v>
+      </c>
+      <c r="D27" s="6" t="s">
+        <v>27</v>
+      </c>
+      <c r="E27" s="6" t="s">
+        <v>12</v>
+      </c>
+      <c r="F27" s="6" t="s">
+        <v>31</v>
+      </c>
+      <c r="G27" s="6">
+        <v>5734914</v>
+      </c>
+      <c r="H27" s="6">
+        <v>85874</v>
+      </c>
+    </row>
+    <row r="28" spans="1:15" ht="60.25" customHeight="1" x14ac:dyDescent="0.15">
+      <c r="A28" s="6" t="s">
+        <v>84</v>
+      </c>
+      <c r="B28" s="6" t="s">
+        <v>9</v>
+      </c>
+      <c r="C28" s="6" t="s">
+        <v>83</v>
+      </c>
+      <c r="D28" s="6" t="s">
+        <v>27</v>
+      </c>
+      <c r="E28" s="6" t="s">
+        <v>12</v>
+      </c>
+      <c r="F28" s="6" t="s">
+        <v>24</v>
+      </c>
+      <c r="G28" s="6">
+        <v>6055495</v>
+      </c>
+      <c r="H28" s="6">
+        <v>111352</v>
+      </c>
+    </row>
+    <row r="29" spans="1:15" ht="60.25" customHeight="1" x14ac:dyDescent="0.15">
+      <c r="A29" s="6" t="s">
+        <v>85</v>
+      </c>
+      <c r="B29" s="6" t="s">
+        <v>9</v>
+      </c>
+      <c r="C29" s="6" t="s">
+        <v>86</v>
+      </c>
+      <c r="D29" s="6" t="s">
+        <v>87</v>
+      </c>
+      <c r="E29" s="6" t="s">
+        <v>18</v>
+      </c>
+      <c r="F29" s="6" t="s">
+        <v>57</v>
+      </c>
+      <c r="G29" s="6">
+        <v>6131619</v>
+      </c>
+      <c r="H29" s="6">
+        <v>95906</v>
+      </c>
+    </row>
+    <row r="30" spans="1:15" ht="60.25" customHeight="1" x14ac:dyDescent="0.15">
+      <c r="A30" s="6" t="s">
+        <v>88</v>
+      </c>
+      <c r="B30" s="6" t="s">
+        <v>9</v>
+      </c>
+      <c r="C30" s="6" t="s">
+        <v>89</v>
+      </c>
+      <c r="D30" s="6" t="s">
+        <v>90</v>
+      </c>
+      <c r="E30" s="6" t="s">
+        <v>12</v>
+      </c>
+      <c r="F30" s="6" t="s">
+        <v>31</v>
+      </c>
+      <c r="G30" s="6">
+        <v>5563916</v>
+      </c>
+      <c r="H30" s="6">
+        <v>220072</v>
+      </c>
+    </row>
+    <row r="31" spans="1:15" ht="60.25" customHeight="1" x14ac:dyDescent="0.15">
+      <c r="A31" s="6" t="s">
+        <v>91</v>
+      </c>
+      <c r="B31" s="6" t="s">
+        <v>9</v>
+      </c>
+      <c r="C31" s="6" t="s">
+        <v>92</v>
+      </c>
+      <c r="D31" s="6" t="s">
+        <v>30</v>
+      </c>
+      <c r="E31" s="6" t="s">
+        <v>12</v>
+      </c>
+      <c r="F31" s="6" t="s">
+        <v>19</v>
+      </c>
+      <c r="G31" s="6">
+        <v>4709389</v>
+      </c>
+      <c r="H31" s="6">
+        <v>221066</v>
+      </c>
+    </row>
+    <row r="32" spans="1:15" ht="60.25" customHeight="1" x14ac:dyDescent="0.15">
+      <c r="A32" s="6" t="s">
+        <v>93</v>
+      </c>
+      <c r="B32" s="6" t="s">
+        <v>15</v>
+      </c>
+      <c r="C32" s="6" t="s">
+        <v>94</v>
+      </c>
+      <c r="D32" s="6" t="s">
+        <v>17</v>
+      </c>
+      <c r="E32" s="6" t="s">
+        <v>18</v>
+      </c>
+      <c r="F32" s="6" t="s">
+        <v>31</v>
+      </c>
+      <c r="G32" s="6">
+        <v>4959610</v>
+      </c>
+      <c r="H32" s="6">
+        <v>151120</v>
+      </c>
+    </row>
+    <row r="33" spans="1:8" ht="60.25" customHeight="1" x14ac:dyDescent="0.15">
+      <c r="A33" s="6" t="s">
+        <v>95</v>
+      </c>
+      <c r="B33" s="6" t="s">
+        <v>15</v>
+      </c>
+      <c r="C33" s="6" t="s">
+        <v>96</v>
+      </c>
+      <c r="D33" s="6" t="s">
+        <v>97</v>
+      </c>
+      <c r="E33" s="6" t="s">
+        <v>12</v>
+      </c>
+      <c r="F33" s="6" t="s">
+        <v>43</v>
+      </c>
+      <c r="G33" s="6">
+        <v>4617348</v>
+      </c>
+      <c r="H33" s="6">
+        <v>171564</v>
+      </c>
+    </row>
+    <row r="34" spans="1:8" ht="60.25" customHeight="1" x14ac:dyDescent="0.15">
+      <c r="A34" s="6" t="s">
+        <v>98</v>
+      </c>
+      <c r="B34" s="6" t="s">
+        <v>15</v>
+      </c>
+      <c r="C34" s="6" t="s">
+        <v>99</v>
+      </c>
+      <c r="D34" s="6" t="s">
+        <v>100</v>
+      </c>
+      <c r="E34" s="6" t="s">
+        <v>12</v>
+      </c>
+      <c r="F34" s="6" t="s">
+        <v>13</v>
+      </c>
+      <c r="G34" s="6">
+        <v>5003119</v>
+      </c>
+      <c r="H34" s="6">
+        <v>24112</v>
+      </c>
+    </row>
+    <row r="35" spans="1:8" ht="60.25" customHeight="1" x14ac:dyDescent="0.15">
+      <c r="A35" s="6" t="s">
+        <v>101</v>
+      </c>
+      <c r="B35" s="6" t="s">
+        <v>9</v>
+      </c>
+      <c r="C35" s="6" t="s">
+        <v>102</v>
+      </c>
+      <c r="D35" s="6" t="s">
+        <v>87</v>
+      </c>
+      <c r="E35" s="6" t="s">
+        <v>18</v>
+      </c>
+      <c r="F35" s="6" t="s">
+        <v>43</v>
+      </c>
+      <c r="G35" s="6">
+        <v>5561977</v>
+      </c>
+      <c r="H35" s="6">
+        <v>71203</v>
+      </c>
+    </row>
+    <row r="36" spans="1:8" ht="60.25" customHeight="1" x14ac:dyDescent="0.15">
+      <c r="A36" s="6" t="s">
+        <v>103</v>
+      </c>
+      <c r="B36" s="6" t="s">
+        <v>9</v>
+      </c>
+      <c r="C36" s="6" t="s">
+        <v>104</v>
+      </c>
+      <c r="D36" s="6" t="s">
+        <v>100</v>
+      </c>
+      <c r="E36" s="6" t="s">
+        <v>12</v>
+      </c>
+      <c r="F36" s="6" t="s">
+        <v>19</v>
+      </c>
+      <c r="G36" s="6">
+        <v>6495117</v>
+      </c>
+      <c r="H36" s="6">
+        <v>175099</v>
+      </c>
+    </row>
+    <row r="37" spans="1:8" ht="60.25" customHeight="1" x14ac:dyDescent="0.15">
+      <c r="A37" s="6" t="s">
+        <v>105</v>
+      </c>
+      <c r="B37" s="6" t="s">
+        <v>9</v>
+      </c>
+      <c r="C37" s="6" t="s">
+        <v>106</v>
+      </c>
+      <c r="D37" s="6" t="s">
+        <v>107</v>
+      </c>
+      <c r="E37" s="6" t="s">
+        <v>23</v>
+      </c>
+      <c r="F37" s="6" t="s">
+        <v>46</v>
+      </c>
+      <c r="G37" s="6">
+        <v>6083045</v>
+      </c>
+      <c r="H37" s="6">
+        <v>190952</v>
+      </c>
+    </row>
+    <row r="38" spans="1:8" ht="60.25" customHeight="1" x14ac:dyDescent="0.15">
+      <c r="A38" s="6" t="s">
+        <v>108</v>
+      </c>
+      <c r="B38" s="6" t="s">
+        <v>15</v>
+      </c>
+      <c r="C38" s="6" t="s">
+        <v>109</v>
+      </c>
+      <c r="D38" s="6" t="s">
+        <v>87</v>
+      </c>
+      <c r="E38" s="6" t="s">
+        <v>18</v>
+      </c>
+      <c r="F38" s="6" t="s">
+        <v>13</v>
+      </c>
+      <c r="G38" s="6">
+        <v>5606685</v>
+      </c>
+      <c r="H38" s="6">
+        <v>6797</v>
+      </c>
+    </row>
+    <row r="39" spans="1:8" ht="60.25" customHeight="1" x14ac:dyDescent="0.15">
+      <c r="A39" s="6" t="s">
+        <v>110</v>
+      </c>
+      <c r="B39" s="6" t="s">
+        <v>9</v>
+      </c>
+      <c r="C39" s="6" t="s">
+        <v>111</v>
+      </c>
+      <c r="D39" s="6" t="s">
+        <v>42</v>
+      </c>
+      <c r="E39" s="6" t="s">
+        <v>23</v>
+      </c>
+      <c r="F39" s="6" t="s">
+        <v>39</v>
+      </c>
+      <c r="G39" s="6">
+        <v>6153147</v>
+      </c>
+      <c r="H39" s="6">
+        <v>140752</v>
+      </c>
+    </row>
+    <row r="40" spans="1:8" ht="60.25" customHeight="1" x14ac:dyDescent="0.15">
+      <c r="A40" s="6" t="s">
+        <v>112</v>
+      </c>
+      <c r="B40" s="6" t="s">
+        <v>15</v>
+      </c>
+      <c r="C40" s="6" t="s">
+        <v>113</v>
+      </c>
+      <c r="D40" s="6" t="s">
+        <v>97</v>
+      </c>
+      <c r="E40" s="6" t="s">
+        <v>12</v>
+      </c>
+      <c r="F40" s="6" t="s">
+        <v>52</v>
+      </c>
+      <c r="G40" s="6">
+        <v>5827858</v>
+      </c>
+      <c r="H40" s="6">
+        <v>238612</v>
+      </c>
+    </row>
+    <row r="41" spans="1:8" ht="60.25" customHeight="1" x14ac:dyDescent="0.15">
+      <c r="A41" s="6" t="s">
+        <v>114</v>
+      </c>
+      <c r="B41" s="6" t="s">
+        <v>15</v>
+      </c>
+      <c r="C41" s="6" t="s">
+        <v>115</v>
+      </c>
+      <c r="D41" s="6" t="s">
+        <v>30</v>
+      </c>
+      <c r="E41" s="6" t="s">
+        <v>12</v>
+      </c>
+      <c r="F41" s="6" t="s">
+        <v>19</v>
+      </c>
+      <c r="G41" s="6">
+        <v>4874017</v>
+      </c>
+      <c r="H41" s="6">
+        <v>194350</v>
+      </c>
+    </row>
+    <row r="42" spans="1:8" ht="60.25" customHeight="1" x14ac:dyDescent="0.15">
+      <c r="A42" s="6" t="s">
+        <v>116</v>
+      </c>
+      <c r="B42" s="6" t="s">
+        <v>9</v>
+      </c>
+      <c r="C42" s="6" t="s">
+        <v>117</v>
+      </c>
+      <c r="D42" s="6" t="s">
+        <v>17</v>
+      </c>
+      <c r="E42" s="6" t="s">
+        <v>18</v>
+      </c>
+      <c r="F42" s="6" t="s">
+        <v>19</v>
+      </c>
+      <c r="G42" s="6">
+        <v>4943961</v>
+      </c>
+      <c r="H42" s="6">
+        <v>207056</v>
+      </c>
+    </row>
+    <row r="43" spans="1:8" ht="60.25" customHeight="1" x14ac:dyDescent="0.15">
+      <c r="A43" s="6" t="s">
+        <v>118</v>
+      </c>
+      <c r="B43" s="6" t="s">
+        <v>9</v>
+      </c>
+      <c r="C43" s="6" t="s">
+        <v>119</v>
+      </c>
+      <c r="D43" s="6" t="s">
+        <v>107</v>
+      </c>
+      <c r="E43" s="6" t="s">
+        <v>23</v>
+      </c>
+      <c r="F43" s="6" t="s">
+        <v>19</v>
+      </c>
+      <c r="G43" s="6">
+        <v>5085234</v>
+      </c>
+      <c r="H43" s="6">
+        <v>76830</v>
+      </c>
+    </row>
+    <row r="44" spans="1:8" ht="60.25" customHeight="1" x14ac:dyDescent="0.15">
+      <c r="A44" s="6" t="s">
+        <v>120</v>
+      </c>
+      <c r="B44" s="6" t="s">
+        <v>15</v>
+      </c>
+      <c r="C44" s="6" t="s">
+        <v>75</v>
+      </c>
+      <c r="D44" s="6" t="s">
+        <v>30</v>
+      </c>
+      <c r="E44" s="6" t="s">
+        <v>12</v>
+      </c>
+      <c r="F44" s="6" t="s">
+        <v>39</v>
+      </c>
+      <c r="G44" s="6">
+        <v>6338271</v>
+      </c>
+      <c r="H44" s="6">
+        <v>216241</v>
+      </c>
+    </row>
+    <row r="45" spans="1:8" ht="60.25" customHeight="1" x14ac:dyDescent="0.15">
+      <c r="A45" s="6" t="s">
+        <v>121</v>
+      </c>
+      <c r="B45" s="6" t="s">
+        <v>9</v>
+      </c>
+      <c r="C45" s="6" t="s">
+        <v>86</v>
+      </c>
+      <c r="D45" s="6" t="s">
+        <v>87</v>
+      </c>
+      <c r="E45" s="6" t="s">
+        <v>18</v>
+      </c>
+      <c r="F45" s="6" t="s">
+        <v>39</v>
+      </c>
+      <c r="G45" s="6">
+        <v>6318975</v>
+      </c>
+      <c r="H45" s="6">
+        <v>146281</v>
+      </c>
+    </row>
+    <row r="46" spans="1:8" ht="60.25" customHeight="1" x14ac:dyDescent="0.15">
+      <c r="A46" s="6" t="s">
+        <v>122</v>
+      </c>
+      <c r="B46" s="6" t="s">
+        <v>15</v>
+      </c>
+      <c r="C46" s="6" t="s">
+        <v>123</v>
+      </c>
+      <c r="D46" s="6" t="s">
+        <v>42</v>
+      </c>
+      <c r="E46" s="6" t="s">
+        <v>23</v>
+      </c>
+      <c r="F46" s="6" t="s">
+        <v>52</v>
+      </c>
+      <c r="G46" s="6">
+        <v>5753572</v>
+      </c>
+      <c r="H46" s="6">
+        <v>226433</v>
+      </c>
+    </row>
+    <row r="47" spans="1:8" ht="60.25" customHeight="1" x14ac:dyDescent="0.15">
+      <c r="A47" s="6" t="s">
+        <v>124</v>
+      </c>
+      <c r="B47" s="6" t="s">
+        <v>9</v>
+      </c>
+      <c r="C47" s="6" t="s">
+        <v>125</v>
+      </c>
+      <c r="D47" s="6" t="s">
+        <v>90</v>
+      </c>
+      <c r="E47" s="6" t="s">
+        <v>12</v>
+      </c>
+      <c r="F47" s="6" t="s">
+        <v>43</v>
+      </c>
+      <c r="G47" s="6">
+        <v>5710328</v>
+      </c>
+      <c r="H47" s="6">
+        <v>78084</v>
+      </c>
+    </row>
   </sheetData>
-  <pageMargins left="0.5" right="0.5" top="0.75" bottom="0.75" header="0.277778" footer="0.277778"/>
-  <pageSetup firstPageNumber="1" fitToHeight="1" fitToWidth="1" scale="72" useFirstPageNumber="0" orientation="portrait" pageOrder="downThenOver"/>
+  <pageMargins left="0.5" right="0.5" top="0.75" bottom="0.75" header="0.27777800000000002" footer="0.27777800000000002"/>
+  <pageSetup scale="72" orientation="portrait"/>
   <headerFooter>
     <oddFooter>&amp;C&amp;"Helvetica Neue,Regular"&amp;12&amp;K000000&amp;P</oddFooter>
   </headerFooter>

--- a/mockdata/StarAMR_Metrics.xlsx
+++ b/mockdata/StarAMR_Metrics.xlsx
@@ -1,131 +1,55 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
-<workbook xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+<workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+  <workbookPr/>
   <bookViews>
-    <workbookView xWindow="0" yWindow="40" windowWidth="15960" windowHeight="18080"/>
+    <workbookView visibility="visible" minimized="0" showHorizontalScroll="1" showVerticalScroll="1" showSheetTabs="1" xWindow="0" yWindow="40" windowWidth="15960" windowHeight="18080" tabRatio="600" firstSheet="0" activeTab="0" autoFilterDateGrouping="1"/>
   </bookViews>
   <sheets>
-    <sheet name="Sheet 1" sheetId="1" r:id="rId4"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Sheet 1" sheetId="1" state="visible" r:id="rId1"/>
   </sheets>
+  <definedNames/>
 </workbook>
-</file>
-
-<file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" uniqueCount="25">
-  <si>
-    <t>Isolate ID</t>
-  </si>
-  <si>
-    <t>Quality Status</t>
-  </si>
-  <si>
-    <t>Genotype</t>
-  </si>
-  <si>
-    <t>Predicted Phenotype</t>
-  </si>
-  <si>
-    <t>SIR Profile</t>
-  </si>
-  <si>
-    <t>Plasmid</t>
-  </si>
-  <si>
-    <t>Genome Length</t>
-  </si>
-  <si>
-    <t>N50 Value</t>
-  </si>
-  <si>
-    <t>ISO-101</t>
-  </si>
-  <si>
-    <t>Passed</t>
-  </si>
-  <si>
-    <t>aph(3')-Ia, blaCTX-M-14</t>
-  </si>
-  <si>
-    <t>kanamycin, ampicillin, ceftriaxone</t>
-  </si>
-  <si>
-    <t>Resistant</t>
-  </si>
-  <si>
-    <t>IncFIB(K)</t>
-  </si>
-  <si>
-    <t>ISO-102</t>
-  </si>
-  <si>
-    <t>Failed</t>
-  </si>
-  <si>
-    <t>tet(A)</t>
-  </si>
-  <si>
-    <t>tetracycline</t>
-  </si>
-  <si>
-    <t>Intermediate</t>
-  </si>
-  <si>
-    <t>Col(BS512)</t>
-  </si>
-  <si>
-    <t>ISO-103</t>
-  </si>
-  <si>
-    <t>blaTEM-1B, sul2</t>
-  </si>
-  <si>
-    <t>ampicillin, sulfisoxazole</t>
-  </si>
-  <si>
-    <t>Susceptible</t>
-  </si>
-  <si>
-    <t>IncX1</t>
-  </si>
-</sst>
 </file>
 
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
-  <numFmts count="1">
-    <numFmt numFmtId="0" formatCode="General"/>
-  </numFmts>
-  <fonts count="5">
+  <numFmts count="0"/>
+  <fonts count="6">
     <font>
+      <name val="Helvetica Neue"/>
+      <color indexed="8"/>
       <sz val="10"/>
-      <color indexed="8"/>
-      <name val="Helvetica Neue"/>
     </font>
     <font>
+      <name val="Helvetica Neue"/>
+      <color indexed="8"/>
       <sz val="12"/>
-      <color indexed="8"/>
-      <name val="Helvetica Neue"/>
     </font>
     <font>
+      <name val="Calibri"/>
+      <color indexed="8"/>
       <sz val="15"/>
-      <color indexed="8"/>
-      <name val="Calibri"/>
+    </font>
+    <font>
+      <name val="Helvetica"/>
+      <b val="1"/>
+      <color indexed="9"/>
+      <sz val="12"/>
+    </font>
+    <font>
+      <name val="Helvetica"/>
+      <color indexed="9"/>
+      <sz val="12"/>
     </font>
     <font>
       <b val="1"/>
-      <sz val="12"/>
-      <color indexed="9"/>
-      <name val="Helvetica"/>
-    </font>
-    <font>
-      <sz val="12"/>
-      <color indexed="9"/>
-      <name val="Helvetica"/>
+      <color rgb="00FFFFFF"/>
     </font>
   </fonts>
-  <fills count="3">
+  <fills count="4">
     <fill>
-      <patternFill patternType="none"/>
+      <patternFill/>
     </fill>
     <fill>
       <patternFill patternType="gray125"/>
@@ -134,6 +58,11 @@
       <patternFill patternType="solid">
         <fgColor indexed="10"/>
         <bgColor auto="1"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="001F3864"/>
       </patternFill>
     </fill>
   </fills>
@@ -162,41 +91,44 @@
     </border>
   </borders>
   <cellStyleXfs count="1">
-    <xf numFmtId="0" fontId="0" applyNumberFormat="0" applyFont="1" applyFill="0" applyBorder="0" applyAlignment="1" applyProtection="0">
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" applyAlignment="1">
       <alignment vertical="top" wrapText="1"/>
     </xf>
   </cellStyleXfs>
-  <cellXfs count="8">
-    <xf numFmtId="0" fontId="0" applyNumberFormat="0" applyFont="1" applyFill="0" applyBorder="0" applyAlignment="1" applyProtection="0">
+  <cellXfs count="10">
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment vertical="top" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="0" applyNumberFormat="1" applyFont="1" applyFill="0" applyBorder="0" applyAlignment="1" applyProtection="0">
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment vertical="top" wrapText="1"/>
     </xf>
-    <xf numFmtId="49" fontId="3" fillId="2" borderId="1" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="0">
+    <xf numFmtId="49" fontId="3" fillId="2" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="3" fillId="2" borderId="1" applyNumberFormat="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="0">
+    <xf numFmtId="0" fontId="3" fillId="2" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="49" fontId="4" borderId="1" applyNumberFormat="1" applyFont="1" applyFill="0" applyBorder="1" applyAlignment="1" applyProtection="0">
+    <xf numFmtId="49" fontId="4" fillId="0" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="4" borderId="1" applyNumberFormat="1" applyFont="1" applyFill="0" applyBorder="1" applyAlignment="1" applyProtection="0">
+    <xf numFmtId="0" fontId="4" fillId="0" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="4" borderId="1" applyNumberFormat="0" applyFont="1" applyFill="0" applyBorder="1" applyAlignment="1" applyProtection="0">
+    <xf numFmtId="0" fontId="4" fillId="0" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="0" borderId="1" applyNumberFormat="0" applyFont="1" applyFill="0" applyBorder="1" applyAlignment="1" applyProtection="0">
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment vertical="top" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="49" fontId="5" fillId="3" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="center"/>
     </xf>
   </cellXfs>
   <cellStyles count="1">
     <cellStyle name="Normal" xfId="0" builtinId="0"/>
   </cellStyles>
-  <dxfs count="0"/>
-  <tableStyles count="0"/>
+  <tableStyles count="0" defaultTableStyle="TableStyleMedium9" defaultPivotStyle="PivotStyleLight16"/>
   <colors>
     <indexedColors>
       <rgbColor rgb="ff000000"/>
@@ -1241,457 +1173,3497 @@
 </file>
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
-  <dimension ref="A1:O22"/>
-  <sheetFormatPr defaultColWidth="16.3333" defaultRowHeight="13.9" customHeight="1" outlineLevelRow="0" outlineLevelCol="0"/>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+  <sheetPr>
+    <outlinePr summaryBelow="1" summaryRight="1"/>
+    <pageSetUpPr/>
+  </sheetPr>
+  <dimension ref="A1:O91"/>
+  <sheetFormatPr baseColWidth="8" defaultColWidth="16.3333" defaultRowHeight="13.9" customHeight="1" outlineLevelRow="0"/>
   <cols>
-    <col min="1" max="15" width="16.3516" style="1" customWidth="1"/>
-    <col min="16" max="16384" width="16.3516" style="1" customWidth="1"/>
+    <col width="16.3516" customWidth="1" style="1" min="1" max="15"/>
+    <col width="16.3516" customWidth="1" style="1" min="16" max="16384"/>
   </cols>
   <sheetData>
-    <row r="1" ht="60.55" customHeight="1">
-      <c r="A1" t="s" s="2">
-        <v>0</v>
-      </c>
-      <c r="B1" t="s" s="2">
-        <v>1</v>
-      </c>
-      <c r="C1" t="s" s="2">
-        <v>2</v>
-      </c>
-      <c r="D1" t="s" s="2">
-        <v>3</v>
-      </c>
-      <c r="E1" t="s" s="2">
-        <v>4</v>
-      </c>
-      <c r="F1" t="s" s="2">
-        <v>5</v>
-      </c>
-      <c r="G1" t="s" s="2">
-        <v>6</v>
-      </c>
-      <c r="H1" t="s" s="2">
-        <v>7</v>
-      </c>
-      <c r="I1" s="3"/>
-      <c r="J1" s="3"/>
-      <c r="K1" s="3"/>
-      <c r="L1" s="3"/>
-      <c r="M1" s="3"/>
-      <c r="N1" s="3"/>
-      <c r="O1" s="3"/>
-    </row>
-    <row r="2" ht="74.55" customHeight="1">
-      <c r="A2" t="s" s="4">
-        <v>8</v>
-      </c>
-      <c r="B2" t="s" s="4">
-        <v>9</v>
-      </c>
-      <c r="C2" t="s" s="4">
-        <v>10</v>
-      </c>
-      <c r="D2" t="s" s="4">
-        <v>11</v>
-      </c>
-      <c r="E2" t="s" s="4">
-        <v>12</v>
-      </c>
-      <c r="F2" t="s" s="4">
-        <v>13</v>
-      </c>
-      <c r="G2" s="5">
-        <v>5017831</v>
-      </c>
-      <c r="H2" s="5">
-        <v>156657</v>
-      </c>
-      <c r="I2" s="6"/>
-      <c r="J2" s="6"/>
-      <c r="K2" s="6"/>
-      <c r="L2" s="6"/>
-      <c r="M2" s="6"/>
-      <c r="N2" s="6"/>
-      <c r="O2" s="6"/>
-    </row>
-    <row r="3" ht="46.35" customHeight="1">
-      <c r="A3" t="s" s="4">
-        <v>14</v>
-      </c>
-      <c r="B3" t="s" s="4">
-        <v>15</v>
-      </c>
-      <c r="C3" t="s" s="4">
-        <v>16</v>
-      </c>
-      <c r="D3" t="s" s="4">
-        <v>17</v>
-      </c>
-      <c r="E3" t="s" s="4">
-        <v>18</v>
-      </c>
-      <c r="F3" t="s" s="4">
-        <v>19</v>
-      </c>
-      <c r="G3" s="5">
-        <v>6133820</v>
-      </c>
-      <c r="H3" s="5">
-        <v>1660</v>
-      </c>
-      <c r="I3" s="6"/>
-      <c r="J3" s="6"/>
-      <c r="K3" s="6"/>
-      <c r="L3" s="6"/>
-      <c r="M3" s="6"/>
-      <c r="N3" s="6"/>
-      <c r="O3" s="6"/>
-    </row>
-    <row r="4" ht="60.35" customHeight="1">
-      <c r="A4" t="s" s="4">
-        <v>20</v>
-      </c>
-      <c r="B4" t="s" s="4">
-        <v>9</v>
-      </c>
-      <c r="C4" t="s" s="4">
-        <v>21</v>
-      </c>
-      <c r="D4" t="s" s="4">
-        <v>22</v>
-      </c>
-      <c r="E4" t="s" s="4">
-        <v>23</v>
-      </c>
-      <c r="F4" t="s" s="4">
-        <v>24</v>
-      </c>
-      <c r="G4" s="5">
-        <v>5025249</v>
-      </c>
-      <c r="H4" s="5">
-        <v>125507</v>
-      </c>
-      <c r="I4" s="6"/>
-      <c r="J4" s="6"/>
-      <c r="K4" s="6"/>
-      <c r="L4" s="6"/>
-      <c r="M4" s="6"/>
-      <c r="N4" s="6"/>
-      <c r="O4" s="6"/>
-    </row>
-    <row r="5" ht="46.35" customHeight="1">
-      <c r="A5" s="6"/>
-      <c r="B5" s="6"/>
-      <c r="C5" s="6"/>
-      <c r="D5" s="6"/>
-      <c r="E5" s="6"/>
-      <c r="F5" s="6"/>
-      <c r="G5" s="6"/>
-      <c r="H5" s="6"/>
-      <c r="I5" s="6"/>
-      <c r="J5" s="6"/>
-      <c r="K5" s="6"/>
-      <c r="L5" s="6"/>
-      <c r="M5" s="7"/>
-      <c r="N5" s="7"/>
-      <c r="O5" s="7"/>
-    </row>
-    <row r="6" ht="20.05" customHeight="1">
-      <c r="A6" s="7"/>
-      <c r="B6" s="7"/>
-      <c r="C6" s="7"/>
-      <c r="D6" s="7"/>
-      <c r="E6" s="7"/>
-      <c r="F6" s="7"/>
-      <c r="G6" s="7"/>
-      <c r="H6" s="7"/>
-      <c r="I6" s="7"/>
-      <c r="J6" s="7"/>
-      <c r="K6" s="7"/>
-      <c r="L6" s="7"/>
-      <c r="M6" s="7"/>
-      <c r="N6" s="7"/>
-      <c r="O6" s="7"/>
-    </row>
-    <row r="7" ht="20.05" customHeight="1">
-      <c r="A7" s="7"/>
-      <c r="B7" s="7"/>
-      <c r="C7" s="7"/>
-      <c r="D7" s="7"/>
-      <c r="E7" s="7"/>
-      <c r="F7" s="7"/>
-      <c r="G7" s="7"/>
-      <c r="H7" s="7"/>
-      <c r="I7" s="7"/>
-      <c r="J7" s="7"/>
-      <c r="K7" s="7"/>
-      <c r="L7" s="7"/>
-      <c r="M7" s="7"/>
-      <c r="N7" s="7"/>
-      <c r="O7" s="7"/>
-    </row>
-    <row r="8" ht="20.05" customHeight="1">
-      <c r="A8" s="7"/>
-      <c r="B8" s="7"/>
-      <c r="C8" s="7"/>
-      <c r="D8" s="7"/>
-      <c r="E8" s="7"/>
-      <c r="F8" s="7"/>
-      <c r="G8" s="7"/>
-      <c r="H8" s="7"/>
-      <c r="I8" s="7"/>
-      <c r="J8" s="7"/>
-      <c r="K8" s="7"/>
-      <c r="L8" s="7"/>
-      <c r="M8" s="7"/>
-      <c r="N8" s="7"/>
-      <c r="O8" s="7"/>
-    </row>
-    <row r="9" ht="20.05" customHeight="1">
-      <c r="A9" s="7"/>
-      <c r="B9" s="7"/>
-      <c r="C9" s="7"/>
-      <c r="D9" s="7"/>
-      <c r="E9" s="7"/>
-      <c r="F9" s="7"/>
-      <c r="G9" s="7"/>
-      <c r="H9" s="7"/>
-      <c r="I9" s="7"/>
-      <c r="J9" s="7"/>
-      <c r="K9" s="7"/>
-      <c r="L9" s="7"/>
-      <c r="M9" s="7"/>
-      <c r="N9" s="7"/>
-      <c r="O9" s="7"/>
-    </row>
-    <row r="10" ht="20.05" customHeight="1">
-      <c r="A10" s="7"/>
-      <c r="B10" s="7"/>
-      <c r="C10" s="7"/>
-      <c r="D10" s="7"/>
-      <c r="E10" s="7"/>
-      <c r="F10" s="7"/>
-      <c r="G10" s="7"/>
-      <c r="H10" s="7"/>
-      <c r="I10" s="7"/>
-      <c r="J10" s="7"/>
-      <c r="K10" s="7"/>
-      <c r="L10" s="7"/>
-      <c r="M10" s="7"/>
-      <c r="N10" s="7"/>
-      <c r="O10" s="7"/>
-    </row>
-    <row r="11" ht="20.05" customHeight="1">
-      <c r="A11" s="7"/>
-      <c r="B11" s="7"/>
-      <c r="C11" s="7"/>
-      <c r="D11" s="7"/>
-      <c r="E11" s="7"/>
-      <c r="F11" s="7"/>
-      <c r="G11" s="7"/>
-      <c r="H11" s="7"/>
-      <c r="I11" s="7"/>
-      <c r="J11" s="7"/>
-      <c r="K11" s="7"/>
-      <c r="L11" s="7"/>
-      <c r="M11" s="7"/>
-      <c r="N11" s="7"/>
-      <c r="O11" s="7"/>
-    </row>
-    <row r="12" ht="20.05" customHeight="1">
-      <c r="A12" s="7"/>
-      <c r="B12" s="7"/>
-      <c r="C12" s="7"/>
-      <c r="D12" s="7"/>
-      <c r="E12" s="7"/>
-      <c r="F12" s="7"/>
-      <c r="G12" s="7"/>
-      <c r="H12" s="7"/>
-      <c r="I12" s="7"/>
-      <c r="J12" s="7"/>
-      <c r="K12" s="7"/>
-      <c r="L12" s="7"/>
-      <c r="M12" s="7"/>
-      <c r="N12" s="7"/>
-      <c r="O12" s="7"/>
-    </row>
-    <row r="13" ht="20.05" customHeight="1">
-      <c r="A13" s="7"/>
-      <c r="B13" s="7"/>
-      <c r="C13" s="7"/>
-      <c r="D13" s="7"/>
-      <c r="E13" s="7"/>
-      <c r="F13" s="7"/>
-      <c r="G13" s="7"/>
-      <c r="H13" s="7"/>
-      <c r="I13" s="7"/>
-      <c r="J13" s="7"/>
-      <c r="K13" s="7"/>
-      <c r="L13" s="7"/>
-      <c r="M13" s="7"/>
-      <c r="N13" s="7"/>
-      <c r="O13" s="7"/>
-    </row>
-    <row r="14" ht="20.05" customHeight="1">
-      <c r="A14" s="7"/>
-      <c r="B14" s="7"/>
-      <c r="C14" s="7"/>
-      <c r="D14" s="7"/>
-      <c r="E14" s="7"/>
-      <c r="F14" s="7"/>
-      <c r="G14" s="7"/>
-      <c r="H14" s="7"/>
-      <c r="I14" s="7"/>
-      <c r="J14" s="7"/>
-      <c r="K14" s="7"/>
-      <c r="L14" s="7"/>
-      <c r="M14" s="7"/>
-      <c r="N14" s="7"/>
-      <c r="O14" s="7"/>
-    </row>
-    <row r="15" ht="20.05" customHeight="1">
-      <c r="A15" s="7"/>
-      <c r="B15" s="7"/>
-      <c r="C15" s="7"/>
-      <c r="D15" s="7"/>
-      <c r="E15" s="7"/>
-      <c r="F15" s="7"/>
-      <c r="G15" s="7"/>
-      <c r="H15" s="7"/>
-      <c r="I15" s="7"/>
-      <c r="J15" s="7"/>
-      <c r="K15" s="7"/>
-      <c r="L15" s="7"/>
-      <c r="M15" s="7"/>
-      <c r="N15" s="7"/>
-      <c r="O15" s="7"/>
-    </row>
-    <row r="16" ht="20.05" customHeight="1">
-      <c r="A16" s="7"/>
-      <c r="B16" s="7"/>
-      <c r="C16" s="7"/>
-      <c r="D16" s="7"/>
-      <c r="E16" s="7"/>
-      <c r="F16" s="7"/>
-      <c r="G16" s="7"/>
-      <c r="H16" s="7"/>
-      <c r="I16" s="7"/>
-      <c r="J16" s="7"/>
-      <c r="K16" s="7"/>
-      <c r="L16" s="7"/>
-      <c r="M16" s="7"/>
-      <c r="N16" s="7"/>
-      <c r="O16" s="7"/>
-    </row>
-    <row r="17" ht="20.05" customHeight="1">
-      <c r="A17" s="7"/>
-      <c r="B17" s="7"/>
-      <c r="C17" s="7"/>
-      <c r="D17" s="7"/>
-      <c r="E17" s="7"/>
-      <c r="F17" s="7"/>
-      <c r="G17" s="7"/>
-      <c r="H17" s="7"/>
-      <c r="I17" s="7"/>
-      <c r="J17" s="7"/>
-      <c r="K17" s="7"/>
-      <c r="L17" s="7"/>
-      <c r="M17" s="7"/>
-      <c r="N17" s="7"/>
-      <c r="O17" s="7"/>
-    </row>
-    <row r="18" ht="20.05" customHeight="1">
-      <c r="A18" s="7"/>
-      <c r="B18" s="7"/>
-      <c r="C18" s="7"/>
-      <c r="D18" s="7"/>
-      <c r="E18" s="7"/>
-      <c r="F18" s="7"/>
-      <c r="G18" s="7"/>
-      <c r="H18" s="7"/>
-      <c r="I18" s="7"/>
-      <c r="J18" s="7"/>
-      <c r="K18" s="7"/>
-      <c r="L18" s="7"/>
-      <c r="M18" s="7"/>
-      <c r="N18" s="7"/>
-      <c r="O18" s="7"/>
-    </row>
-    <row r="19" ht="20.05" customHeight="1">
-      <c r="A19" s="7"/>
-      <c r="B19" s="7"/>
-      <c r="C19" s="7"/>
-      <c r="D19" s="7"/>
-      <c r="E19" s="7"/>
-      <c r="F19" s="7"/>
-      <c r="G19" s="7"/>
-      <c r="H19" s="7"/>
-      <c r="I19" s="7"/>
-      <c r="J19" s="7"/>
-      <c r="K19" s="7"/>
-      <c r="L19" s="7"/>
-      <c r="M19" s="7"/>
-      <c r="N19" s="7"/>
-      <c r="O19" s="7"/>
-    </row>
-    <row r="20" ht="20.05" customHeight="1">
-      <c r="A20" s="7"/>
-      <c r="B20" s="7"/>
-      <c r="C20" s="7"/>
-      <c r="D20" s="7"/>
-      <c r="E20" s="7"/>
-      <c r="F20" s="7"/>
-      <c r="G20" s="7"/>
-      <c r="H20" s="7"/>
-      <c r="I20" s="7"/>
-      <c r="J20" s="7"/>
-      <c r="K20" s="7"/>
-      <c r="L20" s="7"/>
-      <c r="M20" s="7"/>
-      <c r="N20" s="7"/>
-      <c r="O20" s="7"/>
-    </row>
-    <row r="21" ht="20.05" customHeight="1">
-      <c r="A21" s="7"/>
-      <c r="B21" s="7"/>
-      <c r="C21" s="7"/>
-      <c r="D21" s="7"/>
-      <c r="E21" s="7"/>
-      <c r="F21" s="7"/>
-      <c r="G21" s="7"/>
-      <c r="H21" s="7"/>
-      <c r="I21" s="7"/>
-      <c r="J21" s="7"/>
-      <c r="K21" s="7"/>
-      <c r="L21" s="7"/>
-      <c r="M21" s="7"/>
-      <c r="N21" s="7"/>
-      <c r="O21" s="7"/>
-    </row>
-    <row r="22" ht="20.05" customHeight="1">
-      <c r="A22" s="7"/>
-      <c r="B22" s="7"/>
-      <c r="C22" s="7"/>
-      <c r="D22" s="7"/>
-      <c r="E22" s="7"/>
-      <c r="F22" s="7"/>
-      <c r="G22" s="7"/>
-      <c r="H22" s="7"/>
-      <c r="I22" s="7"/>
-      <c r="J22" s="7"/>
-      <c r="K22" s="7"/>
-      <c r="L22" s="7"/>
-      <c r="M22" s="7"/>
-      <c r="N22" s="7"/>
-      <c r="O22" s="7"/>
+    <row r="1" ht="60.55" customHeight="1" s="8">
+      <c r="A1" s="9" t="inlineStr">
+        <is>
+          <t>Isolate ID</t>
+        </is>
+      </c>
+      <c r="B1" s="9" t="inlineStr">
+        <is>
+          <t>Quality Status</t>
+        </is>
+      </c>
+      <c r="C1" s="9" t="inlineStr">
+        <is>
+          <t>Genotype</t>
+        </is>
+      </c>
+      <c r="D1" s="9" t="inlineStr">
+        <is>
+          <t>Predicted Phenotype</t>
+        </is>
+      </c>
+      <c r="E1" s="9" t="inlineStr">
+        <is>
+          <t>SIR Profile</t>
+        </is>
+      </c>
+      <c r="F1" s="9" t="inlineStr">
+        <is>
+          <t>Plasmid</t>
+        </is>
+      </c>
+      <c r="G1" s="9" t="inlineStr">
+        <is>
+          <t>Genome Length</t>
+        </is>
+      </c>
+      <c r="H1" s="9" t="inlineStr">
+        <is>
+          <t>N50 Value</t>
+        </is>
+      </c>
+      <c r="I1" s="3" t="n"/>
+      <c r="J1" s="3" t="n"/>
+      <c r="K1" s="3" t="n"/>
+      <c r="L1" s="3" t="n"/>
+      <c r="M1" s="3" t="n"/>
+      <c r="N1" s="3" t="n"/>
+      <c r="O1" s="3" t="n"/>
+    </row>
+    <row r="2" ht="74.55" customHeight="1" s="8">
+      <c r="A2" t="inlineStr">
+        <is>
+          <t>ISO-101</t>
+        </is>
+      </c>
+      <c r="B2" t="inlineStr">
+        <is>
+          <t>Passed</t>
+        </is>
+      </c>
+      <c r="C2" t="inlineStr">
+        <is>
+          <t>aph(3')-Ia</t>
+        </is>
+      </c>
+      <c r="D2" t="inlineStr">
+        <is>
+          <t>ciprofloxacin, ceftriaxone</t>
+        </is>
+      </c>
+      <c r="E2" t="inlineStr">
+        <is>
+          <t>Resistant</t>
+        </is>
+      </c>
+      <c r="F2" t="inlineStr">
+        <is>
+          <t>IncL/M</t>
+        </is>
+      </c>
+      <c r="G2" t="n">
+        <v>6652054</v>
+      </c>
+      <c r="H2" t="n">
+        <v>467886</v>
+      </c>
+    </row>
+    <row r="3" ht="46.35" customHeight="1" s="8">
+      <c r="A3" t="inlineStr">
+        <is>
+          <t>ISO-102</t>
+        </is>
+      </c>
+      <c r="B3" t="inlineStr">
+        <is>
+          <t>Passed</t>
+        </is>
+      </c>
+      <c r="C3" t="inlineStr">
+        <is>
+          <t>aph(3')-Ia</t>
+        </is>
+      </c>
+      <c r="D3" t="inlineStr">
+        <is>
+          <t>cefotaxime, erythromycin, florfenicol</t>
+        </is>
+      </c>
+      <c r="E3" t="inlineStr">
+        <is>
+          <t>Resistant</t>
+        </is>
+      </c>
+      <c r="F3" t="inlineStr">
+        <is>
+          <t>IncFIA</t>
+        </is>
+      </c>
+      <c r="G3" t="n">
+        <v>5406711</v>
+      </c>
+      <c r="H3" t="n">
+        <v>94870</v>
+      </c>
+    </row>
+    <row r="4" ht="60.35" customHeight="1" s="8">
+      <c r="A4" t="inlineStr">
+        <is>
+          <t>ISO-103</t>
+        </is>
+      </c>
+      <c r="B4" t="inlineStr">
+        <is>
+          <t>Passed</t>
+        </is>
+      </c>
+      <c r="C4" t="inlineStr">
+        <is>
+          <t>blaTEM-1</t>
+        </is>
+      </c>
+      <c r="D4" t="inlineStr">
+        <is>
+          <t>tetracycline, gentamicin, imipenem</t>
+        </is>
+      </c>
+      <c r="E4" t="inlineStr">
+        <is>
+          <t>Resistant</t>
+        </is>
+      </c>
+      <c r="F4" t="inlineStr">
+        <is>
+          <t>IncX3</t>
+        </is>
+      </c>
+      <c r="G4" t="n">
+        <v>4086939</v>
+      </c>
+      <c r="H4" t="n">
+        <v>557478</v>
+      </c>
+    </row>
+    <row r="5" ht="46.35" customHeight="1" s="8">
+      <c r="A5" t="inlineStr">
+        <is>
+          <t>ISO-104</t>
+        </is>
+      </c>
+      <c r="B5" t="inlineStr">
+        <is>
+          <t>Failed</t>
+        </is>
+      </c>
+      <c r="C5" t="inlineStr">
+        <is>
+          <t>aph(3')-Ia, catA1, floR, blaOXA-48, dfrA1</t>
+        </is>
+      </c>
+      <c r="D5" t="inlineStr">
+        <is>
+          <t>ertapenem, vancomycin, imipenem</t>
+        </is>
+      </c>
+      <c r="E5" t="inlineStr">
+        <is>
+          <t>Susceptible</t>
+        </is>
+      </c>
+      <c r="F5" t="inlineStr">
+        <is>
+          <t>IncFIC(FII)</t>
+        </is>
+      </c>
+      <c r="G5" t="n">
+        <v>4711190</v>
+      </c>
+      <c r="H5" t="n">
+        <v>92098</v>
+      </c>
+    </row>
+    <row r="6" ht="20.05" customHeight="1" s="8">
+      <c r="A6" t="inlineStr">
+        <is>
+          <t>ISO-105</t>
+        </is>
+      </c>
+      <c r="B6" t="inlineStr">
+        <is>
+          <t>Passed</t>
+        </is>
+      </c>
+      <c r="C6" t="inlineStr">
+        <is>
+          <t>blaSHV-11</t>
+        </is>
+      </c>
+      <c r="D6" t="inlineStr">
+        <is>
+          <t>trimethoprim-sulfamethoxazole</t>
+        </is>
+      </c>
+      <c r="E6" t="inlineStr">
+        <is>
+          <t>Intermediate</t>
+        </is>
+      </c>
+      <c r="F6" t="inlineStr">
+        <is>
+          <t>IncP1</t>
+        </is>
+      </c>
+      <c r="G6" t="n">
+        <v>5119123</v>
+      </c>
+      <c r="H6" t="n">
+        <v>147822</v>
+      </c>
+    </row>
+    <row r="7" ht="20.05" customHeight="1" s="8">
+      <c r="A7" t="inlineStr">
+        <is>
+          <t>ISO-106</t>
+        </is>
+      </c>
+      <c r="B7" t="inlineStr">
+        <is>
+          <t>Passed</t>
+        </is>
+      </c>
+      <c r="C7" t="inlineStr">
+        <is>
+          <t>tet(B), floR</t>
+        </is>
+      </c>
+      <c r="D7" t="inlineStr">
+        <is>
+          <t>kanamycin</t>
+        </is>
+      </c>
+      <c r="E7" t="inlineStr">
+        <is>
+          <t>Susceptible</t>
+        </is>
+      </c>
+      <c r="F7" t="inlineStr">
+        <is>
+          <t>IncB/O/K/Z</t>
+        </is>
+      </c>
+      <c r="G7" t="n">
+        <v>4995044</v>
+      </c>
+      <c r="H7" t="n">
+        <v>29327</v>
+      </c>
+    </row>
+    <row r="8" ht="20.05" customHeight="1" s="8">
+      <c r="A8" t="inlineStr">
+        <is>
+          <t>ISO-107</t>
+        </is>
+      </c>
+      <c r="B8" t="inlineStr">
+        <is>
+          <t>Passed</t>
+        </is>
+      </c>
+      <c r="C8" t="inlineStr">
+        <is>
+          <t>blaNDM-1, qnrB2, catA1</t>
+        </is>
+      </c>
+      <c r="D8" t="inlineStr">
+        <is>
+          <t>doxycycline, gentamicin</t>
+        </is>
+      </c>
+      <c r="E8" t="inlineStr">
+        <is>
+          <t>Resistant</t>
+        </is>
+      </c>
+      <c r="F8" t="inlineStr">
+        <is>
+          <t>IncHI2</t>
+        </is>
+      </c>
+      <c r="G8" t="n">
+        <v>5418521</v>
+      </c>
+      <c r="H8" t="n">
+        <v>119420</v>
+      </c>
+    </row>
+    <row r="9" ht="20.05" customHeight="1" s="8">
+      <c r="A9" t="inlineStr">
+        <is>
+          <t>ISO-108</t>
+        </is>
+      </c>
+      <c r="B9" t="inlineStr">
+        <is>
+          <t>Failed</t>
+        </is>
+      </c>
+      <c r="C9" t="inlineStr">
+        <is>
+          <t>qnrS1, floR</t>
+        </is>
+      </c>
+      <c r="D9" t="inlineStr">
+        <is>
+          <t>levofloxacin</t>
+        </is>
+      </c>
+      <c r="E9" t="inlineStr">
+        <is>
+          <t>Resistant</t>
+        </is>
+      </c>
+      <c r="F9" t="inlineStr">
+        <is>
+          <t>IncQ1</t>
+        </is>
+      </c>
+      <c r="G9" t="n">
+        <v>5127382</v>
+      </c>
+      <c r="H9" t="n">
+        <v>139594</v>
+      </c>
+    </row>
+    <row r="10" ht="20.05" customHeight="1" s="8">
+      <c r="A10" t="inlineStr">
+        <is>
+          <t>ISO-109</t>
+        </is>
+      </c>
+      <c r="B10" t="inlineStr">
+        <is>
+          <t>Passed</t>
+        </is>
+      </c>
+      <c r="C10" t="inlineStr">
+        <is>
+          <t>vanA, sul2, ermC, mcr-1</t>
+        </is>
+      </c>
+      <c r="D10" t="inlineStr">
+        <is>
+          <t>ciprofloxacin, ceftriaxone</t>
+        </is>
+      </c>
+      <c r="E10" t="inlineStr">
+        <is>
+          <t>Resistant</t>
+        </is>
+      </c>
+      <c r="F10" t="inlineStr">
+        <is>
+          <t>IncFIB(K)</t>
+        </is>
+      </c>
+      <c r="G10" t="n">
+        <v>4899684</v>
+      </c>
+      <c r="H10" t="n">
+        <v>227422</v>
+      </c>
+    </row>
+    <row r="11" ht="20.05" customHeight="1" s="8">
+      <c r="A11" t="inlineStr">
+        <is>
+          <t>ISO-110</t>
+        </is>
+      </c>
+      <c r="B11" t="inlineStr">
+        <is>
+          <t>Passed</t>
+        </is>
+      </c>
+      <c r="C11" t="inlineStr">
+        <is>
+          <t>blaCTX-M-14</t>
+        </is>
+      </c>
+      <c r="D11" t="inlineStr">
+        <is>
+          <t>levofloxacin, gentamicin, vancomycin, florfenicol</t>
+        </is>
+      </c>
+      <c r="E11" t="inlineStr">
+        <is>
+          <t>Intermediate</t>
+        </is>
+      </c>
+      <c r="F11" t="inlineStr">
+        <is>
+          <t>IncP1</t>
+        </is>
+      </c>
+      <c r="G11" t="n">
+        <v>6743607</v>
+      </c>
+      <c r="H11" t="n">
+        <v>423018</v>
+      </c>
+    </row>
+    <row r="12" ht="20.05" customHeight="1" s="8">
+      <c r="A12" t="inlineStr">
+        <is>
+          <t>ISO-111</t>
+        </is>
+      </c>
+      <c r="B12" t="inlineStr">
+        <is>
+          <t>Passed</t>
+        </is>
+      </c>
+      <c r="C12" t="inlineStr">
+        <is>
+          <t>floR</t>
+        </is>
+      </c>
+      <c r="D12" t="inlineStr">
+        <is>
+          <t>amikacin, ceftriaxone</t>
+        </is>
+      </c>
+      <c r="E12" t="inlineStr">
+        <is>
+          <t>Susceptible</t>
+        </is>
+      </c>
+      <c r="F12" t="inlineStr">
+        <is>
+          <t>IncHI1</t>
+        </is>
+      </c>
+      <c r="G12" t="n">
+        <v>7189249</v>
+      </c>
+      <c r="H12" t="n">
+        <v>164124</v>
+      </c>
+    </row>
+    <row r="13" ht="20.05" customHeight="1" s="8">
+      <c r="A13" t="inlineStr">
+        <is>
+          <t>ISO-112</t>
+        </is>
+      </c>
+      <c r="B13" t="inlineStr">
+        <is>
+          <t>Passed</t>
+        </is>
+      </c>
+      <c r="C13" t="inlineStr">
+        <is>
+          <t>ermB, sul1, vanA, floR, aph(6)-Id</t>
+        </is>
+      </c>
+      <c r="D13" t="inlineStr">
+        <is>
+          <t>gentamicin</t>
+        </is>
+      </c>
+      <c r="E13" t="inlineStr">
+        <is>
+          <t>Susceptible</t>
+        </is>
+      </c>
+      <c r="F13" t="inlineStr">
+        <is>
+          <t>IncFIA</t>
+        </is>
+      </c>
+      <c r="G13" t="n">
+        <v>4042875</v>
+      </c>
+      <c r="H13" t="n">
+        <v>257555</v>
+      </c>
+    </row>
+    <row r="14" ht="20.05" customHeight="1" s="8">
+      <c r="A14" t="inlineStr">
+        <is>
+          <t>ISO-113</t>
+        </is>
+      </c>
+      <c r="B14" t="inlineStr">
+        <is>
+          <t>Passed</t>
+        </is>
+      </c>
+      <c r="C14" t="inlineStr">
+        <is>
+          <t>sul2</t>
+        </is>
+      </c>
+      <c r="D14" t="inlineStr">
+        <is>
+          <t>azithromycin</t>
+        </is>
+      </c>
+      <c r="E14" t="inlineStr">
+        <is>
+          <t>Resistant</t>
+        </is>
+      </c>
+      <c r="F14" t="inlineStr">
+        <is>
+          <t>p0111</t>
+        </is>
+      </c>
+      <c r="G14" t="n">
+        <v>6593740</v>
+      </c>
+      <c r="H14" t="n">
+        <v>185378</v>
+      </c>
+    </row>
+    <row r="15" ht="20.05" customHeight="1" s="8">
+      <c r="A15" t="inlineStr">
+        <is>
+          <t>ISO-114</t>
+        </is>
+      </c>
+      <c r="B15" t="inlineStr">
+        <is>
+          <t>Passed</t>
+        </is>
+      </c>
+      <c r="C15" t="inlineStr">
+        <is>
+          <t>aph(3')-Ia</t>
+        </is>
+      </c>
+      <c r="D15" t="inlineStr">
+        <is>
+          <t>florfenicol, ampicillin</t>
+        </is>
+      </c>
+      <c r="E15" t="inlineStr">
+        <is>
+          <t>Intermediate</t>
+        </is>
+      </c>
+      <c r="F15" t="inlineStr">
+        <is>
+          <t>IncL/M</t>
+        </is>
+      </c>
+      <c r="G15" t="n">
+        <v>5969389</v>
+      </c>
+      <c r="H15" t="n">
+        <v>273040</v>
+      </c>
+    </row>
+    <row r="16" ht="20.05" customHeight="1" s="8">
+      <c r="A16" t="inlineStr">
+        <is>
+          <t>ISO-115</t>
+        </is>
+      </c>
+      <c r="B16" t="inlineStr">
+        <is>
+          <t>Failed</t>
+        </is>
+      </c>
+      <c r="C16" t="inlineStr">
+        <is>
+          <t>ermC, blaSHV-11</t>
+        </is>
+      </c>
+      <c r="D16" t="inlineStr">
+        <is>
+          <t>cefotaxime, ampicillin, streptomycin</t>
+        </is>
+      </c>
+      <c r="E16" t="inlineStr">
+        <is>
+          <t>Intermediate</t>
+        </is>
+      </c>
+      <c r="F16" t="inlineStr">
+        <is>
+          <t>IncL/M</t>
+        </is>
+      </c>
+      <c r="G16" t="n">
+        <v>4067898</v>
+      </c>
+      <c r="H16" t="n">
+        <v>276922</v>
+      </c>
+    </row>
+    <row r="17" ht="20.05" customHeight="1" s="8">
+      <c r="A17" t="inlineStr">
+        <is>
+          <t>ISO-116</t>
+        </is>
+      </c>
+      <c r="B17" t="inlineStr">
+        <is>
+          <t>Passed</t>
+        </is>
+      </c>
+      <c r="C17" t="inlineStr">
+        <is>
+          <t>floR, blaCTX-M-15, qnrS1, dfrA1, qnrB2</t>
+        </is>
+      </c>
+      <c r="D17" t="inlineStr">
+        <is>
+          <t>amoxicillin-clavulanate, ciprofloxacin, trimethoprim-sulfamethoxazole</t>
+        </is>
+      </c>
+      <c r="E17" t="inlineStr">
+        <is>
+          <t>Resistant</t>
+        </is>
+      </c>
+      <c r="F17" t="inlineStr">
+        <is>
+          <t>IncFIB(AP001918)</t>
+        </is>
+      </c>
+      <c r="G17" t="n">
+        <v>7043576</v>
+      </c>
+      <c r="H17" t="n">
+        <v>109103</v>
+      </c>
+    </row>
+    <row r="18" ht="20.05" customHeight="1" s="8">
+      <c r="A18" t="inlineStr">
+        <is>
+          <t>ISO-117</t>
+        </is>
+      </c>
+      <c r="B18" t="inlineStr">
+        <is>
+          <t>Failed</t>
+        </is>
+      </c>
+      <c r="C18" t="inlineStr">
+        <is>
+          <t>aadA1, aac(6')-Ib-cr, blaTEM-1, tet(A), qnrB2</t>
+        </is>
+      </c>
+      <c r="D18" t="inlineStr">
+        <is>
+          <t>amoxicillin-clavulanate</t>
+        </is>
+      </c>
+      <c r="E18" t="inlineStr">
+        <is>
+          <t>Resistant</t>
+        </is>
+      </c>
+      <c r="F18" t="inlineStr">
+        <is>
+          <t>IncFIA</t>
+        </is>
+      </c>
+      <c r="G18" t="n">
+        <v>3992860</v>
+      </c>
+      <c r="H18" t="n">
+        <v>495881</v>
+      </c>
+    </row>
+    <row r="19" ht="20.05" customHeight="1" s="8">
+      <c r="A19" t="inlineStr">
+        <is>
+          <t>ISO-118</t>
+        </is>
+      </c>
+      <c r="B19" t="inlineStr">
+        <is>
+          <t>Failed</t>
+        </is>
+      </c>
+      <c r="C19" t="inlineStr">
+        <is>
+          <t>sul1, blaSHV-11, blaOXA-48</t>
+        </is>
+      </c>
+      <c r="D19" t="inlineStr">
+        <is>
+          <t>trimethoprim</t>
+        </is>
+      </c>
+      <c r="E19" t="inlineStr">
+        <is>
+          <t>Susceptible</t>
+        </is>
+      </c>
+      <c r="F19" t="inlineStr">
+        <is>
+          <t>IncP1</t>
+        </is>
+      </c>
+      <c r="G19" t="n">
+        <v>4741685</v>
+      </c>
+      <c r="H19" t="n">
+        <v>338633</v>
+      </c>
+    </row>
+    <row r="20" ht="20.05" customHeight="1" s="8">
+      <c r="A20" t="inlineStr">
+        <is>
+          <t>ISO-119</t>
+        </is>
+      </c>
+      <c r="B20" t="inlineStr">
+        <is>
+          <t>Passed</t>
+        </is>
+      </c>
+      <c r="C20" t="inlineStr">
+        <is>
+          <t>sul2, aac(6')-Ib-cr</t>
+        </is>
+      </c>
+      <c r="D20" t="inlineStr">
+        <is>
+          <t>amikacin, ceftriaxone, trimethoprim-sulfamethoxazole</t>
+        </is>
+      </c>
+      <c r="E20" t="inlineStr">
+        <is>
+          <t>Susceptible</t>
+        </is>
+      </c>
+      <c r="F20" t="inlineStr">
+        <is>
+          <t>Col(BS512)</t>
+        </is>
+      </c>
+      <c r="G20" t="n">
+        <v>4552224</v>
+      </c>
+      <c r="H20" t="n">
+        <v>235226</v>
+      </c>
+    </row>
+    <row r="21" ht="20.05" customHeight="1" s="8">
+      <c r="A21" t="inlineStr">
+        <is>
+          <t>ISO-120</t>
+        </is>
+      </c>
+      <c r="B21" t="inlineStr">
+        <is>
+          <t>Passed</t>
+        </is>
+      </c>
+      <c r="C21" t="inlineStr">
+        <is>
+          <t>blaCTX-M-14, sul1, blaCTX-M-15, dfrA1, tet(M)</t>
+        </is>
+      </c>
+      <c r="D21" t="inlineStr">
+        <is>
+          <t>streptomycin, ceftriaxone, trimethoprim</t>
+        </is>
+      </c>
+      <c r="E21" t="inlineStr">
+        <is>
+          <t>Intermediate</t>
+        </is>
+      </c>
+      <c r="F21" t="inlineStr">
+        <is>
+          <t>IncHI1</t>
+        </is>
+      </c>
+      <c r="G21" t="n">
+        <v>5023038</v>
+      </c>
+      <c r="H21" t="n">
+        <v>592394</v>
+      </c>
+    </row>
+    <row r="22" ht="20.05" customHeight="1" s="8">
+      <c r="A22" t="inlineStr">
+        <is>
+          <t>ISO-121</t>
+        </is>
+      </c>
+      <c r="B22" t="inlineStr">
+        <is>
+          <t>Passed</t>
+        </is>
+      </c>
+      <c r="C22" t="inlineStr">
+        <is>
+          <t>aac(6')-Ib-cr, catA1, tet(A)</t>
+        </is>
+      </c>
+      <c r="D22" t="inlineStr">
+        <is>
+          <t>tetracycline, trimethoprim-sulfamethoxazole, ciprofloxacin, ertapenem</t>
+        </is>
+      </c>
+      <c r="E22" t="inlineStr">
+        <is>
+          <t>Susceptible</t>
+        </is>
+      </c>
+      <c r="F22" t="inlineStr">
+        <is>
+          <t>IncFIA</t>
+        </is>
+      </c>
+      <c r="G22" t="n">
+        <v>4431521</v>
+      </c>
+      <c r="H22" t="n">
+        <v>7887</v>
+      </c>
+    </row>
+    <row r="23">
+      <c r="A23" t="inlineStr">
+        <is>
+          <t>ISO-122</t>
+        </is>
+      </c>
+      <c r="B23" t="inlineStr">
+        <is>
+          <t>Passed</t>
+        </is>
+      </c>
+      <c r="C23" t="inlineStr">
+        <is>
+          <t>aph(3')-Ia, tet(A), mcr-1, ermC</t>
+        </is>
+      </c>
+      <c r="D23" t="inlineStr">
+        <is>
+          <t>streptomycin</t>
+        </is>
+      </c>
+      <c r="E23" t="inlineStr">
+        <is>
+          <t>Susceptible</t>
+        </is>
+      </c>
+      <c r="F23" t="inlineStr">
+        <is>
+          <t>IncW</t>
+        </is>
+      </c>
+      <c r="G23" t="n">
+        <v>6895743</v>
+      </c>
+      <c r="H23" t="n">
+        <v>323648</v>
+      </c>
+    </row>
+    <row r="24">
+      <c r="A24" t="inlineStr">
+        <is>
+          <t>ISO-123</t>
+        </is>
+      </c>
+      <c r="B24" t="inlineStr">
+        <is>
+          <t>Failed</t>
+        </is>
+      </c>
+      <c r="C24" t="inlineStr">
+        <is>
+          <t>blaNDM-1</t>
+        </is>
+      </c>
+      <c r="D24" t="inlineStr">
+        <is>
+          <t>erythromycin, ciprofloxacin</t>
+        </is>
+      </c>
+      <c r="E24" t="inlineStr">
+        <is>
+          <t>Resistant</t>
+        </is>
+      </c>
+      <c r="F24" t="inlineStr">
+        <is>
+          <t>IncFIB(AP001918)</t>
+        </is>
+      </c>
+      <c r="G24" t="n">
+        <v>4190182</v>
+      </c>
+      <c r="H24" t="n">
+        <v>47232</v>
+      </c>
+    </row>
+    <row r="25">
+      <c r="A25" t="inlineStr">
+        <is>
+          <t>ISO-124</t>
+        </is>
+      </c>
+      <c r="B25" t="inlineStr">
+        <is>
+          <t>Passed</t>
+        </is>
+      </c>
+      <c r="C25" t="inlineStr">
+        <is>
+          <t>qnrB2, sul2</t>
+        </is>
+      </c>
+      <c r="D25" t="inlineStr">
+        <is>
+          <t>azithromycin, ceftriaxone, trimethoprim-sulfamethoxazole</t>
+        </is>
+      </c>
+      <c r="E25" t="inlineStr">
+        <is>
+          <t>Resistant</t>
+        </is>
+      </c>
+      <c r="F25" t="inlineStr">
+        <is>
+          <t>IncW</t>
+        </is>
+      </c>
+      <c r="G25" t="n">
+        <v>4113861</v>
+      </c>
+      <c r="H25" t="n">
+        <v>621847</v>
+      </c>
+    </row>
+    <row r="26">
+      <c r="A26" t="inlineStr">
+        <is>
+          <t>ISO-125</t>
+        </is>
+      </c>
+      <c r="B26" t="inlineStr">
+        <is>
+          <t>Passed</t>
+        </is>
+      </c>
+      <c r="C26" t="inlineStr">
+        <is>
+          <t>blaCTX-M-14, sul2, aadA1, blaSHV-11, tet(A)</t>
+        </is>
+      </c>
+      <c r="D26" t="inlineStr">
+        <is>
+          <t>amikacin, streptomycin, doxycycline</t>
+        </is>
+      </c>
+      <c r="E26" t="inlineStr">
+        <is>
+          <t>Susceptible</t>
+        </is>
+      </c>
+      <c r="F26" t="inlineStr">
+        <is>
+          <t>ColRNAI</t>
+        </is>
+      </c>
+      <c r="G26" t="n">
+        <v>5134030</v>
+      </c>
+      <c r="H26" t="n">
+        <v>475951</v>
+      </c>
+    </row>
+    <row r="27">
+      <c r="A27" t="inlineStr">
+        <is>
+          <t>ISO-126</t>
+        </is>
+      </c>
+      <c r="B27" t="inlineStr">
+        <is>
+          <t>Passed</t>
+        </is>
+      </c>
+      <c r="C27" t="inlineStr">
+        <is>
+          <t>tet(A), blaCTX-M-15, blaNDM-1</t>
+        </is>
+      </c>
+      <c r="D27" t="inlineStr">
+        <is>
+          <t>trimethoprim-sulfamethoxazole, cefotaxime</t>
+        </is>
+      </c>
+      <c r="E27" t="inlineStr">
+        <is>
+          <t>Resistant</t>
+        </is>
+      </c>
+      <c r="F27" t="inlineStr">
+        <is>
+          <t>IncFIC(FII)</t>
+        </is>
+      </c>
+      <c r="G27" t="n">
+        <v>5754776</v>
+      </c>
+      <c r="H27" t="n">
+        <v>330487</v>
+      </c>
+    </row>
+    <row r="28">
+      <c r="A28" t="inlineStr">
+        <is>
+          <t>ISO-127</t>
+        </is>
+      </c>
+      <c r="B28" t="inlineStr">
+        <is>
+          <t>Passed</t>
+        </is>
+      </c>
+      <c r="C28" t="inlineStr">
+        <is>
+          <t>blaTEM-1, mcr-1, ermC, aph(6)-Id</t>
+        </is>
+      </c>
+      <c r="D28" t="inlineStr">
+        <is>
+          <t>azithromycin, gentamicin</t>
+        </is>
+      </c>
+      <c r="E28" t="inlineStr">
+        <is>
+          <t>Resistant</t>
+        </is>
+      </c>
+      <c r="F28" t="inlineStr">
+        <is>
+          <t>IncFII</t>
+        </is>
+      </c>
+      <c r="G28" t="n">
+        <v>4461086</v>
+      </c>
+      <c r="H28" t="n">
+        <v>320192</v>
+      </c>
+    </row>
+    <row r="29">
+      <c r="A29" t="inlineStr">
+        <is>
+          <t>ISO-128</t>
+        </is>
+      </c>
+      <c r="B29" t="inlineStr">
+        <is>
+          <t>Passed</t>
+        </is>
+      </c>
+      <c r="C29" t="inlineStr">
+        <is>
+          <t>blaCTX-M-14, blaNDM-1, ermB, blaSHV-11, blaCTX-M-15</t>
+        </is>
+      </c>
+      <c r="D29" t="inlineStr">
+        <is>
+          <t>tetracycline, doxycycline</t>
+        </is>
+      </c>
+      <c r="E29" t="inlineStr">
+        <is>
+          <t>Susceptible</t>
+        </is>
+      </c>
+      <c r="F29" t="inlineStr">
+        <is>
+          <t>p0111</t>
+        </is>
+      </c>
+      <c r="G29" t="n">
+        <v>4891218</v>
+      </c>
+      <c r="H29" t="n">
+        <v>183513</v>
+      </c>
+    </row>
+    <row r="30">
+      <c r="A30" t="inlineStr">
+        <is>
+          <t>ISO-129</t>
+        </is>
+      </c>
+      <c r="B30" t="inlineStr">
+        <is>
+          <t>Passed</t>
+        </is>
+      </c>
+      <c r="C30" t="inlineStr">
+        <is>
+          <t>sul1</t>
+        </is>
+      </c>
+      <c r="D30" t="inlineStr">
+        <is>
+          <t>trimethoprim, kanamycin, cefotaxime, azithromycin</t>
+        </is>
+      </c>
+      <c r="E30" t="inlineStr">
+        <is>
+          <t>Resistant</t>
+        </is>
+      </c>
+      <c r="F30" t="inlineStr">
+        <is>
+          <t>IncI1</t>
+        </is>
+      </c>
+      <c r="G30" t="n">
+        <v>3850150</v>
+      </c>
+      <c r="H30" t="n">
+        <v>65864</v>
+      </c>
+    </row>
+    <row r="31">
+      <c r="A31" t="inlineStr">
+        <is>
+          <t>ISO-130</t>
+        </is>
+      </c>
+      <c r="B31" t="inlineStr">
+        <is>
+          <t>Passed</t>
+        </is>
+      </c>
+      <c r="C31" t="inlineStr">
+        <is>
+          <t>blaSHV-11, blaNDM-1</t>
+        </is>
+      </c>
+      <c r="D31" t="inlineStr">
+        <is>
+          <t>tetracycline, chloramphenicol, vancomycin, ceftriaxone</t>
+        </is>
+      </c>
+      <c r="E31" t="inlineStr">
+        <is>
+          <t>Intermediate</t>
+        </is>
+      </c>
+      <c r="F31" t="inlineStr">
+        <is>
+          <t>IncFII</t>
+        </is>
+      </c>
+      <c r="G31" t="n">
+        <v>3891436</v>
+      </c>
+      <c r="H31" t="n">
+        <v>68803</v>
+      </c>
+    </row>
+    <row r="32">
+      <c r="A32" t="inlineStr">
+        <is>
+          <t>ISO-131</t>
+        </is>
+      </c>
+      <c r="B32" t="inlineStr">
+        <is>
+          <t>Passed</t>
+        </is>
+      </c>
+      <c r="C32" t="inlineStr">
+        <is>
+          <t>floR, dfrA1</t>
+        </is>
+      </c>
+      <c r="D32" t="inlineStr">
+        <is>
+          <t>ceftriaxone, streptomycin</t>
+        </is>
+      </c>
+      <c r="E32" t="inlineStr">
+        <is>
+          <t>Intermediate</t>
+        </is>
+      </c>
+      <c r="F32" t="inlineStr">
+        <is>
+          <t>Col(BS512)</t>
+        </is>
+      </c>
+      <c r="G32" t="n">
+        <v>4504597</v>
+      </c>
+      <c r="H32" t="n">
+        <v>602961</v>
+      </c>
+    </row>
+    <row r="33">
+      <c r="A33" t="inlineStr">
+        <is>
+          <t>ISO-132</t>
+        </is>
+      </c>
+      <c r="B33" t="inlineStr">
+        <is>
+          <t>Passed</t>
+        </is>
+      </c>
+      <c r="C33" t="inlineStr">
+        <is>
+          <t>aac(6')-Ib-cr, sul1, qnrS1, aph(3')-Ia</t>
+        </is>
+      </c>
+      <c r="D33" t="inlineStr">
+        <is>
+          <t>chloramphenicol, erythromycin, meropenem, tetracycline</t>
+        </is>
+      </c>
+      <c r="E33" t="inlineStr">
+        <is>
+          <t>Resistant</t>
+        </is>
+      </c>
+      <c r="F33" t="inlineStr">
+        <is>
+          <t>IncFIB(AP001918)</t>
+        </is>
+      </c>
+      <c r="G33" t="n">
+        <v>4973795</v>
+      </c>
+      <c r="H33" t="n">
+        <v>468876</v>
+      </c>
+    </row>
+    <row r="34">
+      <c r="A34" t="inlineStr">
+        <is>
+          <t>ISO-133</t>
+        </is>
+      </c>
+      <c r="B34" t="inlineStr">
+        <is>
+          <t>Passed</t>
+        </is>
+      </c>
+      <c r="C34" t="inlineStr">
+        <is>
+          <t>blaCTX-M-14, catA1</t>
+        </is>
+      </c>
+      <c r="D34" t="inlineStr">
+        <is>
+          <t>vancomycin, gentamicin</t>
+        </is>
+      </c>
+      <c r="E34" t="inlineStr">
+        <is>
+          <t>Susceptible</t>
+        </is>
+      </c>
+      <c r="F34" t="inlineStr">
+        <is>
+          <t>IncHI2</t>
+        </is>
+      </c>
+      <c r="G34" t="n">
+        <v>4055764</v>
+      </c>
+      <c r="H34" t="n">
+        <v>93182</v>
+      </c>
+    </row>
+    <row r="35">
+      <c r="A35" t="inlineStr">
+        <is>
+          <t>ISO-134</t>
+        </is>
+      </c>
+      <c r="B35" t="inlineStr">
+        <is>
+          <t>Passed</t>
+        </is>
+      </c>
+      <c r="C35" t="inlineStr">
+        <is>
+          <t>sul1, blaSHV-11, sul2</t>
+        </is>
+      </c>
+      <c r="D35" t="inlineStr">
+        <is>
+          <t>vancomycin, levofloxacin</t>
+        </is>
+      </c>
+      <c r="E35" t="inlineStr">
+        <is>
+          <t>Susceptible</t>
+        </is>
+      </c>
+      <c r="F35" t="inlineStr">
+        <is>
+          <t>IncFIB(K)</t>
+        </is>
+      </c>
+      <c r="G35" t="n">
+        <v>5404313</v>
+      </c>
+      <c r="H35" t="n">
+        <v>377756</v>
+      </c>
+    </row>
+    <row r="36">
+      <c r="A36" t="inlineStr">
+        <is>
+          <t>ISO-135</t>
+        </is>
+      </c>
+      <c r="B36" t="inlineStr">
+        <is>
+          <t>Passed</t>
+        </is>
+      </c>
+      <c r="C36" t="inlineStr">
+        <is>
+          <t>mcr-1, qnrS1, ermC, vanA</t>
+        </is>
+      </c>
+      <c r="D36" t="inlineStr">
+        <is>
+          <t>doxycycline, amikacin, meropenem</t>
+        </is>
+      </c>
+      <c r="E36" t="inlineStr">
+        <is>
+          <t>Susceptible</t>
+        </is>
+      </c>
+      <c r="F36" t="inlineStr">
+        <is>
+          <t>IncFIA</t>
+        </is>
+      </c>
+      <c r="G36" t="n">
+        <v>3922907</v>
+      </c>
+      <c r="H36" t="n">
+        <v>295779</v>
+      </c>
+    </row>
+    <row r="37">
+      <c r="A37" t="inlineStr">
+        <is>
+          <t>ISO-136</t>
+        </is>
+      </c>
+      <c r="B37" t="inlineStr">
+        <is>
+          <t>Passed</t>
+        </is>
+      </c>
+      <c r="C37" t="inlineStr">
+        <is>
+          <t>qnrS1</t>
+        </is>
+      </c>
+      <c r="D37" t="inlineStr">
+        <is>
+          <t>trimethoprim-sulfamethoxazole, kanamycin, meropenem</t>
+        </is>
+      </c>
+      <c r="E37" t="inlineStr">
+        <is>
+          <t>Susceptible</t>
+        </is>
+      </c>
+      <c r="F37" t="inlineStr">
+        <is>
+          <t>IncFIA</t>
+        </is>
+      </c>
+      <c r="G37" t="n">
+        <v>4917895</v>
+      </c>
+      <c r="H37" t="n">
+        <v>560814</v>
+      </c>
+    </row>
+    <row r="38">
+      <c r="A38" t="inlineStr">
+        <is>
+          <t>ISO-137</t>
+        </is>
+      </c>
+      <c r="B38" t="inlineStr">
+        <is>
+          <t>Passed</t>
+        </is>
+      </c>
+      <c r="C38" t="inlineStr">
+        <is>
+          <t>aph(6)-Id</t>
+        </is>
+      </c>
+      <c r="D38" t="inlineStr">
+        <is>
+          <t>trimethoprim-sulfamethoxazole, doxycycline</t>
+        </is>
+      </c>
+      <c r="E38" t="inlineStr">
+        <is>
+          <t>Resistant</t>
+        </is>
+      </c>
+      <c r="F38" t="inlineStr">
+        <is>
+          <t>IncN</t>
+        </is>
+      </c>
+      <c r="G38" t="n">
+        <v>4792167</v>
+      </c>
+      <c r="H38" t="n">
+        <v>622501</v>
+      </c>
+    </row>
+    <row r="39">
+      <c r="A39" t="inlineStr">
+        <is>
+          <t>ISO-138</t>
+        </is>
+      </c>
+      <c r="B39" t="inlineStr">
+        <is>
+          <t>Passed</t>
+        </is>
+      </c>
+      <c r="C39" t="inlineStr">
+        <is>
+          <t>aac(6')-Ib-cr, aadA2, ermC</t>
+        </is>
+      </c>
+      <c r="D39" t="inlineStr">
+        <is>
+          <t>florfenicol</t>
+        </is>
+      </c>
+      <c r="E39" t="inlineStr">
+        <is>
+          <t>Susceptible</t>
+        </is>
+      </c>
+      <c r="F39" t="inlineStr">
+        <is>
+          <t>ColE1</t>
+        </is>
+      </c>
+      <c r="G39" t="n">
+        <v>4396020</v>
+      </c>
+      <c r="H39" t="n">
+        <v>591662</v>
+      </c>
+    </row>
+    <row r="40">
+      <c r="A40" t="inlineStr">
+        <is>
+          <t>ISO-139</t>
+        </is>
+      </c>
+      <c r="B40" t="inlineStr">
+        <is>
+          <t>Passed</t>
+        </is>
+      </c>
+      <c r="C40" t="inlineStr">
+        <is>
+          <t>qnrS1, mcr-1</t>
+        </is>
+      </c>
+      <c r="D40" t="inlineStr">
+        <is>
+          <t>meropenem, ciprofloxacin, amoxicillin-clavulanate</t>
+        </is>
+      </c>
+      <c r="E40" t="inlineStr">
+        <is>
+          <t>Resistant</t>
+        </is>
+      </c>
+      <c r="F40" t="inlineStr">
+        <is>
+          <t>IncB/O/K/Z</t>
+        </is>
+      </c>
+      <c r="G40" t="n">
+        <v>4717751</v>
+      </c>
+      <c r="H40" t="n">
+        <v>22096</v>
+      </c>
+    </row>
+    <row r="41">
+      <c r="A41" t="inlineStr">
+        <is>
+          <t>ISO-140</t>
+        </is>
+      </c>
+      <c r="B41" t="inlineStr">
+        <is>
+          <t>Passed</t>
+        </is>
+      </c>
+      <c r="C41" t="inlineStr">
+        <is>
+          <t>qnrS1, aph(3')-Ia, ermB, catA1, blaNDM-1</t>
+        </is>
+      </c>
+      <c r="D41" t="inlineStr">
+        <is>
+          <t>streptomycin, florfenicol</t>
+        </is>
+      </c>
+      <c r="E41" t="inlineStr">
+        <is>
+          <t>Intermediate</t>
+        </is>
+      </c>
+      <c r="F41" t="inlineStr">
+        <is>
+          <t>Col(BS512)</t>
+        </is>
+      </c>
+      <c r="G41" t="n">
+        <v>3891909</v>
+      </c>
+      <c r="H41" t="n">
+        <v>156087</v>
+      </c>
+    </row>
+    <row r="42">
+      <c r="A42" t="inlineStr">
+        <is>
+          <t>ISO-141</t>
+        </is>
+      </c>
+      <c r="B42" t="inlineStr">
+        <is>
+          <t>Failed</t>
+        </is>
+      </c>
+      <c r="C42" t="inlineStr">
+        <is>
+          <t>aadA2, blaSHV-11, aph(6)-Id, blaTEM-1, qnrB2</t>
+        </is>
+      </c>
+      <c r="D42" t="inlineStr">
+        <is>
+          <t>ceftriaxone, tetracycline, florfenicol</t>
+        </is>
+      </c>
+      <c r="E42" t="inlineStr">
+        <is>
+          <t>Intermediate</t>
+        </is>
+      </c>
+      <c r="F42" t="inlineStr">
+        <is>
+          <t>ColE1</t>
+        </is>
+      </c>
+      <c r="G42" t="n">
+        <v>4223759</v>
+      </c>
+      <c r="H42" t="n">
+        <v>354109</v>
+      </c>
+    </row>
+    <row r="43">
+      <c r="A43" t="inlineStr">
+        <is>
+          <t>ISO-142</t>
+        </is>
+      </c>
+      <c r="B43" t="inlineStr">
+        <is>
+          <t>Passed</t>
+        </is>
+      </c>
+      <c r="C43" t="inlineStr">
+        <is>
+          <t>ermB, blaSHV-11, blaOXA-48</t>
+        </is>
+      </c>
+      <c r="D43" t="inlineStr">
+        <is>
+          <t>vancomycin, ciprofloxacin, streptomycin, meropenem</t>
+        </is>
+      </c>
+      <c r="E43" t="inlineStr">
+        <is>
+          <t>Susceptible</t>
+        </is>
+      </c>
+      <c r="F43" t="inlineStr">
+        <is>
+          <t>IncB/O/K/Z</t>
+        </is>
+      </c>
+      <c r="G43" t="n">
+        <v>7100882</v>
+      </c>
+      <c r="H43" t="n">
+        <v>375358</v>
+      </c>
+    </row>
+    <row r="44">
+      <c r="A44" t="inlineStr">
+        <is>
+          <t>ISO-143</t>
+        </is>
+      </c>
+      <c r="B44" t="inlineStr">
+        <is>
+          <t>Passed</t>
+        </is>
+      </c>
+      <c r="C44" t="inlineStr">
+        <is>
+          <t>aadA1, vanA</t>
+        </is>
+      </c>
+      <c r="D44" t="inlineStr">
+        <is>
+          <t>doxycycline, gentamicin</t>
+        </is>
+      </c>
+      <c r="E44" t="inlineStr">
+        <is>
+          <t>Intermediate</t>
+        </is>
+      </c>
+      <c r="F44" t="inlineStr">
+        <is>
+          <t>IncX3</t>
+        </is>
+      </c>
+      <c r="G44" t="n">
+        <v>4545362</v>
+      </c>
+      <c r="H44" t="n">
+        <v>3085</v>
+      </c>
+    </row>
+    <row r="45">
+      <c r="A45" t="inlineStr">
+        <is>
+          <t>ISO-144</t>
+        </is>
+      </c>
+      <c r="B45" t="inlineStr">
+        <is>
+          <t>Passed</t>
+        </is>
+      </c>
+      <c r="C45" t="inlineStr">
+        <is>
+          <t>sul1, aph(6)-Id, vanA, blaCTX-M-14, blaOXA-48</t>
+        </is>
+      </c>
+      <c r="D45" t="inlineStr">
+        <is>
+          <t>colistin, kanamycin, vancomycin</t>
+        </is>
+      </c>
+      <c r="E45" t="inlineStr">
+        <is>
+          <t>Intermediate</t>
+        </is>
+      </c>
+      <c r="F45" t="inlineStr">
+        <is>
+          <t>IncX3</t>
+        </is>
+      </c>
+      <c r="G45" t="n">
+        <v>5189021</v>
+      </c>
+      <c r="H45" t="n">
+        <v>82786</v>
+      </c>
+    </row>
+    <row r="46">
+      <c r="A46" t="inlineStr">
+        <is>
+          <t>ISO-145</t>
+        </is>
+      </c>
+      <c r="B46" t="inlineStr">
+        <is>
+          <t>Failed</t>
+        </is>
+      </c>
+      <c r="C46" t="inlineStr">
+        <is>
+          <t>ermC, ermB</t>
+        </is>
+      </c>
+      <c r="D46" t="inlineStr">
+        <is>
+          <t>vancomycin, ceftriaxone</t>
+        </is>
+      </c>
+      <c r="E46" t="inlineStr">
+        <is>
+          <t>Susceptible</t>
+        </is>
+      </c>
+      <c r="F46" t="inlineStr">
+        <is>
+          <t>ColRNAI</t>
+        </is>
+      </c>
+      <c r="G46" t="n">
+        <v>5673301</v>
+      </c>
+      <c r="H46" t="n">
+        <v>13149</v>
+      </c>
+    </row>
+    <row r="47">
+      <c r="A47" t="inlineStr">
+        <is>
+          <t>ISO-146</t>
+        </is>
+      </c>
+      <c r="B47" t="inlineStr">
+        <is>
+          <t>Passed</t>
+        </is>
+      </c>
+      <c r="C47" t="inlineStr">
+        <is>
+          <t>blaNDM-1, tet(A), aadA2</t>
+        </is>
+      </c>
+      <c r="D47" t="inlineStr">
+        <is>
+          <t>tetracycline</t>
+        </is>
+      </c>
+      <c r="E47" t="inlineStr">
+        <is>
+          <t>Resistant</t>
+        </is>
+      </c>
+      <c r="F47" t="inlineStr">
+        <is>
+          <t>IncFIB(K)</t>
+        </is>
+      </c>
+      <c r="G47" t="n">
+        <v>4001945</v>
+      </c>
+      <c r="H47" t="n">
+        <v>405884</v>
+      </c>
+    </row>
+    <row r="48">
+      <c r="A48" t="inlineStr">
+        <is>
+          <t>ISO-147</t>
+        </is>
+      </c>
+      <c r="B48" t="inlineStr">
+        <is>
+          <t>Failed</t>
+        </is>
+      </c>
+      <c r="C48" t="inlineStr">
+        <is>
+          <t>aac(6')-Ib-cr, sul2, blaOXA-48, qnrS1</t>
+        </is>
+      </c>
+      <c r="D48" t="inlineStr">
+        <is>
+          <t>tetracycline, trimethoprim, doxycycline, cefotaxime</t>
+        </is>
+      </c>
+      <c r="E48" t="inlineStr">
+        <is>
+          <t>Susceptible</t>
+        </is>
+      </c>
+      <c r="F48" t="inlineStr">
+        <is>
+          <t>IncFIA</t>
+        </is>
+      </c>
+      <c r="G48" t="n">
+        <v>4482230</v>
+      </c>
+      <c r="H48" t="n">
+        <v>474409</v>
+      </c>
+    </row>
+    <row r="49">
+      <c r="A49" t="inlineStr">
+        <is>
+          <t>ISO-148</t>
+        </is>
+      </c>
+      <c r="B49" t="inlineStr">
+        <is>
+          <t>Failed</t>
+        </is>
+      </c>
+      <c r="C49" t="inlineStr">
+        <is>
+          <t>blaCTX-M-14</t>
+        </is>
+      </c>
+      <c r="D49" t="inlineStr">
+        <is>
+          <t>ampicillin, streptomycin, amikacin</t>
+        </is>
+      </c>
+      <c r="E49" t="inlineStr">
+        <is>
+          <t>Resistant</t>
+        </is>
+      </c>
+      <c r="F49" t="inlineStr">
+        <is>
+          <t>ColRNAI</t>
+        </is>
+      </c>
+      <c r="G49" t="n">
+        <v>4513472</v>
+      </c>
+      <c r="H49" t="n">
+        <v>394896</v>
+      </c>
+    </row>
+    <row r="50">
+      <c r="A50" t="inlineStr">
+        <is>
+          <t>ISO-149</t>
+        </is>
+      </c>
+      <c r="B50" t="inlineStr">
+        <is>
+          <t>Passed</t>
+        </is>
+      </c>
+      <c r="C50" t="inlineStr">
+        <is>
+          <t>aac(6')-Ib-cr, blaCTX-M-15</t>
+        </is>
+      </c>
+      <c r="D50" t="inlineStr">
+        <is>
+          <t>streptomycin</t>
+        </is>
+      </c>
+      <c r="E50" t="inlineStr">
+        <is>
+          <t>Susceptible</t>
+        </is>
+      </c>
+      <c r="F50" t="inlineStr">
+        <is>
+          <t>IncHI2</t>
+        </is>
+      </c>
+      <c r="G50" t="n">
+        <v>6754906</v>
+      </c>
+      <c r="H50" t="n">
+        <v>33698</v>
+      </c>
+    </row>
+    <row r="51">
+      <c r="A51" t="inlineStr">
+        <is>
+          <t>ISO-150</t>
+        </is>
+      </c>
+      <c r="B51" t="inlineStr">
+        <is>
+          <t>Passed</t>
+        </is>
+      </c>
+      <c r="C51" t="inlineStr">
+        <is>
+          <t>floR, blaOXA-48, catA1, sul2</t>
+        </is>
+      </c>
+      <c r="D51" t="inlineStr">
+        <is>
+          <t>amoxicillin-clavulanate, cefotaxime</t>
+        </is>
+      </c>
+      <c r="E51" t="inlineStr">
+        <is>
+          <t>Resistant</t>
+        </is>
+      </c>
+      <c r="F51" t="inlineStr">
+        <is>
+          <t>IncP1</t>
+        </is>
+      </c>
+      <c r="G51" t="n">
+        <v>6724254</v>
+      </c>
+      <c r="H51" t="n">
+        <v>582228</v>
+      </c>
+    </row>
+    <row r="52">
+      <c r="A52" t="inlineStr">
+        <is>
+          <t>ISO-151</t>
+        </is>
+      </c>
+      <c r="B52" t="inlineStr">
+        <is>
+          <t>Passed</t>
+        </is>
+      </c>
+      <c r="C52" t="inlineStr">
+        <is>
+          <t>tet(B), aadA1, tet(M), tet(A), blaTEM-1</t>
+        </is>
+      </c>
+      <c r="D52" t="inlineStr">
+        <is>
+          <t>doxycycline</t>
+        </is>
+      </c>
+      <c r="E52" t="inlineStr">
+        <is>
+          <t>Intermediate</t>
+        </is>
+      </c>
+      <c r="F52" t="inlineStr">
+        <is>
+          <t>IncX3</t>
+        </is>
+      </c>
+      <c r="G52" t="n">
+        <v>4028609</v>
+      </c>
+      <c r="H52" t="n">
+        <v>379556</v>
+      </c>
+    </row>
+    <row r="53">
+      <c r="A53" t="inlineStr">
+        <is>
+          <t>ISO-152</t>
+        </is>
+      </c>
+      <c r="B53" t="inlineStr">
+        <is>
+          <t>Failed</t>
+        </is>
+      </c>
+      <c r="C53" t="inlineStr">
+        <is>
+          <t>sul2</t>
+        </is>
+      </c>
+      <c r="D53" t="inlineStr">
+        <is>
+          <t>gentamicin</t>
+        </is>
+      </c>
+      <c r="E53" t="inlineStr">
+        <is>
+          <t>Susceptible</t>
+        </is>
+      </c>
+      <c r="F53" t="inlineStr">
+        <is>
+          <t>IncB/O/K/Z</t>
+        </is>
+      </c>
+      <c r="G53" t="n">
+        <v>5814643</v>
+      </c>
+      <c r="H53" t="n">
+        <v>210574</v>
+      </c>
+    </row>
+    <row r="54">
+      <c r="A54" t="inlineStr">
+        <is>
+          <t>ISO-153</t>
+        </is>
+      </c>
+      <c r="B54" t="inlineStr">
+        <is>
+          <t>Passed</t>
+        </is>
+      </c>
+      <c r="C54" t="inlineStr">
+        <is>
+          <t>aph(3')-Ia</t>
+        </is>
+      </c>
+      <c r="D54" t="inlineStr">
+        <is>
+          <t>meropenem, vancomycin</t>
+        </is>
+      </c>
+      <c r="E54" t="inlineStr">
+        <is>
+          <t>Resistant</t>
+        </is>
+      </c>
+      <c r="F54" t="inlineStr">
+        <is>
+          <t>IncHI2</t>
+        </is>
+      </c>
+      <c r="G54" t="n">
+        <v>4284479</v>
+      </c>
+      <c r="H54" t="n">
+        <v>324531</v>
+      </c>
+    </row>
+    <row r="55">
+      <c r="A55" t="inlineStr">
+        <is>
+          <t>ISO-154</t>
+        </is>
+      </c>
+      <c r="B55" t="inlineStr">
+        <is>
+          <t>Passed</t>
+        </is>
+      </c>
+      <c r="C55" t="inlineStr">
+        <is>
+          <t>qnrS1, aadA1, tet(B), blaCTX-M-15</t>
+        </is>
+      </c>
+      <c r="D55" t="inlineStr">
+        <is>
+          <t>meropenem, tetracycline, doxycycline, azithromycin</t>
+        </is>
+      </c>
+      <c r="E55" t="inlineStr">
+        <is>
+          <t>Intermediate</t>
+        </is>
+      </c>
+      <c r="F55" t="inlineStr">
+        <is>
+          <t>IncFIC(FII)</t>
+        </is>
+      </c>
+      <c r="G55" t="n">
+        <v>4904783</v>
+      </c>
+      <c r="H55" t="n">
+        <v>238432</v>
+      </c>
+    </row>
+    <row r="56">
+      <c r="A56" t="inlineStr">
+        <is>
+          <t>ISO-155</t>
+        </is>
+      </c>
+      <c r="B56" t="inlineStr">
+        <is>
+          <t>Passed</t>
+        </is>
+      </c>
+      <c r="C56" t="inlineStr">
+        <is>
+          <t>vanA, blaCTX-M-14, blaSHV-11</t>
+        </is>
+      </c>
+      <c r="D56" t="inlineStr">
+        <is>
+          <t>ceftriaxone</t>
+        </is>
+      </c>
+      <c r="E56" t="inlineStr">
+        <is>
+          <t>Susceptible</t>
+        </is>
+      </c>
+      <c r="F56" t="inlineStr">
+        <is>
+          <t>IncP1</t>
+        </is>
+      </c>
+      <c r="G56" t="n">
+        <v>6972810</v>
+      </c>
+      <c r="H56" t="n">
+        <v>619572</v>
+      </c>
+    </row>
+    <row r="57">
+      <c r="A57" t="inlineStr">
+        <is>
+          <t>ISO-156</t>
+        </is>
+      </c>
+      <c r="B57" t="inlineStr">
+        <is>
+          <t>Failed</t>
+        </is>
+      </c>
+      <c r="C57" t="inlineStr">
+        <is>
+          <t>mcr-1, blaCTX-M-14</t>
+        </is>
+      </c>
+      <c r="D57" t="inlineStr">
+        <is>
+          <t>levofloxacin, erythromycin, trimethoprim, chloramphenicol</t>
+        </is>
+      </c>
+      <c r="E57" t="inlineStr">
+        <is>
+          <t>Intermediate</t>
+        </is>
+      </c>
+      <c r="F57" t="inlineStr">
+        <is>
+          <t>ColE1</t>
+        </is>
+      </c>
+      <c r="G57" t="n">
+        <v>4788354</v>
+      </c>
+      <c r="H57" t="n">
+        <v>500597</v>
+      </c>
+    </row>
+    <row r="58">
+      <c r="A58" t="inlineStr">
+        <is>
+          <t>ISO-157</t>
+        </is>
+      </c>
+      <c r="B58" t="inlineStr">
+        <is>
+          <t>Passed</t>
+        </is>
+      </c>
+      <c r="C58" t="inlineStr">
+        <is>
+          <t>blaCTX-M-15, sul1, aadA2</t>
+        </is>
+      </c>
+      <c r="D58" t="inlineStr">
+        <is>
+          <t>levofloxacin</t>
+        </is>
+      </c>
+      <c r="E58" t="inlineStr">
+        <is>
+          <t>Susceptible</t>
+        </is>
+      </c>
+      <c r="F58" t="inlineStr">
+        <is>
+          <t>ColE1</t>
+        </is>
+      </c>
+      <c r="G58" t="n">
+        <v>6641787</v>
+      </c>
+      <c r="H58" t="n">
+        <v>155810</v>
+      </c>
+    </row>
+    <row r="59">
+      <c r="A59" t="inlineStr">
+        <is>
+          <t>ISO-158</t>
+        </is>
+      </c>
+      <c r="B59" t="inlineStr">
+        <is>
+          <t>Passed</t>
+        </is>
+      </c>
+      <c r="C59" t="inlineStr">
+        <is>
+          <t>aph(6)-Id</t>
+        </is>
+      </c>
+      <c r="D59" t="inlineStr">
+        <is>
+          <t>meropenem, ertapenem, imipenem, amoxicillin-clavulanate</t>
+        </is>
+      </c>
+      <c r="E59" t="inlineStr">
+        <is>
+          <t>Susceptible</t>
+        </is>
+      </c>
+      <c r="F59" t="inlineStr">
+        <is>
+          <t>IncP1</t>
+        </is>
+      </c>
+      <c r="G59" t="n">
+        <v>4646910</v>
+      </c>
+      <c r="H59" t="n">
+        <v>156261</v>
+      </c>
+    </row>
+    <row r="60">
+      <c r="A60" t="inlineStr">
+        <is>
+          <t>ISO-159</t>
+        </is>
+      </c>
+      <c r="B60" t="inlineStr">
+        <is>
+          <t>Passed</t>
+        </is>
+      </c>
+      <c r="C60" t="inlineStr">
+        <is>
+          <t>tet(B), ermB, aac(6')-Ib-cr, blaCTX-M-15, sul1</t>
+        </is>
+      </c>
+      <c r="D60" t="inlineStr">
+        <is>
+          <t>trimethoprim, streptomycin, amikacin, levofloxacin</t>
+        </is>
+      </c>
+      <c r="E60" t="inlineStr">
+        <is>
+          <t>Resistant</t>
+        </is>
+      </c>
+      <c r="F60" t="inlineStr">
+        <is>
+          <t>IncB/O/K/Z</t>
+        </is>
+      </c>
+      <c r="G60" t="n">
+        <v>6264472</v>
+      </c>
+      <c r="H60" t="n">
+        <v>549145</v>
+      </c>
+    </row>
+    <row r="61">
+      <c r="A61" t="inlineStr">
+        <is>
+          <t>ISO-160</t>
+        </is>
+      </c>
+      <c r="B61" t="inlineStr">
+        <is>
+          <t>Passed</t>
+        </is>
+      </c>
+      <c r="C61" t="inlineStr">
+        <is>
+          <t>blaTEM-1, sul2, blaSHV-11, vanA</t>
+        </is>
+      </c>
+      <c r="D61" t="inlineStr">
+        <is>
+          <t>cefotaxime</t>
+        </is>
+      </c>
+      <c r="E61" t="inlineStr">
+        <is>
+          <t>Resistant</t>
+        </is>
+      </c>
+      <c r="F61" t="inlineStr">
+        <is>
+          <t>p0111</t>
+        </is>
+      </c>
+      <c r="G61" t="n">
+        <v>6046609</v>
+      </c>
+      <c r="H61" t="n">
+        <v>361772</v>
+      </c>
+    </row>
+    <row r="62">
+      <c r="A62" t="inlineStr">
+        <is>
+          <t>ISO-161</t>
+        </is>
+      </c>
+      <c r="B62" t="inlineStr">
+        <is>
+          <t>Passed</t>
+        </is>
+      </c>
+      <c r="C62" t="inlineStr">
+        <is>
+          <t>tet(B), sul1, floR, qnrS1</t>
+        </is>
+      </c>
+      <c r="D62" t="inlineStr">
+        <is>
+          <t>amoxicillin-clavulanate, meropenem, amikacin, doxycycline</t>
+        </is>
+      </c>
+      <c r="E62" t="inlineStr">
+        <is>
+          <t>Susceptible</t>
+        </is>
+      </c>
+      <c r="F62" t="inlineStr">
+        <is>
+          <t>IncW</t>
+        </is>
+      </c>
+      <c r="G62" t="n">
+        <v>3962665</v>
+      </c>
+      <c r="H62" t="n">
+        <v>416218</v>
+      </c>
+    </row>
+    <row r="63">
+      <c r="A63" t="inlineStr">
+        <is>
+          <t>ISO-162</t>
+        </is>
+      </c>
+      <c r="B63" t="inlineStr">
+        <is>
+          <t>Failed</t>
+        </is>
+      </c>
+      <c r="C63" t="inlineStr">
+        <is>
+          <t>aadA2, tet(A), blaCTX-M-14</t>
+        </is>
+      </c>
+      <c r="D63" t="inlineStr">
+        <is>
+          <t>amikacin, tetracycline, ampicillin, streptomycin</t>
+        </is>
+      </c>
+      <c r="E63" t="inlineStr">
+        <is>
+          <t>Intermediate</t>
+        </is>
+      </c>
+      <c r="F63" t="inlineStr">
+        <is>
+          <t>p0111</t>
+        </is>
+      </c>
+      <c r="G63" t="n">
+        <v>4975859</v>
+      </c>
+      <c r="H63" t="n">
+        <v>516700</v>
+      </c>
+    </row>
+    <row r="64">
+      <c r="A64" t="inlineStr">
+        <is>
+          <t>ISO-163</t>
+        </is>
+      </c>
+      <c r="B64" t="inlineStr">
+        <is>
+          <t>Failed</t>
+        </is>
+      </c>
+      <c r="C64" t="inlineStr">
+        <is>
+          <t>tet(A)</t>
+        </is>
+      </c>
+      <c r="D64" t="inlineStr">
+        <is>
+          <t>gentamicin, azithromycin</t>
+        </is>
+      </c>
+      <c r="E64" t="inlineStr">
+        <is>
+          <t>Intermediate</t>
+        </is>
+      </c>
+      <c r="F64" t="inlineStr">
+        <is>
+          <t>IncFIB(AP001918)</t>
+        </is>
+      </c>
+      <c r="G64" t="n">
+        <v>6856806</v>
+      </c>
+      <c r="H64" t="n">
+        <v>438217</v>
+      </c>
+    </row>
+    <row r="65">
+      <c r="A65" t="inlineStr">
+        <is>
+          <t>ISO-164</t>
+        </is>
+      </c>
+      <c r="B65" t="inlineStr">
+        <is>
+          <t>Passed</t>
+        </is>
+      </c>
+      <c r="C65" t="inlineStr">
+        <is>
+          <t>floR, blaCTX-M-15, blaNDM-1, dfrA1, sul2</t>
+        </is>
+      </c>
+      <c r="D65" t="inlineStr">
+        <is>
+          <t>levofloxacin, tetracycline, amoxicillin-clavulanate, meropenem</t>
+        </is>
+      </c>
+      <c r="E65" t="inlineStr">
+        <is>
+          <t>Susceptible</t>
+        </is>
+      </c>
+      <c r="F65" t="inlineStr">
+        <is>
+          <t>IncL/M</t>
+        </is>
+      </c>
+      <c r="G65" t="n">
+        <v>5491919</v>
+      </c>
+      <c r="H65" t="n">
+        <v>143439</v>
+      </c>
+    </row>
+    <row r="66">
+      <c r="A66" t="inlineStr">
+        <is>
+          <t>ISO-165</t>
+        </is>
+      </c>
+      <c r="B66" t="inlineStr">
+        <is>
+          <t>Passed</t>
+        </is>
+      </c>
+      <c r="C66" t="inlineStr">
+        <is>
+          <t>vanA, aph(3')-Ia, blaOXA-48, blaNDM-1, blaCTX-M-14</t>
+        </is>
+      </c>
+      <c r="D66" t="inlineStr">
+        <is>
+          <t>amoxicillin-clavulanate, azithromycin</t>
+        </is>
+      </c>
+      <c r="E66" t="inlineStr">
+        <is>
+          <t>Intermediate</t>
+        </is>
+      </c>
+      <c r="F66" t="inlineStr">
+        <is>
+          <t>IncHI1</t>
+        </is>
+      </c>
+      <c r="G66" t="n">
+        <v>4949144</v>
+      </c>
+      <c r="H66" t="n">
+        <v>387444</v>
+      </c>
+    </row>
+    <row r="67">
+      <c r="A67" t="inlineStr">
+        <is>
+          <t>ISO-166</t>
+        </is>
+      </c>
+      <c r="B67" t="inlineStr">
+        <is>
+          <t>Passed</t>
+        </is>
+      </c>
+      <c r="C67" t="inlineStr">
+        <is>
+          <t>qnrB2, sul1, floR, blaTEM-1</t>
+        </is>
+      </c>
+      <c r="D67" t="inlineStr">
+        <is>
+          <t>kanamycin</t>
+        </is>
+      </c>
+      <c r="E67" t="inlineStr">
+        <is>
+          <t>Susceptible</t>
+        </is>
+      </c>
+      <c r="F67" t="inlineStr">
+        <is>
+          <t>IncFIC(FII)</t>
+        </is>
+      </c>
+      <c r="G67" t="n">
+        <v>4544839</v>
+      </c>
+      <c r="H67" t="n">
+        <v>498835</v>
+      </c>
+    </row>
+    <row r="68">
+      <c r="A68" t="inlineStr">
+        <is>
+          <t>ISO-167</t>
+        </is>
+      </c>
+      <c r="B68" t="inlineStr">
+        <is>
+          <t>Passed</t>
+        </is>
+      </c>
+      <c r="C68" t="inlineStr">
+        <is>
+          <t>mcr-1, ermC, blaOXA-48, tet(B), aac(6')-Ib-cr</t>
+        </is>
+      </c>
+      <c r="D68" t="inlineStr">
+        <is>
+          <t>gentamicin</t>
+        </is>
+      </c>
+      <c r="E68" t="inlineStr">
+        <is>
+          <t>Resistant</t>
+        </is>
+      </c>
+      <c r="F68" t="inlineStr">
+        <is>
+          <t>IncN</t>
+        </is>
+      </c>
+      <c r="G68" t="n">
+        <v>6200224</v>
+      </c>
+      <c r="H68" t="n">
+        <v>225929</v>
+      </c>
+    </row>
+    <row r="69">
+      <c r="A69" t="inlineStr">
+        <is>
+          <t>ISO-168</t>
+        </is>
+      </c>
+      <c r="B69" t="inlineStr">
+        <is>
+          <t>Passed</t>
+        </is>
+      </c>
+      <c r="C69" t="inlineStr">
+        <is>
+          <t>floR, tet(A)</t>
+        </is>
+      </c>
+      <c r="D69" t="inlineStr">
+        <is>
+          <t>amikacin, vancomycin</t>
+        </is>
+      </c>
+      <c r="E69" t="inlineStr">
+        <is>
+          <t>Resistant</t>
+        </is>
+      </c>
+      <c r="F69" t="inlineStr">
+        <is>
+          <t>IncFIB(K)</t>
+        </is>
+      </c>
+      <c r="G69" t="n">
+        <v>5788507</v>
+      </c>
+      <c r="H69" t="n">
+        <v>139941</v>
+      </c>
+    </row>
+    <row r="70">
+      <c r="A70" t="inlineStr">
+        <is>
+          <t>ISO-169</t>
+        </is>
+      </c>
+      <c r="B70" t="inlineStr">
+        <is>
+          <t>Failed</t>
+        </is>
+      </c>
+      <c r="C70" t="inlineStr">
+        <is>
+          <t>catA1, aph(3')-Ia</t>
+        </is>
+      </c>
+      <c r="D70" t="inlineStr">
+        <is>
+          <t>amikacin, colistin</t>
+        </is>
+      </c>
+      <c r="E70" t="inlineStr">
+        <is>
+          <t>Intermediate</t>
+        </is>
+      </c>
+      <c r="F70" t="inlineStr">
+        <is>
+          <t>IncFIB(AP001918)</t>
+        </is>
+      </c>
+      <c r="G70" t="n">
+        <v>5577574</v>
+      </c>
+      <c r="H70" t="n">
+        <v>395963</v>
+      </c>
+    </row>
+    <row r="71">
+      <c r="A71" t="inlineStr">
+        <is>
+          <t>ISO-170</t>
+        </is>
+      </c>
+      <c r="B71" t="inlineStr">
+        <is>
+          <t>Passed</t>
+        </is>
+      </c>
+      <c r="C71" t="inlineStr">
+        <is>
+          <t>dfrA1, tet(B), blaNDM-1</t>
+        </is>
+      </c>
+      <c r="D71" t="inlineStr">
+        <is>
+          <t>gentamicin, chloramphenicol, levofloxacin, colistin</t>
+        </is>
+      </c>
+      <c r="E71" t="inlineStr">
+        <is>
+          <t>Resistant</t>
+        </is>
+      </c>
+      <c r="F71" t="inlineStr">
+        <is>
+          <t>IncFIB(K)</t>
+        </is>
+      </c>
+      <c r="G71" t="n">
+        <v>5945444</v>
+      </c>
+      <c r="H71" t="n">
+        <v>393608</v>
+      </c>
+    </row>
+    <row r="72">
+      <c r="A72" t="inlineStr">
+        <is>
+          <t>ISO-171</t>
+        </is>
+      </c>
+      <c r="B72" t="inlineStr">
+        <is>
+          <t>Passed</t>
+        </is>
+      </c>
+      <c r="C72" t="inlineStr">
+        <is>
+          <t>floR, catA1, tet(M), aadA1, blaTEM-1</t>
+        </is>
+      </c>
+      <c r="D72" t="inlineStr">
+        <is>
+          <t>ceftriaxone, streptomycin, amikacin, vancomycin</t>
+        </is>
+      </c>
+      <c r="E72" t="inlineStr">
+        <is>
+          <t>Intermediate</t>
+        </is>
+      </c>
+      <c r="F72" t="inlineStr">
+        <is>
+          <t>IncFIB(AP001918)</t>
+        </is>
+      </c>
+      <c r="G72" t="n">
+        <v>6551965</v>
+      </c>
+      <c r="H72" t="n">
+        <v>314505</v>
+      </c>
+    </row>
+    <row r="73">
+      <c r="A73" t="inlineStr">
+        <is>
+          <t>ISO-172</t>
+        </is>
+      </c>
+      <c r="B73" t="inlineStr">
+        <is>
+          <t>Passed</t>
+        </is>
+      </c>
+      <c r="C73" t="inlineStr">
+        <is>
+          <t>blaSHV-11, qnrB2</t>
+        </is>
+      </c>
+      <c r="D73" t="inlineStr">
+        <is>
+          <t>amoxicillin-clavulanate, colistin</t>
+        </is>
+      </c>
+      <c r="E73" t="inlineStr">
+        <is>
+          <t>Intermediate</t>
+        </is>
+      </c>
+      <c r="F73" t="inlineStr">
+        <is>
+          <t>IncX3</t>
+        </is>
+      </c>
+      <c r="G73" t="n">
+        <v>6825281</v>
+      </c>
+      <c r="H73" t="n">
+        <v>27891</v>
+      </c>
+    </row>
+    <row r="74">
+      <c r="A74" t="inlineStr">
+        <is>
+          <t>ISO-173</t>
+        </is>
+      </c>
+      <c r="B74" t="inlineStr">
+        <is>
+          <t>Passed</t>
+        </is>
+      </c>
+      <c r="C74" t="inlineStr">
+        <is>
+          <t>tet(M), tet(B), sul2, sul1</t>
+        </is>
+      </c>
+      <c r="D74" t="inlineStr">
+        <is>
+          <t>amoxicillin-clavulanate, trimethoprim-sulfamethoxazole, florfenicol, ertapenem</t>
+        </is>
+      </c>
+      <c r="E74" t="inlineStr">
+        <is>
+          <t>Susceptible</t>
+        </is>
+      </c>
+      <c r="F74" t="inlineStr">
+        <is>
+          <t>IncFIA</t>
+        </is>
+      </c>
+      <c r="G74" t="n">
+        <v>6678626</v>
+      </c>
+      <c r="H74" t="n">
+        <v>561805</v>
+      </c>
+    </row>
+    <row r="75">
+      <c r="A75" t="inlineStr">
+        <is>
+          <t>ISO-174</t>
+        </is>
+      </c>
+      <c r="B75" t="inlineStr">
+        <is>
+          <t>Passed</t>
+        </is>
+      </c>
+      <c r="C75" t="inlineStr">
+        <is>
+          <t>aadA1, ermC, qnrB2, tet(M)</t>
+        </is>
+      </c>
+      <c r="D75" t="inlineStr">
+        <is>
+          <t>chloramphenicol, trimethoprim</t>
+        </is>
+      </c>
+      <c r="E75" t="inlineStr">
+        <is>
+          <t>Resistant</t>
+        </is>
+      </c>
+      <c r="F75" t="inlineStr">
+        <is>
+          <t>IncHI2</t>
+        </is>
+      </c>
+      <c r="G75" t="n">
+        <v>4336636</v>
+      </c>
+      <c r="H75" t="n">
+        <v>272416</v>
+      </c>
+    </row>
+    <row r="76">
+      <c r="A76" t="inlineStr">
+        <is>
+          <t>ISO-175</t>
+        </is>
+      </c>
+      <c r="B76" t="inlineStr">
+        <is>
+          <t>Passed</t>
+        </is>
+      </c>
+      <c r="C76" t="inlineStr">
+        <is>
+          <t>aph(6)-Id, blaOXA-48, aadA1, ermB, floR</t>
+        </is>
+      </c>
+      <c r="D76" t="inlineStr">
+        <is>
+          <t>kanamycin</t>
+        </is>
+      </c>
+      <c r="E76" t="inlineStr">
+        <is>
+          <t>Susceptible</t>
+        </is>
+      </c>
+      <c r="F76" t="inlineStr">
+        <is>
+          <t>p0111</t>
+        </is>
+      </c>
+      <c r="G76" t="n">
+        <v>5563589</v>
+      </c>
+      <c r="H76" t="n">
+        <v>348611</v>
+      </c>
+    </row>
+    <row r="77">
+      <c r="A77" t="inlineStr">
+        <is>
+          <t>ISO-176</t>
+        </is>
+      </c>
+      <c r="B77" t="inlineStr">
+        <is>
+          <t>Passed</t>
+        </is>
+      </c>
+      <c r="C77" t="inlineStr">
+        <is>
+          <t>tet(B), vanA, tet(M)</t>
+        </is>
+      </c>
+      <c r="D77" t="inlineStr">
+        <is>
+          <t>cefotaxime, ciprofloxacin, amoxicillin-clavulanate, vancomycin</t>
+        </is>
+      </c>
+      <c r="E77" t="inlineStr">
+        <is>
+          <t>Susceptible</t>
+        </is>
+      </c>
+      <c r="F77" t="inlineStr">
+        <is>
+          <t>IncFII</t>
+        </is>
+      </c>
+      <c r="G77" t="n">
+        <v>5780632</v>
+      </c>
+      <c r="H77" t="n">
+        <v>205193</v>
+      </c>
+    </row>
+    <row r="78">
+      <c r="A78" t="inlineStr">
+        <is>
+          <t>ISO-177</t>
+        </is>
+      </c>
+      <c r="B78" t="inlineStr">
+        <is>
+          <t>Passed</t>
+        </is>
+      </c>
+      <c r="C78" t="inlineStr">
+        <is>
+          <t>blaTEM-1, aadA1, sul1, qnrB2, tet(M)</t>
+        </is>
+      </c>
+      <c r="D78" t="inlineStr">
+        <is>
+          <t>amoxicillin-clavulanate, imipenem, ertapenem, streptomycin</t>
+        </is>
+      </c>
+      <c r="E78" t="inlineStr">
+        <is>
+          <t>Susceptible</t>
+        </is>
+      </c>
+      <c r="F78" t="inlineStr">
+        <is>
+          <t>IncFIC(FII)</t>
+        </is>
+      </c>
+      <c r="G78" t="n">
+        <v>4400725</v>
+      </c>
+      <c r="H78" t="n">
+        <v>332952</v>
+      </c>
+    </row>
+    <row r="79">
+      <c r="A79" t="inlineStr">
+        <is>
+          <t>ISO-178</t>
+        </is>
+      </c>
+      <c r="B79" t="inlineStr">
+        <is>
+          <t>Passed</t>
+        </is>
+      </c>
+      <c r="C79" t="inlineStr">
+        <is>
+          <t>aph(6)-Id, blaCTX-M-15</t>
+        </is>
+      </c>
+      <c r="D79" t="inlineStr">
+        <is>
+          <t>streptomycin, vancomycin, meropenem, amoxicillin-clavulanate</t>
+        </is>
+      </c>
+      <c r="E79" t="inlineStr">
+        <is>
+          <t>Intermediate</t>
+        </is>
+      </c>
+      <c r="F79" t="inlineStr">
+        <is>
+          <t>IncHI1</t>
+        </is>
+      </c>
+      <c r="G79" t="n">
+        <v>6992676</v>
+      </c>
+      <c r="H79" t="n">
+        <v>177995</v>
+      </c>
+    </row>
+    <row r="80">
+      <c r="A80" t="inlineStr">
+        <is>
+          <t>ISO-179</t>
+        </is>
+      </c>
+      <c r="B80" t="inlineStr">
+        <is>
+          <t>Passed</t>
+        </is>
+      </c>
+      <c r="C80" t="inlineStr">
+        <is>
+          <t>aph(6)-Id, blaOXA-48, qnrS1, blaCTX-M-15, blaSHV-11</t>
+        </is>
+      </c>
+      <c r="D80" t="inlineStr">
+        <is>
+          <t>vancomycin, erythromycin, doxycycline, ciprofloxacin</t>
+        </is>
+      </c>
+      <c r="E80" t="inlineStr">
+        <is>
+          <t>Resistant</t>
+        </is>
+      </c>
+      <c r="F80" t="inlineStr">
+        <is>
+          <t>IncR</t>
+        </is>
+      </c>
+      <c r="G80" t="n">
+        <v>4636403</v>
+      </c>
+      <c r="H80" t="n">
+        <v>392425</v>
+      </c>
+    </row>
+    <row r="81">
+      <c r="A81" t="inlineStr">
+        <is>
+          <t>ISO-180</t>
+        </is>
+      </c>
+      <c r="B81" t="inlineStr">
+        <is>
+          <t>Passed</t>
+        </is>
+      </c>
+      <c r="C81" t="inlineStr">
+        <is>
+          <t>ermB</t>
+        </is>
+      </c>
+      <c r="D81" t="inlineStr">
+        <is>
+          <t>ampicillin, chloramphenicol</t>
+        </is>
+      </c>
+      <c r="E81" t="inlineStr">
+        <is>
+          <t>Susceptible</t>
+        </is>
+      </c>
+      <c r="F81" t="inlineStr">
+        <is>
+          <t>IncFIA</t>
+        </is>
+      </c>
+      <c r="G81" t="n">
+        <v>4749027</v>
+      </c>
+      <c r="H81" t="n">
+        <v>362276</v>
+      </c>
+    </row>
+    <row r="82">
+      <c r="A82" t="inlineStr">
+        <is>
+          <t>ISO-181</t>
+        </is>
+      </c>
+      <c r="B82" t="inlineStr">
+        <is>
+          <t>Passed</t>
+        </is>
+      </c>
+      <c r="C82" t="inlineStr">
+        <is>
+          <t>blaSHV-11, blaTEM-1, sul1</t>
+        </is>
+      </c>
+      <c r="D82" t="inlineStr">
+        <is>
+          <t>meropenem, ceftriaxone, amoxicillin-clavulanate</t>
+        </is>
+      </c>
+      <c r="E82" t="inlineStr">
+        <is>
+          <t>Intermediate</t>
+        </is>
+      </c>
+      <c r="F82" t="inlineStr">
+        <is>
+          <t>IncFIC(FII)</t>
+        </is>
+      </c>
+      <c r="G82" t="n">
+        <v>6852748</v>
+      </c>
+      <c r="H82" t="n">
+        <v>546761</v>
+      </c>
+    </row>
+    <row r="83">
+      <c r="A83" t="inlineStr">
+        <is>
+          <t>ISO-182</t>
+        </is>
+      </c>
+      <c r="B83" t="inlineStr">
+        <is>
+          <t>Passed</t>
+        </is>
+      </c>
+      <c r="C83" t="inlineStr">
+        <is>
+          <t>qnrB2, ermB, sul2, aadA1, blaSHV-11</t>
+        </is>
+      </c>
+      <c r="D83" t="inlineStr">
+        <is>
+          <t>ciprofloxacin, tetracycline, ertapenem</t>
+        </is>
+      </c>
+      <c r="E83" t="inlineStr">
+        <is>
+          <t>Intermediate</t>
+        </is>
+      </c>
+      <c r="F83" t="inlineStr">
+        <is>
+          <t>IncFIB(K)</t>
+        </is>
+      </c>
+      <c r="G83" t="n">
+        <v>4758055</v>
+      </c>
+      <c r="H83" t="n">
+        <v>236417</v>
+      </c>
+    </row>
+    <row r="84">
+      <c r="A84" t="inlineStr">
+        <is>
+          <t>ISO-183</t>
+        </is>
+      </c>
+      <c r="B84" t="inlineStr">
+        <is>
+          <t>Passed</t>
+        </is>
+      </c>
+      <c r="C84" t="inlineStr">
+        <is>
+          <t>blaNDM-1, aac(6')-Ib-cr</t>
+        </is>
+      </c>
+      <c r="D84" t="inlineStr">
+        <is>
+          <t>trimethoprim-sulfamethoxazole</t>
+        </is>
+      </c>
+      <c r="E84" t="inlineStr">
+        <is>
+          <t>Resistant</t>
+        </is>
+      </c>
+      <c r="F84" t="inlineStr">
+        <is>
+          <t>IncQ1</t>
+        </is>
+      </c>
+      <c r="G84" t="n">
+        <v>6782611</v>
+      </c>
+      <c r="H84" t="n">
+        <v>40378</v>
+      </c>
+    </row>
+    <row r="85">
+      <c r="A85" t="inlineStr">
+        <is>
+          <t>ISO-184</t>
+        </is>
+      </c>
+      <c r="B85" t="inlineStr">
+        <is>
+          <t>Failed</t>
+        </is>
+      </c>
+      <c r="C85" t="inlineStr">
+        <is>
+          <t>floR, tet(B), aph(6)-Id, mcr-1</t>
+        </is>
+      </c>
+      <c r="D85" t="inlineStr">
+        <is>
+          <t>colistin</t>
+        </is>
+      </c>
+      <c r="E85" t="inlineStr">
+        <is>
+          <t>Susceptible</t>
+        </is>
+      </c>
+      <c r="F85" t="inlineStr">
+        <is>
+          <t>IncI1</t>
+        </is>
+      </c>
+      <c r="G85" t="n">
+        <v>6541261</v>
+      </c>
+      <c r="H85" t="n">
+        <v>21900</v>
+      </c>
+    </row>
+    <row r="86">
+      <c r="A86" t="inlineStr">
+        <is>
+          <t>ISO-185</t>
+        </is>
+      </c>
+      <c r="B86" t="inlineStr">
+        <is>
+          <t>Passed</t>
+        </is>
+      </c>
+      <c r="C86" t="inlineStr">
+        <is>
+          <t>aadA2</t>
+        </is>
+      </c>
+      <c r="D86" t="inlineStr">
+        <is>
+          <t>erythromycin</t>
+        </is>
+      </c>
+      <c r="E86" t="inlineStr">
+        <is>
+          <t>Resistant</t>
+        </is>
+      </c>
+      <c r="F86" t="inlineStr">
+        <is>
+          <t>IncR</t>
+        </is>
+      </c>
+      <c r="G86" t="n">
+        <v>4860061</v>
+      </c>
+      <c r="H86" t="n">
+        <v>498640</v>
+      </c>
+    </row>
+    <row r="87">
+      <c r="A87" t="inlineStr">
+        <is>
+          <t>ISO-186</t>
+        </is>
+      </c>
+      <c r="B87" t="inlineStr">
+        <is>
+          <t>Passed</t>
+        </is>
+      </c>
+      <c r="C87" t="inlineStr">
+        <is>
+          <t>blaNDM-1, aadA2</t>
+        </is>
+      </c>
+      <c r="D87" t="inlineStr">
+        <is>
+          <t>gentamicin</t>
+        </is>
+      </c>
+      <c r="E87" t="inlineStr">
+        <is>
+          <t>Resistant</t>
+        </is>
+      </c>
+      <c r="F87" t="inlineStr">
+        <is>
+          <t>IncL/M</t>
+        </is>
+      </c>
+      <c r="G87" t="n">
+        <v>4932366</v>
+      </c>
+      <c r="H87" t="n">
+        <v>636253</v>
+      </c>
+    </row>
+    <row r="88">
+      <c r="A88" t="inlineStr">
+        <is>
+          <t>ISO-187</t>
+        </is>
+      </c>
+      <c r="B88" t="inlineStr">
+        <is>
+          <t>Passed</t>
+        </is>
+      </c>
+      <c r="C88" t="inlineStr">
+        <is>
+          <t>sul2, blaTEM-1</t>
+        </is>
+      </c>
+      <c r="D88" t="inlineStr">
+        <is>
+          <t>gentamicin</t>
+        </is>
+      </c>
+      <c r="E88" t="inlineStr">
+        <is>
+          <t>Resistant</t>
+        </is>
+      </c>
+      <c r="F88" t="inlineStr">
+        <is>
+          <t>IncHI2</t>
+        </is>
+      </c>
+      <c r="G88" t="n">
+        <v>4633184</v>
+      </c>
+      <c r="H88" t="n">
+        <v>639784</v>
+      </c>
+    </row>
+    <row r="89">
+      <c r="A89" t="inlineStr">
+        <is>
+          <t>ISO-188</t>
+        </is>
+      </c>
+      <c r="B89" t="inlineStr">
+        <is>
+          <t>Passed</t>
+        </is>
+      </c>
+      <c r="C89" t="inlineStr">
+        <is>
+          <t>aph(6)-Id, tet(B)</t>
+        </is>
+      </c>
+      <c r="D89" t="inlineStr">
+        <is>
+          <t>tetracycline, florfenicol</t>
+        </is>
+      </c>
+      <c r="E89" t="inlineStr">
+        <is>
+          <t>Resistant</t>
+        </is>
+      </c>
+      <c r="F89" t="inlineStr">
+        <is>
+          <t>Col(BS512)</t>
+        </is>
+      </c>
+      <c r="G89" t="n">
+        <v>6099060</v>
+      </c>
+      <c r="H89" t="n">
+        <v>521665</v>
+      </c>
+    </row>
+    <row r="90">
+      <c r="A90" t="inlineStr">
+        <is>
+          <t>ISO-189</t>
+        </is>
+      </c>
+      <c r="B90" t="inlineStr">
+        <is>
+          <t>Passed</t>
+        </is>
+      </c>
+      <c r="C90" t="inlineStr">
+        <is>
+          <t>aadA2, qnrS1</t>
+        </is>
+      </c>
+      <c r="D90" t="inlineStr">
+        <is>
+          <t>kanamycin, ampicillin, chloramphenicol</t>
+        </is>
+      </c>
+      <c r="E90" t="inlineStr">
+        <is>
+          <t>Resistant</t>
+        </is>
+      </c>
+      <c r="F90" t="inlineStr">
+        <is>
+          <t>ColE1</t>
+        </is>
+      </c>
+      <c r="G90" t="n">
+        <v>6606081</v>
+      </c>
+      <c r="H90" t="n">
+        <v>519305</v>
+      </c>
+    </row>
+    <row r="91">
+      <c r="A91" t="inlineStr">
+        <is>
+          <t>ISO-190</t>
+        </is>
+      </c>
+      <c r="B91" t="inlineStr">
+        <is>
+          <t>Failed</t>
+        </is>
+      </c>
+      <c r="C91" t="inlineStr">
+        <is>
+          <t>blaCTX-M-15, aph(6)-Id</t>
+        </is>
+      </c>
+      <c r="D91" t="inlineStr">
+        <is>
+          <t>cefotaxime</t>
+        </is>
+      </c>
+      <c r="E91" t="inlineStr">
+        <is>
+          <t>Susceptible</t>
+        </is>
+      </c>
+      <c r="F91" t="inlineStr">
+        <is>
+          <t>IncFIA</t>
+        </is>
+      </c>
+      <c r="G91" t="n">
+        <v>5715753</v>
+      </c>
+      <c r="H91" t="n">
+        <v>311601</v>
+      </c>
     </row>
   </sheetData>
   <pageMargins left="0.5" right="0.5" top="0.75" bottom="0.75" header="0.277778" footer="0.277778"/>
-  <pageSetup firstPageNumber="1" fitToHeight="1" fitToWidth="1" scale="72" useFirstPageNumber="0" orientation="portrait" pageOrder="downThenOver"/>
+  <pageSetup orientation="portrait" scale="72" fitToHeight="1" fitToWidth="1" firstPageNumber="1" useFirstPageNumber="0" pageOrder="downThenOver"/>
   <headerFooter>
-    <oddFooter>&amp;C&amp;"Helvetica Neue,Regular"&amp;12&amp;K000000&amp;P</oddFooter>
+    <oddHeader/>
+    <oddFooter>&amp;C&amp;"Helvetica Neue,Regular"&amp;12 &amp;K000000&amp;P</oddFooter>
+    <evenHeader/>
+    <evenFooter/>
+    <firstHeader/>
+    <firstFooter/>
   </headerFooter>
 </worksheet>
 </file>